--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352D2E90-A09A-47EF-8732-65547AD15861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3B50DB-0A71-4894-B84A-351264157695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57315" yWindow="0" windowWidth="20955" windowHeight="16665" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <author>tc={B694AA91-5F28-404D-8B9F-89A2BFECAE55}</author>
     <author>tc={15E8E758-37B6-468B-81A6-B3305FD6827A}</author>
     <author>tc={95169845-1F7F-4051-990A-FE3D69449576}</author>
+    <author>tc={939E2C75-C2A6-4046-AF27-AFF4D420F9BB}</author>
   </authors>
   <commentList>
     <comment ref="L6" authorId="0" shapeId="0" xr:uid="{B694AA91-5F28-404D-8B9F-89A2BFECAE55}">
@@ -59,7 +60,17 @@
     Q2: 410-414m</t>
       </text>
     </comment>
-    <comment ref="S6" authorId="2" shapeId="0" xr:uid="{95169845-1F7F-4051-990A-FE3D69449576}">
+    <comment ref="V6" authorId="2" shapeId="0" xr:uid="{95169845-1F7F-4051-990A-FE3D69449576}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Q2: 1610-1630m
+Reply:
+    Q1: 1600-1620m</t>
+      </text>
+    </comment>
+    <comment ref="V7" authorId="3" shapeId="0" xr:uid="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -74,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>Price</t>
   </si>
@@ -248,12 +259,47 @@
   </si>
   <si>
     <t>CFFO</t>
+  </si>
+  <si>
+    <t>Q123</t>
+  </si>
+  <si>
+    <t>Q223</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>Terminal Rate</t>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Market Cap</t>
+  </si>
+  <si>
+    <t>FY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -276,9 +322,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -290,7 +336,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -298,12 +344,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -328,18 +392,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -416,9 +489,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -456,7 +529,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -562,7 +635,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -704,7 +777,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -718,10 +791,16 @@
   <threadedComment ref="M6" dT="2022-09-02T14:59:12.36" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{15E8E758-37B6-468B-81A6-B3305FD6827A}">
     <text>Q2: 410-414m</text>
   </threadedComment>
-  <threadedComment ref="S6" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{95169845-1F7F-4051-990A-FE3D69449576}">
+  <threadedComment ref="V6" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{95169845-1F7F-4051-990A-FE3D69449576}">
     <text>Q2: 1610-1630m</text>
   </threadedComment>
-  <threadedComment ref="S6" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{618BFB8A-809A-468A-BF3E-6286A5CBAEB3}" parentId="{95169845-1F7F-4051-990A-FE3D69449576}">
+  <threadedComment ref="V6" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{618BFB8A-809A-468A-BF3E-6286A5CBAEB3}" parentId="{95169845-1F7F-4051-990A-FE3D69449576}">
+    <text>Q1: 1600-1620m</text>
+  </threadedComment>
+  <threadedComment ref="V7" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
+    <text>Q2: 1610-1630m</text>
+  </threadedComment>
+  <threadedComment ref="V7" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{67F1968D-792E-4F6B-B86B-D7480C200BB9}" parentId="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
     <text>Q1: 1600-1620m</text>
   </threadedComment>
 </ThreadedComments>
@@ -737,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>97.2</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -745,11 +824,9 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>315</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>296.27</v>
+      </c>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N4" t="s">
@@ -757,7 +834,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>30618</v>
+        <v>32551.1849</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -765,22 +842,18 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <v>1707</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N6" t="s">
         <v>4</v>
       </c>
       <c r="O6" s="5">
-        <v>737</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>846.33</v>
+      </c>
+      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N7" t="s">
@@ -788,7 +861,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>29648</v>
+        <v>31395.514900000002</v>
       </c>
     </row>
   </sheetData>
@@ -798,20 +871,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
-  <dimension ref="A1:U54"/>
+  <dimension ref="A1:CZ54"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="2"/>
+    <col min="3" max="13" width="9.140625" style="2"/>
+    <col min="14" max="14" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:104" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="L1" s="13">
+        <v>44742</v>
+      </c>
+      <c r="M1" s="13">
+        <v>44834</v>
+      </c>
+      <c r="N1" s="13">
+        <v>44926</v>
+      </c>
+      <c r="O1" s="14">
+        <v>45016</v>
+      </c>
+      <c r="S1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:104" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -848,27 +939,56 @@
       <c r="N2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2">
+      <c r="O2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2">
+        <v>2019</v>
+      </c>
+      <c r="T2">
         <v>2020</v>
       </c>
-      <c r="R2">
-        <f>+Q2+1</f>
+      <c r="U2">
+        <f>+T2+1</f>
         <v>2021</v>
       </c>
-      <c r="S2">
-        <f t="shared" ref="S2:U2" si="0">+R2+1</f>
+      <c r="V2">
+        <f t="shared" ref="V2:X2" si="0">+U2+1</f>
         <v>2022</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="U2">
+      <c r="X2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="Y2">
+        <v>2025</v>
+      </c>
+      <c r="Z2">
+        <v>2026</v>
+      </c>
+      <c r="AA2">
+        <v>2027</v>
+      </c>
+      <c r="AB2">
+        <v>2028</v>
+      </c>
+      <c r="AC2">
+        <v>2029</v>
+      </c>
+      <c r="AD2">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="3" spans="1:104" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -885,7 +1005,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:104" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
@@ -916,17 +1036,360 @@
         <v>406.13799999999998</v>
       </c>
       <c r="M6" s="4">
-        <v>415</v>
+        <v>436.53300000000002</v>
       </c>
       <c r="N6" s="4">
-        <v>450</v>
+        <v>469.399</v>
+      </c>
+      <c r="O6" s="3">
+        <v>481.714</v>
+      </c>
+      <c r="P6" s="3">
+        <v>509.64</v>
       </c>
       <c r="S6" s="3">
-        <f>SUM(K6:N6)</f>
-        <v>1634.1679999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>362.78</v>
+      </c>
+      <c r="T6" s="3">
+        <v>603.46600000000001</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1028.7840000000001</v>
+      </c>
+      <c r="V6" s="3">
+        <f>SUM($K$6:$N$6)</f>
+        <v>1675.1</v>
+      </c>
+      <c r="W6" s="3">
+        <f t="shared" ref="W6:AD6" si="1">V6*(1+$S$23)</f>
+        <v>2177.63</v>
+      </c>
+      <c r="X6" s="3">
+        <f t="shared" si="1"/>
+        <v>2830.9190000000003</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="1"/>
+        <v>3680.1947000000005</v>
+      </c>
+      <c r="Z6" s="3">
+        <f t="shared" si="1"/>
+        <v>4784.2531100000006</v>
+      </c>
+      <c r="AA6" s="3">
+        <f t="shared" si="1"/>
+        <v>6219.5290430000014</v>
+      </c>
+      <c r="AB6" s="3">
+        <f t="shared" si="1"/>
+        <v>8085.387755900002</v>
+      </c>
+      <c r="AC6" s="3">
+        <f t="shared" si="1"/>
+        <v>10511.004082670002</v>
+      </c>
+      <c r="AD6" s="3">
+        <f t="shared" si="1"/>
+        <v>13664.305307471004</v>
+      </c>
+      <c r="AE6" s="3">
+        <f>AD6*(1+S24)</f>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AF6" s="3">
+        <f t="shared" ref="AF6:CQ6" si="2">AE6*(1+T24)</f>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AG6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AH6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AI6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AJ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AK6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AL6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AM6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AN6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AO6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AP6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AQ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AR6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AS6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AT6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AU6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AV6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AW6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AX6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AY6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="AZ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BA6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BB6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BC6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BD6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BE6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BF6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BG6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BH6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BI6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BJ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BK6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BL6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BM6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BN6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BO6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BP6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BQ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BR6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BS6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BT6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BU6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BV6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BW6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BX6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BY6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="BZ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CA6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CB6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CC6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CD6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CE6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CF6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CG6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CH6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CI6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CJ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CK6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CL6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CM6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CN6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CO6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CP6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CQ6" s="3">
+        <f t="shared" si="2"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CR6" s="3">
+        <f t="shared" ref="CR6:CZ6" si="3">CQ6*(1+CF24)</f>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CS6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CT6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CU6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CV6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CW6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CX6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CY6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+      <c r="CZ6" s="3">
+        <f t="shared" si="3"/>
+        <v>13800.948360545714</v>
+      </c>
+    </row>
+    <row r="7" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -956,51 +1419,92 @@
       <c r="L7" s="6">
         <v>81.924999999999997</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="6">
+        <v>93.599000000000004</v>
+      </c>
+      <c r="N7" s="6">
+        <v>96.757000000000005</v>
+      </c>
+      <c r="O7" s="5">
+        <v>99.914000000000001</v>
+      </c>
+      <c r="P7" s="5">
+        <v>101.846</v>
+      </c>
+      <c r="S7" s="3">
+        <v>362.78</v>
+      </c>
+      <c r="T7" s="3">
+        <v>603.46600000000001</v>
+      </c>
+      <c r="U7" s="3">
+        <v>1028.7840000000001</v>
+      </c>
+      <c r="V7" s="3">
+        <f>SUM($K$6:$N$6)</f>
+        <v>1675.1</v>
+      </c>
+      <c r="W7" s="5">
+        <f>SUM(O6:R6)</f>
+        <v>991.35400000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
-        <f>+E6-E7</f>
+        <f t="shared" ref="E8:P8" si="4">+E6-E7</f>
         <v>120.691</v>
       </c>
       <c r="F8" s="6">
-        <f>+F6-F7</f>
+        <f t="shared" si="4"/>
         <v>136.67500000000001</v>
       </c>
       <c r="G8" s="6">
-        <f>+G6-G7</f>
+        <f t="shared" si="4"/>
         <v>151.88300000000001</v>
       </c>
       <c r="H8" s="6">
-        <f>+H6-H7</f>
+        <f t="shared" si="4"/>
         <v>176.45100000000002</v>
       </c>
       <c r="I8" s="6">
-        <f>+I6-I7</f>
+        <f t="shared" si="4"/>
         <v>207.15600000000001</v>
       </c>
       <c r="J8" s="6">
-        <f>+J6-J7</f>
+        <f t="shared" si="4"/>
         <v>259.04899999999998</v>
       </c>
       <c r="K8" s="6">
-        <f>+K6-K7</f>
+        <f t="shared" si="4"/>
         <v>288.56799999999998</v>
       </c>
       <c r="L8" s="6">
-        <f>+L6-L7</f>
+        <f t="shared" si="4"/>
         <v>324.21299999999997</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="6">
+        <f t="shared" si="4"/>
+        <v>342.93400000000003</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" si="4"/>
+        <v>372.642</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="4"/>
+        <v>381.8</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="4"/>
+        <v>407.79399999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -1030,10 +1534,20 @@
       <c r="L9" s="6">
         <v>177.69900000000001</v>
       </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="6">
+        <v>205.38800000000001</v>
+      </c>
+      <c r="N9" s="6">
+        <v>218.65600000000001</v>
+      </c>
+      <c r="O9" s="5">
+        <v>229.47800000000001</v>
+      </c>
+      <c r="P9" s="5">
+        <v>239.494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
@@ -1063,10 +1577,20 @@
       <c r="L10" s="6">
         <v>115.27</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M10" s="6">
+        <v>129.49299999999999</v>
+      </c>
+      <c r="N10" s="6">
+        <v>149.35900000000001</v>
+      </c>
+      <c r="O10" s="5">
+        <v>144.971</v>
+      </c>
+      <c r="P10" s="5">
+        <v>147.45500000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1096,92 +1620,130 @@
       <c r="L11" s="6">
         <v>34.383000000000003</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="6">
+        <v>39.395000000000003</v>
+      </c>
+      <c r="N11" s="6">
+        <v>39.255000000000003</v>
+      </c>
+      <c r="O11" s="5">
+        <v>42.320999999999998</v>
+      </c>
+      <c r="P11" s="5">
+        <v>42.670999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f>SUM(E9:E11)</f>
+        <f t="shared" ref="E12:P12" si="5">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
-        <f>SUM(F9:F11)</f>
+        <f t="shared" si="5"/>
         <v>145.613</v>
       </c>
       <c r="G12" s="6">
-        <f>SUM(G9:G11)</f>
+        <f t="shared" si="5"/>
         <v>164.71299999999999</v>
       </c>
       <c r="H12" s="6">
-        <f>SUM(H9:H11)</f>
+        <f t="shared" si="5"/>
         <v>186.33699999999999</v>
       </c>
       <c r="I12" s="6">
-        <f>SUM(I9:I11)</f>
+        <f t="shared" si="5"/>
         <v>212.05100000000002</v>
       </c>
       <c r="J12" s="6">
-        <f>SUM(J9:J11)</f>
+        <f t="shared" si="5"/>
         <v>250.59399999999999</v>
       </c>
       <c r="K12" s="6">
-        <f>SUM(K9:K11)</f>
+        <f t="shared" si="5"/>
         <v>278.154</v>
       </c>
       <c r="L12" s="6">
-        <f>SUM(L9:L11)</f>
+        <f t="shared" si="5"/>
         <v>327.35199999999998</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M12" s="6">
+        <f t="shared" si="5"/>
+        <v>374.27599999999995</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="5"/>
+        <v>407.27</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="5"/>
+        <v>416.77</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="5"/>
+        <v>429.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f>E8-E12</f>
+        <f t="shared" ref="E13:P13" si="6">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
-        <f>F8-F12</f>
+        <f t="shared" si="6"/>
         <v>-8.9379999999999882</v>
       </c>
       <c r="G13" s="6">
-        <f>G8-G12</f>
+        <f t="shared" si="6"/>
         <v>-12.829999999999984</v>
       </c>
       <c r="H13" s="6">
-        <f>H8-H12</f>
+        <f t="shared" si="6"/>
         <v>-9.8859999999999673</v>
       </c>
       <c r="I13" s="6">
-        <f>I8-I12</f>
+        <f t="shared" si="6"/>
         <v>-4.8950000000000102</v>
       </c>
       <c r="J13" s="6">
-        <f>J8-J12</f>
+        <f t="shared" si="6"/>
         <v>8.4549999999999841</v>
       </c>
       <c r="K13" s="6">
-        <f>K8-K12</f>
+        <f t="shared" si="6"/>
         <v>10.413999999999987</v>
       </c>
       <c r="L13" s="6">
         <f>L8-L12</f>
         <v>-3.13900000000001</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="6">
+        <f t="shared" si="6"/>
+        <v>-31.341999999999928</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="6"/>
+        <v>-34.627999999999986</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" si="6"/>
+        <v>-34.96999999999997</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="6"/>
+        <v>-21.826000000000022</v>
+      </c>
+    </row>
+    <row r="14" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -1216,51 +1778,79 @@
         <f>-4.541+7.669</f>
         <v>3.1279999999999992</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M14" s="6">
+        <f>12.011-2.885</f>
+        <v>9.1259999999999994</v>
+      </c>
+      <c r="N14" s="6">
+        <f>11.793-2.175</f>
+        <v>9.6179999999999986</v>
+      </c>
+      <c r="O14" s="5">
+        <f>16.727-2.181</f>
+        <v>14.545999999999999</v>
+      </c>
+      <c r="P14" s="5">
+        <f>22.624-1.526</f>
+        <v>21.097999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f>+E13+E14</f>
+        <f t="shared" ref="E15:P15" si="7">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
-        <f>+F13+F14</f>
+        <f t="shared" si="7"/>
         <v>-15.166999999999987</v>
       </c>
       <c r="G15" s="6">
-        <f>+G13+G14</f>
+        <f t="shared" si="7"/>
         <v>-12.528999999999986</v>
       </c>
       <c r="H15" s="6">
-        <f>+H13+H14</f>
+        <f t="shared" si="7"/>
         <v>-9.6579999999999675</v>
       </c>
       <c r="I15" s="6">
-        <f>+I13+I14</f>
+        <f t="shared" si="7"/>
         <v>-4.7670000000000101</v>
       </c>
       <c r="J15" s="6">
-        <f>+J13+J14</f>
+        <f t="shared" si="7"/>
         <v>8.531999999999984</v>
       </c>
       <c r="K15" s="6">
-        <f>+K13+K14</f>
+        <f t="shared" si="7"/>
         <v>10.853999999999989</v>
       </c>
       <c r="L15" s="6">
-        <f>+L13+L14</f>
+        <f t="shared" si="7"/>
         <v>-1.1000000000010779E-2</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M15" s="6">
+        <f t="shared" si="7"/>
+        <v>-22.21599999999993</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="7"/>
+        <v>-25.009999999999987</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" si="7"/>
+        <v>-20.423999999999971</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="7"/>
+        <v>-0.72800000000002285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1290,92 +1880,130 @@
       <c r="L16" s="6">
         <v>4.8680000000000003</v>
       </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="6">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="N16" s="6">
+        <v>3.18</v>
+      </c>
+      <c r="O16" s="5">
+        <v>3.6619999999999999</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3.0609999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f>+E15-E16</f>
+        <f t="shared" ref="E17:P17" si="8">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
-        <f>+F15-F16</f>
+        <f t="shared" si="8"/>
         <v>-16.159999999999986</v>
       </c>
       <c r="G17" s="6">
-        <f>+G15-G16</f>
+        <f t="shared" si="8"/>
         <v>-11.989999999999986</v>
       </c>
       <c r="H17" s="6">
-        <f>+H15-H16</f>
+        <f t="shared" si="8"/>
         <v>-6.6979999999999675</v>
       </c>
       <c r="I17" s="6">
-        <f>+I15-I16</f>
+        <f t="shared" si="8"/>
         <v>-4.0500000000000105</v>
       </c>
       <c r="J17" s="6">
-        <f>+J15-J16</f>
+        <f t="shared" si="8"/>
         <v>7.1689999999999845</v>
       </c>
       <c r="K17" s="6">
-        <f>+K15-K16</f>
+        <f t="shared" si="8"/>
         <v>9.7379999999999889</v>
       </c>
       <c r="L17" s="6">
-        <f>+L15-L16</f>
+        <f t="shared" si="8"/>
         <v>-4.8790000000000111</v>
       </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="6">
+        <f t="shared" si="8"/>
+        <v>-25.141999999999932</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" si="8"/>
+        <v>-28.189999999999987</v>
+      </c>
+      <c r="O17" s="6">
+        <f t="shared" si="8"/>
+        <v>-24.08599999999997</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="8"/>
+        <v>-3.7890000000000228</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f>+E17/E19</f>
+        <f t="shared" ref="E18:P18" si="9">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
-        <f>+F17/F19</f>
+        <f t="shared" si="9"/>
         <v>-5.3147929500060795E-2</v>
       </c>
       <c r="G18" s="7">
-        <f>+G17/G19</f>
+        <f t="shared" si="9"/>
         <v>-3.9178653352241861E-2</v>
       </c>
       <c r="H18" s="7">
-        <f>+H17/H19</f>
+        <f t="shared" si="9"/>
         <v>-2.1745411809011676E-2</v>
       </c>
       <c r="I18" s="7">
-        <f>+I17/I19</f>
+        <f t="shared" si="9"/>
         <v>-1.3054114947122809E-2</v>
       </c>
       <c r="J18" s="7">
-        <f>+J17/J19</f>
+        <f t="shared" si="9"/>
         <v>2.0727021455604115E-2</v>
       </c>
       <c r="K18" s="7">
-        <f>+K17/K19</f>
+        <f t="shared" si="9"/>
         <v>2.8171540321927365E-2</v>
       </c>
       <c r="L18" s="7">
-        <f>+L17/L19</f>
+        <f t="shared" si="9"/>
         <v>-1.5498975523753589E-2</v>
       </c>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="7">
+        <f t="shared" si="9"/>
+        <v>-7.9565809044589805E-2</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="9"/>
+        <v>-8.8829928028536453E-2</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="9"/>
+        <v>-7.5437068960117162E-2</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" si="9"/>
+        <v>-1.1759229086169245E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1406,11 +2034,19 @@
         <v>314.79500000000002</v>
       </c>
       <c r="M19" s="6">
-        <v>347</v>
-      </c>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="21" spans="2:14" s="11" customFormat="1" x14ac:dyDescent="0.2">
+        <v>315.99</v>
+      </c>
+      <c r="N19" s="6">
+        <v>317.34800000000001</v>
+      </c>
+      <c r="O19" s="5">
+        <v>319.286</v>
+      </c>
+      <c r="P19" s="5">
+        <v>322.21499999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
@@ -1421,15 +2057,15 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:K21" si="1">+I6/E6-1</f>
+        <f t="shared" ref="I21:K21" si="10">+I6/E6-1</f>
         <v>0.74875060610958455</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.83741431074009598</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0.82841515192723181</v>
       </c>
       <c r="L21" s="10">
@@ -1438,61 +2074,83 @@
       </c>
       <c r="M21" s="10">
         <f>+M6/I6-1</f>
-        <v>0.53426399692407789</v>
+        <v>0.61387196474520134</v>
       </c>
       <c r="N21" s="10">
         <f>+N6/J6-1</f>
-        <v>0.37953022397439606</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="13" t="s">
+        <v>0.43900023911857233</v>
+      </c>
+      <c r="O21" s="10">
+        <f>+O6/K6-1</f>
+        <v>0.32692614935404807</v>
+      </c>
+      <c r="P21" s="10">
+        <f>+P6/L6-1</f>
+        <v>0.25484441249033574</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15">
-        <f t="shared" ref="E22:H22" si="2">+E8/E6</f>
+      <c r="E22" s="12">
+        <f t="shared" ref="E22:H22" si="11">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
-      <c r="F22" s="15">
-        <f t="shared" si="2"/>
+      <c r="F22" s="12">
+        <f t="shared" si="11"/>
         <v>0.76986554460911061</v>
       </c>
-      <c r="G22" s="15">
-        <f t="shared" si="2"/>
+      <c r="G22" s="12">
+        <f t="shared" si="11"/>
         <v>0.7649648197674126</v>
       </c>
-      <c r="H22" s="15">
-        <f t="shared" si="2"/>
+      <c r="H22" s="12">
+        <f t="shared" si="11"/>
         <v>0.75552025485015994</v>
       </c>
-      <c r="I22" s="15">
-        <f t="shared" ref="I22:L22" si="3">+I8/I6</f>
+      <c r="I22" s="12">
+        <f t="shared" ref="I22:K22" si="12">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
-      <c r="J22" s="15">
-        <f t="shared" si="3"/>
+      <c r="J22" s="12">
+        <f t="shared" si="12"/>
         <v>0.79414649997854059</v>
       </c>
-      <c r="K22" s="15">
-        <f t="shared" si="3"/>
+      <c r="K22" s="12">
+        <f t="shared" si="12"/>
         <v>0.79488747486433631</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="12">
         <f>+L8/L6</f>
         <v>0.79828284967178642</v>
       </c>
-      <c r="M22" s="15">
-        <f t="shared" ref="M22:N22" si="4">+M8/M6</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="15">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="12">
+        <f t="shared" ref="M22:P22" si="13">+M8/M6</f>
+        <v>0.78558551129009724</v>
+      </c>
+      <c r="N22" s="12">
+        <f t="shared" si="13"/>
+        <v>0.79387045988593929</v>
+      </c>
+      <c r="O22" s="12">
+        <f t="shared" si="13"/>
+        <v>0.79258647247121738</v>
+      </c>
+      <c r="P22" s="12">
+        <f t="shared" si="13"/>
+        <v>0.8001608978887057</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R23" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="S23" s="20">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
@@ -1514,8 +2172,14 @@
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R24" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="S24" s="16">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -1535,8 +2199,14 @@
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R25" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="S25" s="16">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -1558,8 +2228,15 @@
       </c>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R26" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="S26" s="18">
+        <f>NPV(S25,S6:CZ6)</f>
+        <v>57693.064395439622</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -1579,8 +2256,15 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R27" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S27" s="21">
+        <f>Main!O3</f>
+        <v>296.27</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -1600,8 +2284,15 @@
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R28" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" s="19">
+        <f>S26/S27</f>
+        <v>194.73137474411729</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -1621,8 +2312,15 @@
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R29" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="S29" s="20">
+        <f>(S28-Main!O2)/Main!O2</f>
+        <v>0.77237985568505763</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -1644,8 +2342,15 @@
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
-    </row>
-    <row r="31" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R30" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="S30" s="18">
+        <f>S27*S28</f>
+        <v>57693.064395439629</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -1666,7 +2371,7 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
         <v>32</v>
       </c>

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3B50DB-0A71-4894-B84A-351264157695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88AB9AE-FF4F-40BD-8881-5052BBAE5BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="37440" windowHeight="20805" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
     Q2: 410-414m</t>
       </text>
     </comment>
-    <comment ref="V6" authorId="2" shapeId="0" xr:uid="{95169845-1F7F-4051-990A-FE3D69449576}">
+    <comment ref="Y6" authorId="2" shapeId="0" xr:uid="{95169845-1F7F-4051-990A-FE3D69449576}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,7 +70,7 @@
     Q1: 1600-1620m</t>
       </text>
     </comment>
-    <comment ref="V7" authorId="3" shapeId="0" xr:uid="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
+    <comment ref="Y7" authorId="3" shapeId="0" xr:uid="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>Price</t>
   </si>
@@ -289,16 +289,36 @@
   </si>
   <si>
     <t>FY</t>
+  </si>
+  <si>
+    <t>Q323</t>
+  </si>
+  <si>
+    <t>YOY%</t>
+  </si>
+  <si>
+    <t>Q423</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>if growth accelerates up</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -367,7 +387,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -406,6 +426,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -791,16 +816,16 @@
   <threadedComment ref="M6" dT="2022-09-02T14:59:12.36" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{15E8E758-37B6-468B-81A6-B3305FD6827A}">
     <text>Q2: 410-414m</text>
   </threadedComment>
-  <threadedComment ref="V6" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{95169845-1F7F-4051-990A-FE3D69449576}">
+  <threadedComment ref="Y6" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{95169845-1F7F-4051-990A-FE3D69449576}">
     <text>Q2: 1610-1630m</text>
   </threadedComment>
-  <threadedComment ref="V6" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{618BFB8A-809A-468A-BF3E-6286A5CBAEB3}" parentId="{95169845-1F7F-4051-990A-FE3D69449576}">
+  <threadedComment ref="Y6" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{618BFB8A-809A-468A-BF3E-6286A5CBAEB3}" parentId="{95169845-1F7F-4051-990A-FE3D69449576}">
     <text>Q1: 1600-1620m</text>
   </threadedComment>
-  <threadedComment ref="V7" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
+  <threadedComment ref="Y7" dT="2022-09-02T14:59:40.61" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
     <text>Q2: 1610-1630m</text>
   </threadedComment>
-  <threadedComment ref="V7" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{67F1968D-792E-4F6B-B86B-D7480C200BB9}" parentId="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
+  <threadedComment ref="Y7" dT="2022-09-02T15:01:04.51" personId="{6EBEE36F-B86D-4667-B671-D0667117F4FF}" id="{67F1968D-792E-4F6B-B86B-D7480C200BB9}" parentId="{939E2C75-C2A6-4046-AF27-AFF4D420F9BB}">
     <text>Q1: 1600-1620m</text>
   </threadedComment>
 </ThreadedComments>
@@ -816,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>109.87</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -824,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>296.27</v>
+        <v>325.55700000000002</v>
       </c>
       <c r="P3" s="2"/>
     </row>
@@ -834,7 +859,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>32551.1849</v>
+        <v>43920.894870000004</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -842,7 +867,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <v>2002</v>
+        <v>2080</v>
       </c>
       <c r="P5" s="2"/>
     </row>
@@ -851,7 +876,7 @@
         <v>4</v>
       </c>
       <c r="O6" s="5">
-        <v>846.33</v>
+        <v>1736.826</v>
       </c>
       <c r="P6" s="2"/>
     </row>
@@ -861,7 +886,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>31395.514900000002</v>
+        <v>43577.720870000005</v>
       </c>
     </row>
   </sheetData>
@@ -871,18 +896,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
-  <dimension ref="A1:CZ54"/>
+  <dimension ref="A1:DC54"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="13" width="9.140625" style="2"/>
     <col min="14" max="14" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:107" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -898,11 +925,20 @@
       <c r="O1" s="14">
         <v>45016</v>
       </c>
-      <c r="S1" t="s">
+      <c r="P1" s="13">
+        <v>45107</v>
+      </c>
+      <c r="Q1" s="13">
+        <v>45199</v>
+      </c>
+      <c r="R1" s="13">
+        <v>45291</v>
+      </c>
+      <c r="V1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:104" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -945,50 +981,57 @@
       <c r="P2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2">
+      <c r="Q2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2">
         <v>2019</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <v>2020</v>
       </c>
-      <c r="U2">
-        <f>+T2+1</f>
+      <c r="X2">
+        <f>+W2+1</f>
         <v>2021</v>
       </c>
-      <c r="V2">
-        <f t="shared" ref="V2:X2" si="0">+U2+1</f>
+      <c r="Y2">
+        <f t="shared" ref="Y2:AA2" si="0">+X2+1</f>
         <v>2022</v>
       </c>
-      <c r="W2">
+      <c r="Z2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="X2">
+      <c r="AA2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="Y2">
+      <c r="AB2">
         <v>2025</v>
       </c>
-      <c r="Z2">
+      <c r="AC2">
         <v>2026</v>
       </c>
-      <c r="AA2">
+      <c r="AD2">
         <v>2027</v>
       </c>
-      <c r="AB2">
+      <c r="AE2">
         <v>2028</v>
       </c>
-      <c r="AC2">
+      <c r="AF2">
         <v>2029</v>
       </c>
-      <c r="AD2">
+      <c r="AG2">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:104" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -1005,7 +1048,63 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="6" spans="1:104" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:107" x14ac:dyDescent="0.2">
+      <c r="Z4" s="25"/>
+    </row>
+    <row r="5" spans="1:107" x14ac:dyDescent="0.2">
+      <c r="V5" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="22">
+        <f>(W6-V6)/V6</f>
+        <v>0.66344892221180896</v>
+      </c>
+      <c r="X5" s="22">
+        <f>(X6-W6)/W6</f>
+        <v>0.7047919849668417</v>
+      </c>
+      <c r="Y5" s="22">
+        <f>(Y6-X6)/X6</f>
+        <v>0.62823294296956378</v>
+      </c>
+      <c r="Z5" s="24">
+        <f>(Z6-Y6)/Y6</f>
+        <v>0.25783535311324701</v>
+      </c>
+      <c r="AA5" s="24">
+        <f>(AA6-Z6)/Z6</f>
+        <v>0.26000000000000006</v>
+      </c>
+      <c r="AB5" s="24">
+        <f>(AB6-AA6)/AA6</f>
+        <v>0.26</v>
+      </c>
+      <c r="AC5" s="24">
+        <f>(AC6-AB6)/AB6</f>
+        <v>0.26000000000000012</v>
+      </c>
+      <c r="AD5" s="24">
+        <f>(AD6-AC6)/AC6</f>
+        <v>0.26</v>
+      </c>
+      <c r="AE5" s="24">
+        <f>(AE6-AD6)/AD6</f>
+        <v>0.26000000000000006</v>
+      </c>
+      <c r="AF5" s="24">
+        <f>(AF6-AE6)/AE6</f>
+        <v>0.25999999999999995</v>
+      </c>
+      <c r="AG5" s="24">
+        <f>(AG6-AF6)/AF6</f>
+        <v>0.25999999999999995</v>
+      </c>
+      <c r="AH5" s="24">
+        <f>(AH6-AG6)/AG6</f>
+        <v>1.0000000000000038E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1047,349 +1146,354 @@
       <c r="P6" s="3">
         <v>509.64</v>
       </c>
-      <c r="S6" s="3">
+      <c r="Q6" s="3">
+        <v>547.53599999999994</v>
+      </c>
+      <c r="R6" s="3">
+        <v>568</v>
+      </c>
+      <c r="V6" s="3">
         <v>362.78</v>
       </c>
-      <c r="T6" s="3">
+      <c r="W6" s="3">
         <v>603.46600000000001</v>
       </c>
-      <c r="U6" s="3">
+      <c r="X6" s="3">
         <v>1028.7840000000001</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Y6" s="3">
         <f>SUM($K$6:$N$6)</f>
         <v>1675.1</v>
       </c>
-      <c r="W6" s="3">
-        <f t="shared" ref="W6:AD6" si="1">V6*(1+$S$23)</f>
-        <v>2177.63</v>
-      </c>
-      <c r="X6" s="3">
-        <f t="shared" si="1"/>
-        <v>2830.9190000000003</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="1"/>
-        <v>3680.1947000000005</v>
-      </c>
       <c r="Z6" s="3">
-        <f t="shared" si="1"/>
-        <v>4784.2531100000006</v>
+        <v>2107</v>
       </c>
       <c r="AA6" s="3">
-        <f t="shared" si="1"/>
-        <v>6219.5290430000014</v>
+        <f t="shared" ref="Z6:AG7" si="1">Z6*(1+$V$23)</f>
+        <v>2654.82</v>
       </c>
       <c r="AB6" s="3">
         <f t="shared" si="1"/>
-        <v>8085.387755900002</v>
+        <v>3345.0732000000003</v>
       </c>
       <c r="AC6" s="3">
         <f t="shared" si="1"/>
-        <v>10511.004082670002</v>
+        <v>4214.7922320000007</v>
       </c>
       <c r="AD6" s="3">
         <f t="shared" si="1"/>
-        <v>13664.305307471004</v>
+        <v>5310.638212320001</v>
       </c>
       <c r="AE6" s="3">
-        <f>AD6*(1+S24)</f>
-        <v>13800.948360545714</v>
+        <f t="shared" si="1"/>
+        <v>6691.4041475232016</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" ref="AF6:CQ6" si="2">AE6*(1+T24)</f>
-        <v>13800.948360545714</v>
+        <f t="shared" si="1"/>
+        <v>8431.1692258792336</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <f t="shared" si="1"/>
+        <v>10623.273224607834</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <f>AG6*(1+$V$24)</f>
+        <v>10729.505956853913</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <f t="shared" ref="AI6:CT6" si="2">AH6*(1+$V$24)</f>
+        <v>10836.801016422452</v>
       </c>
       <c r="AJ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>10945.169026586676</v>
       </c>
       <c r="AK6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11054.620716852543</v>
       </c>
       <c r="AL6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11165.166924021069</v>
       </c>
       <c r="AM6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11276.81859326128</v>
       </c>
       <c r="AN6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11389.586779193893</v>
       </c>
       <c r="AO6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11503.482646985831</v>
       </c>
       <c r="AP6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11618.517473455689</v>
       </c>
       <c r="AQ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11734.702648190247</v>
       </c>
       <c r="AR6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11852.049674672149</v>
       </c>
       <c r="AS6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>11970.570171418871</v>
       </c>
       <c r="AT6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12090.27587313306</v>
       </c>
       <c r="AU6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12211.17863186439</v>
       </c>
       <c r="AV6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12333.290418183034</v>
       </c>
       <c r="AW6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12456.623322364865</v>
       </c>
       <c r="AX6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12581.189555588513</v>
       </c>
       <c r="AY6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12707.001451144399</v>
       </c>
       <c r="AZ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12834.071465655843</v>
       </c>
       <c r="BA6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>12962.412180312402</v>
       </c>
       <c r="BB6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13092.036302115526</v>
       </c>
       <c r="BC6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13222.956665136682</v>
       </c>
       <c r="BD6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13355.18623178805</v>
       </c>
       <c r="BE6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13488.738094105931</v>
       </c>
       <c r="BF6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13623.625475046991</v>
       </c>
       <c r="BG6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13759.861729797462</v>
       </c>
       <c r="BH6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>13897.460347095437</v>
       </c>
       <c r="BI6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14036.434950566392</v>
       </c>
       <c r="BJ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14176.799300072056</v>
       </c>
       <c r="BK6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14318.567293072776</v>
       </c>
       <c r="BL6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14461.752966003503</v>
       </c>
       <c r="BM6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14606.370495663539</v>
       </c>
       <c r="BN6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14752.434200620175</v>
       </c>
       <c r="BO6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>14899.958542626377</v>
       </c>
       <c r="BP6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15048.95812805264</v>
       </c>
       <c r="BQ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15199.447709333166</v>
       </c>
       <c r="BR6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15351.442186426499</v>
       </c>
       <c r="BS6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15504.956608290764</v>
       </c>
       <c r="BT6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15660.006174373671</v>
       </c>
       <c r="BU6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15816.606236117408</v>
       </c>
       <c r="BV6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>15974.772298478581</v>
       </c>
       <c r="BW6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16134.520021463368</v>
       </c>
       <c r="BX6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16295.865221678001</v>
       </c>
       <c r="BY6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16458.82387389478</v>
       </c>
       <c r="BZ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16623.412112633727</v>
       </c>
       <c r="CA6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16789.646233760064</v>
       </c>
       <c r="CB6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>16957.542696097666</v>
       </c>
       <c r="CC6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>17127.118123058641</v>
       </c>
       <c r="CD6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>17298.389304289227</v>
       </c>
       <c r="CE6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>17471.373197332119</v>
       </c>
       <c r="CF6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>17646.086929305442</v>
       </c>
       <c r="CG6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>17822.547798598498</v>
       </c>
       <c r="CH6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18000.773276584485</v>
       </c>
       <c r="CI6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18180.781009350329</v>
       </c>
       <c r="CJ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18362.58881944383</v>
       </c>
       <c r="CK6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18546.214707638268</v>
       </c>
       <c r="CL6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18731.676854714649</v>
       </c>
       <c r="CM6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>18918.993623261795</v>
       </c>
       <c r="CN6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>19108.183559494413</v>
       </c>
       <c r="CO6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>19299.265395089358</v>
       </c>
       <c r="CP6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>19492.258049040251</v>
       </c>
       <c r="CQ6" s="3">
         <f t="shared" si="2"/>
-        <v>13800.948360545714</v>
+        <v>19687.180629530652</v>
       </c>
       <c r="CR6" s="3">
-        <f t="shared" ref="CR6:CZ6" si="3">CQ6*(1+CF24)</f>
-        <v>13800.948360545714</v>
+        <f t="shared" si="2"/>
+        <v>19884.052435825961</v>
       </c>
       <c r="CS6" s="3">
-        <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <f t="shared" si="2"/>
+        <v>20082.892960184221</v>
       </c>
       <c r="CT6" s="3">
-        <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <f t="shared" si="2"/>
+        <v>20283.721889786062</v>
       </c>
       <c r="CU6" s="3">
-        <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <f t="shared" ref="CU6:DC6" si="3">CT6*(1+$V$24)</f>
+        <v>20486.559108683923</v>
       </c>
       <c r="CV6" s="3">
         <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <v>20691.424699770763</v>
       </c>
       <c r="CW6" s="3">
         <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <v>20898.338946768472</v>
       </c>
       <c r="CX6" s="3">
         <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <v>21107.322336236157</v>
       </c>
       <c r="CY6" s="3">
         <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
+        <v>21318.395559598517</v>
       </c>
       <c r="CZ6" s="3">
         <f t="shared" si="3"/>
-        <v>13800.948360545714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>21531.579515194502</v>
+      </c>
+      <c r="DA6" s="3">
+        <f t="shared" si="3"/>
+        <v>21746.895310346448</v>
+      </c>
+      <c r="DB6" s="3">
+        <f t="shared" si="3"/>
+        <v>21964.364263449912</v>
+      </c>
+      <c r="DC6" s="3">
+        <f t="shared" si="3"/>
+        <v>22184.007906084411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1431,80 +1535,447 @@
       <c r="P7" s="5">
         <v>101.846</v>
       </c>
-      <c r="S7" s="3">
+      <c r="Q7" s="5">
+        <v>103.319</v>
+      </c>
+      <c r="V7" s="3">
         <v>362.78</v>
       </c>
-      <c r="T7" s="3">
+      <c r="W7" s="3">
         <v>603.46600000000001</v>
       </c>
-      <c r="U7" s="3">
+      <c r="X7" s="3">
         <v>1028.7840000000001</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Y7" s="3">
         <f>SUM($K$6:$N$6)</f>
         <v>1675.1</v>
       </c>
-      <c r="W7" s="5">
-        <f>SUM(O6:R6)</f>
-        <v>991.35400000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Z7" s="5">
+        <f>SUM(O6:U6)</f>
+        <v>2106.89</v>
+      </c>
+      <c r="AA7" s="3">
+        <f>Z7*(1+$X$23)</f>
+        <v>2738.9569999999999</v>
+      </c>
+      <c r="AB7" s="3">
+        <f>AA7*(1+$X$23)</f>
+        <v>3560.6441</v>
+      </c>
+      <c r="AC7" s="3">
+        <f>AB7*(1+$X$23)</f>
+        <v>4628.8373300000003</v>
+      </c>
+      <c r="AD7" s="3">
+        <f>AC7*(1+$X$23)</f>
+        <v>6017.4885290000002</v>
+      </c>
+      <c r="AE7" s="3">
+        <f>AD7*(1+$X$23)</f>
+        <v>7822.7350877000008</v>
+      </c>
+      <c r="AF7" s="3">
+        <f>AE7*(1+$X$23)</f>
+        <v>10169.555614010002</v>
+      </c>
+      <c r="AG7" s="3">
+        <f>AF7*(1+$X$23)</f>
+        <v>13220.422298213003</v>
+      </c>
+      <c r="AH7" s="3">
+        <f>AG7*(1+$V$24)</f>
+        <v>13352.626521195134</v>
+      </c>
+      <c r="AI7" s="3">
+        <f>AH7*(1+$V$24)</f>
+        <v>13486.152786407085</v>
+      </c>
+      <c r="AJ7" s="3">
+        <f t="shared" ref="AJ7:CU7" si="4">AI7*(1+$V$24)</f>
+        <v>13621.014314271157</v>
+      </c>
+      <c r="AK7" s="3">
+        <f t="shared" si="4"/>
+        <v>13757.224457413868</v>
+      </c>
+      <c r="AL7" s="3">
+        <f t="shared" si="4"/>
+        <v>13894.796701988007</v>
+      </c>
+      <c r="AM7" s="3">
+        <f t="shared" si="4"/>
+        <v>14033.744669007887</v>
+      </c>
+      <c r="AN7" s="3">
+        <f t="shared" si="4"/>
+        <v>14174.082115697965</v>
+      </c>
+      <c r="AO7" s="3">
+        <f t="shared" si="4"/>
+        <v>14315.822936854946</v>
+      </c>
+      <c r="AP7" s="3">
+        <f t="shared" si="4"/>
+        <v>14458.981166223495</v>
+      </c>
+      <c r="AQ7" s="3">
+        <f t="shared" si="4"/>
+        <v>14603.570977885731</v>
+      </c>
+      <c r="AR7" s="3">
+        <f t="shared" si="4"/>
+        <v>14749.606687664589</v>
+      </c>
+      <c r="AS7" s="3">
+        <f t="shared" si="4"/>
+        <v>14897.102754541234</v>
+      </c>
+      <c r="AT7" s="3">
+        <f t="shared" si="4"/>
+        <v>15046.073782086647</v>
+      </c>
+      <c r="AU7" s="3">
+        <f t="shared" si="4"/>
+        <v>15196.534519907515</v>
+      </c>
+      <c r="AV7" s="3">
+        <f t="shared" si="4"/>
+        <v>15348.499865106591</v>
+      </c>
+      <c r="AW7" s="3">
+        <f t="shared" si="4"/>
+        <v>15501.984863757656</v>
+      </c>
+      <c r="AX7" s="3">
+        <f t="shared" si="4"/>
+        <v>15657.004712395234</v>
+      </c>
+      <c r="AY7" s="3">
+        <f t="shared" si="4"/>
+        <v>15813.574759519186</v>
+      </c>
+      <c r="AZ7" s="3">
+        <f t="shared" si="4"/>
+        <v>15971.710507114378</v>
+      </c>
+      <c r="BA7" s="3">
+        <f t="shared" si="4"/>
+        <v>16131.427612185522</v>
+      </c>
+      <c r="BB7" s="3">
+        <f t="shared" si="4"/>
+        <v>16292.741888307377</v>
+      </c>
+      <c r="BC7" s="3">
+        <f t="shared" si="4"/>
+        <v>16455.669307190452</v>
+      </c>
+      <c r="BD7" s="3">
+        <f t="shared" si="4"/>
+        <v>16620.226000262355</v>
+      </c>
+      <c r="BE7" s="3">
+        <f t="shared" si="4"/>
+        <v>16786.42826026498</v>
+      </c>
+      <c r="BF7" s="3">
+        <f t="shared" si="4"/>
+        <v>16954.292542867632</v>
+      </c>
+      <c r="BG7" s="3">
+        <f t="shared" si="4"/>
+        <v>17123.835468296307</v>
+      </c>
+      <c r="BH7" s="3">
+        <f t="shared" si="4"/>
+        <v>17295.07382297927</v>
+      </c>
+      <c r="BI7" s="3">
+        <f t="shared" si="4"/>
+        <v>17468.024561209062</v>
+      </c>
+      <c r="BJ7" s="3">
+        <f t="shared" si="4"/>
+        <v>17642.704806821152</v>
+      </c>
+      <c r="BK7" s="3">
+        <f t="shared" si="4"/>
+        <v>17819.131854889365</v>
+      </c>
+      <c r="BL7" s="3">
+        <f t="shared" si="4"/>
+        <v>17997.323173438257</v>
+      </c>
+      <c r="BM7" s="3">
+        <f t="shared" si="4"/>
+        <v>18177.296405172641</v>
+      </c>
+      <c r="BN7" s="3">
+        <f t="shared" si="4"/>
+        <v>18359.069369224369</v>
+      </c>
+      <c r="BO7" s="3">
+        <f t="shared" si="4"/>
+        <v>18542.660062916613</v>
+      </c>
+      <c r="BP7" s="3">
+        <f t="shared" si="4"/>
+        <v>18728.086663545779</v>
+      </c>
+      <c r="BQ7" s="3">
+        <f t="shared" si="4"/>
+        <v>18915.367530181236</v>
+      </c>
+      <c r="BR7" s="3">
+        <f t="shared" si="4"/>
+        <v>19104.521205483048</v>
+      </c>
+      <c r="BS7" s="3">
+        <f t="shared" si="4"/>
+        <v>19295.566417537877</v>
+      </c>
+      <c r="BT7" s="3">
+        <f t="shared" si="4"/>
+        <v>19488.522081713258</v>
+      </c>
+      <c r="BU7" s="3">
+        <f t="shared" si="4"/>
+        <v>19683.407302530391</v>
+      </c>
+      <c r="BV7" s="3">
+        <f t="shared" si="4"/>
+        <v>19880.241375555695</v>
+      </c>
+      <c r="BW7" s="3">
+        <f t="shared" si="4"/>
+        <v>20079.043789311254</v>
+      </c>
+      <c r="BX7" s="3">
+        <f t="shared" si="4"/>
+        <v>20279.834227204366</v>
+      </c>
+      <c r="BY7" s="3">
+        <f t="shared" si="4"/>
+        <v>20482.632569476409</v>
+      </c>
+      <c r="BZ7" s="3">
+        <f t="shared" si="4"/>
+        <v>20687.458895171174</v>
+      </c>
+      <c r="CA7" s="3">
+        <f t="shared" si="4"/>
+        <v>20894.333484122886</v>
+      </c>
+      <c r="CB7" s="3">
+        <f t="shared" si="4"/>
+        <v>21103.276818964114</v>
+      </c>
+      <c r="CC7" s="3">
+        <f t="shared" si="4"/>
+        <v>21314.309587153755</v>
+      </c>
+      <c r="CD7" s="3">
+        <f t="shared" si="4"/>
+        <v>21527.452683025294</v>
+      </c>
+      <c r="CE7" s="3">
+        <f t="shared" si="4"/>
+        <v>21742.727209855548</v>
+      </c>
+      <c r="CF7" s="3">
+        <f t="shared" si="4"/>
+        <v>21960.154481954105</v>
+      </c>
+      <c r="CG7" s="3">
+        <f t="shared" si="4"/>
+        <v>22179.756026773648</v>
+      </c>
+      <c r="CH7" s="3">
+        <f t="shared" si="4"/>
+        <v>22401.553587041384</v>
+      </c>
+      <c r="CI7" s="3">
+        <f t="shared" si="4"/>
+        <v>22625.569122911798</v>
+      </c>
+      <c r="CJ7" s="3">
+        <f t="shared" si="4"/>
+        <v>22851.824814140917</v>
+      </c>
+      <c r="CK7" s="3">
+        <f t="shared" si="4"/>
+        <v>23080.343062282325</v>
+      </c>
+      <c r="CL7" s="3">
+        <f t="shared" si="4"/>
+        <v>23311.146492905147</v>
+      </c>
+      <c r="CM7" s="3">
+        <f t="shared" si="4"/>
+        <v>23544.257957834197</v>
+      </c>
+      <c r="CN7" s="3">
+        <f t="shared" si="4"/>
+        <v>23779.70053741254</v>
+      </c>
+      <c r="CO7" s="3">
+        <f t="shared" si="4"/>
+        <v>24017.497542786667</v>
+      </c>
+      <c r="CP7" s="3">
+        <f t="shared" si="4"/>
+        <v>24257.672518214535</v>
+      </c>
+      <c r="CQ7" s="3">
+        <f t="shared" si="4"/>
+        <v>24500.24924339668</v>
+      </c>
+      <c r="CR7" s="3">
+        <f t="shared" si="4"/>
+        <v>24745.251735830647</v>
+      </c>
+      <c r="CS7" s="3">
+        <f t="shared" si="4"/>
+        <v>24992.704253188953</v>
+      </c>
+      <c r="CT7" s="3">
+        <f t="shared" si="4"/>
+        <v>25242.631295720843</v>
+      </c>
+      <c r="CU7" s="3">
+        <f t="shared" si="4"/>
+        <v>25495.057608678053</v>
+      </c>
+      <c r="CV7" s="3">
+        <f t="shared" ref="CV7:DC7" si="5">CU7*(1+$V$24)</f>
+        <v>25750.008184764833</v>
+      </c>
+      <c r="CW7" s="3">
+        <f t="shared" si="5"/>
+        <v>26007.50826661248</v>
+      </c>
+      <c r="CX7" s="3">
+        <f t="shared" si="5"/>
+        <v>26267.583349278604</v>
+      </c>
+      <c r="CY7" s="3">
+        <f t="shared" si="5"/>
+        <v>26530.259182771391</v>
+      </c>
+      <c r="CZ7" s="3">
+        <f t="shared" si="5"/>
+        <v>26795.561774599104</v>
+      </c>
+      <c r="DA7" s="3">
+        <f t="shared" si="5"/>
+        <v>27063.517392345097</v>
+      </c>
+      <c r="DB7" s="3">
+        <f t="shared" si="5"/>
+        <v>27334.152566268549</v>
+      </c>
+      <c r="DC7" s="3">
+        <f t="shared" si="5"/>
+        <v>27607.494091931236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:P8" si="4">+E6-E7</f>
+        <f t="shared" ref="E8:Q8" si="6">+E6-E7</f>
         <v>120.691</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>136.67500000000001</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>151.88300000000001</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>176.45100000000002</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>207.15600000000001</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>259.04899999999998</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>288.56799999999998</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>324.21299999999997</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>342.93400000000003</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>372.642</v>
       </c>
       <c r="O8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>381.8</v>
       </c>
       <c r="P8" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>407.79399999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q8" s="6">
+        <f t="shared" si="6"/>
+        <v>444.21699999999993</v>
+      </c>
+      <c r="Z8" s="24">
+        <f>(Z7-Y7)/Y7</f>
+        <v>0.25776968539191691</v>
+      </c>
+      <c r="AA8" s="22">
+        <f>(AA7-Z7)/Z7</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AB8" s="22">
+        <f>(AB7-AA7)/AA7</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AC8" s="22">
+        <f>(AC7-AB7)/AB7</f>
+        <v>0.3000000000000001</v>
+      </c>
+      <c r="AD8" s="22">
+        <f>(AD7-AC7)/AC7</f>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="AE8" s="22">
+        <f>(AE7-AD7)/AD7</f>
+        <v>0.3000000000000001</v>
+      </c>
+      <c r="AF8" s="22">
+        <f>(AF7-AE7)/AE7</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AG8" s="22">
+        <f>(AG7-AF7)/AF7</f>
+        <v>0.3000000000000001</v>
+      </c>
+      <c r="AH8" s="22">
+        <f>(AH7-AG7)/AG7</f>
+        <v>1.0000000000000064E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -1546,8 +2017,11 @@
       <c r="P9" s="5">
         <v>239.494</v>
       </c>
-    </row>
-    <row r="10" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q9" s="5">
+        <v>240.22499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
@@ -1589,8 +2063,11 @@
       <c r="P10" s="5">
         <v>147.45500000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q10" s="5">
+        <v>156.87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1632,94 +2109,101 @@
       <c r="P11" s="5">
         <v>42.670999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q11" s="5">
+        <v>51.351999999999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f t="shared" ref="E12:P12" si="5">SUM(E9:E11)</f>
+        <f t="shared" ref="E12:Q12" si="7">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>145.613</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>164.71299999999999</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>186.33699999999999</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>212.05100000000002</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>250.59399999999999</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>278.154</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>327.35199999999998</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>374.27599999999995</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>407.27</v>
       </c>
       <c r="O12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>416.77</v>
       </c>
       <c r="P12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>429.62</v>
       </c>
-    </row>
-    <row r="13" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q12" s="6">
+        <f t="shared" si="7"/>
+        <v>448.447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f t="shared" ref="E13:P13" si="6">E8-E12</f>
+        <f t="shared" ref="E13:Q13" si="8">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-8.9379999999999882</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-12.829999999999984</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-9.8859999999999673</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-4.8950000000000102</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.4549999999999841</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10.413999999999987</v>
       </c>
       <c r="L13" s="6">
@@ -1727,23 +2211,27 @@
         <v>-3.13900000000001</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-31.341999999999928</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-34.627999999999986</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-34.96999999999997</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-21.826000000000022</v>
       </c>
-    </row>
-    <row r="14" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q13" s="6">
+        <f t="shared" si="8"/>
+        <v>-4.230000000000075</v>
+      </c>
+    </row>
+    <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -1794,63 +2282,71 @@
         <f>22.624-1.526</f>
         <v>21.097999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q14" s="5">
+        <f>-1.303+29.883</f>
+        <v>28.58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f t="shared" ref="E15:P15" si="7">+E13+E14</f>
+        <f t="shared" ref="E15:Q15" si="9">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-15.166999999999987</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-12.528999999999986</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-9.6579999999999675</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-4.7670000000000101</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8.531999999999984</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10.853999999999989</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-1.1000000000010779E-2</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-22.21599999999993</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-25.009999999999987</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-20.423999999999971</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>-0.72800000000002285</v>
       </c>
-    </row>
-    <row r="16" spans="1:104" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q15" s="6">
+        <f t="shared" si="9"/>
+        <v>24.349999999999923</v>
+      </c>
+    </row>
+    <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1892,118 +2388,129 @@
       <c r="P16" s="5">
         <v>3.0609999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q16" s="5">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:P17" si="8">+E15-E16</f>
+        <f t="shared" ref="E17:Q17" si="10">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-16.159999999999986</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-11.989999999999986</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-6.6979999999999675</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-4.0500000000000105</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7.1689999999999845</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9.7379999999999889</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-4.8790000000000111</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-25.141999999999932</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-28.189999999999987</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-24.08599999999997</v>
       </c>
       <c r="P17" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>-3.7890000000000228</v>
       </c>
-    </row>
-    <row r="18" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q17" s="6">
+        <f t="shared" si="10"/>
+        <v>22.679999999999922</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:P18" si="9">+E17/E19</f>
+        <f t="shared" ref="E18:Q18" si="11">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-5.3147929500060795E-2</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-3.9178653352241861E-2</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-2.1745411809011676E-2</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-1.3054114947122809E-2</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.0727021455604115E-2</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2.8171540321927365E-2</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-1.5498975523753589E-2</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-7.9565809044589805E-2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-8.8829928028536453E-2</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-7.5437068960117162E-2</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-1.1759229086169245E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q18" s="7">
+        <f t="shared" si="11"/>
+        <v>6.9665219915406279E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -2045,8 +2552,11 @@
       <c r="P19" s="5">
         <v>322.21499999999997</v>
       </c>
-    </row>
-    <row r="21" spans="2:19" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q19" s="5">
+        <v>325.55700000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
@@ -2057,15 +2567,15 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:K21" si="10">+I6/E6-1</f>
+        <f t="shared" ref="I21:K21" si="12">+I6/E6-1</f>
         <v>0.74875060610958455</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.83741431074009598</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82841515192723181</v>
       </c>
       <c r="L21" s="10">
@@ -2088,37 +2598,45 @@
         <f>+P6/L6-1</f>
         <v>0.25484441249033574</v>
       </c>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q21" s="10">
+        <f>+Q6/M6-1</f>
+        <v>0.25428318134024219</v>
+      </c>
+      <c r="R21" s="10">
+        <f>+R6/N6-1</f>
+        <v>0.21005796774172936</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="11">+E8/E6</f>
+        <f t="shared" ref="E22:H22" si="13">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.76986554460911061</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7649648197674126</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.75552025485015994</v>
       </c>
       <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="12">+I8/I6</f>
+        <f t="shared" ref="I22:K22" si="14">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.79414649997854059</v>
       </c>
       <c r="K22" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.79488747486433631</v>
       </c>
       <c r="L22" s="12">
@@ -2126,31 +2644,50 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:P22" si="13">+M8/M6</f>
+        <f t="shared" ref="M22:Q22" si="15">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.79387045988593929</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.79258647247121738</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.8001608978887057</v>
       </c>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="R23" s="15" t="s">
+      <c r="Q22" s="12">
+        <f t="shared" si="15"/>
+        <v>0.81130190526285029</v>
+      </c>
+      <c r="U22" t="s">
+        <v>71</v>
+      </c>
+      <c r="W22" t="s">
+        <v>72</v>
+      </c>
+      <c r="X22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="U23" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="S23" s="20">
+      <c r="V23" s="23">
+        <v>0.26</v>
+      </c>
+      <c r="W23" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="X23" s="23">
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
@@ -2172,14 +2709,14 @@
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
-      <c r="R24" s="17" t="s">
+      <c r="U24" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="S24" s="16">
+      <c r="V24" s="16">
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -2199,14 +2736,14 @@
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
-      <c r="R25" s="17" t="s">
+      <c r="U25" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="S25" s="16">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V25" s="16">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2228,15 +2765,22 @@
       </c>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
-      <c r="R26" s="17" t="s">
+      <c r="U26" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="S26" s="18">
-        <f>NPV(S25,S6:CZ6)</f>
-        <v>57693.064395439622</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V26" s="18">
+        <f>NPV(V25,V6:DC6)</f>
+        <v>58324.781680299697</v>
+      </c>
+      <c r="W26" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="X26" s="26">
+        <f>NPV($V$25,V7:DC7)</f>
+        <v>70118.732659662914</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -2256,15 +2800,22 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
-      <c r="R27" s="17" t="s">
+      <c r="U27" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="S27" s="21">
-        <f>Main!O3</f>
-        <v>296.27</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V27" s="21">
+        <f>Main!$O$3</f>
+        <v>325.55700000000002</v>
+      </c>
+      <c r="W27" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="X27" s="21">
+        <f>Main!$O$3</f>
+        <v>325.55700000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -2284,15 +2835,22 @@
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
-      <c r="R28" s="17" t="s">
+      <c r="U28" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="S28" s="19">
-        <f>S26/S27</f>
-        <v>194.73137474411729</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V28" s="19">
+        <f>V26/V27</f>
+        <v>179.1538246153506</v>
+      </c>
+      <c r="W28" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="X28" s="19">
+        <f>X26/X27</f>
+        <v>215.38081706018579</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2312,15 +2870,22 @@
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
-      <c r="R29" s="17" t="s">
+      <c r="U29" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="S29" s="20">
-        <f>(S28-Main!O2)/Main!O2</f>
-        <v>0.77237985568505763</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V29" s="20">
+        <f>(V28-Main!$O$2)/Main!$O$2</f>
+        <v>0.32795066796642652</v>
+      </c>
+      <c r="W29" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="X29" s="20">
+        <f>(X28-Main!$O$2)/Main!$O$2</f>
+        <v>0.59647777822389592</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -2342,15 +2907,22 @@
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
-      <c r="R30" s="17" t="s">
+      <c r="U30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="S30" s="18">
-        <f>S27*S28</f>
-        <v>57693.064395439629</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="V30" s="18">
+        <f>V27*V28</f>
+        <v>58324.781680299697</v>
+      </c>
+      <c r="W30" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="X30" s="18">
+        <f>X27*X28</f>
+        <v>70118.732659662914</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -2371,7 +2943,7 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="2:19" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
         <v>32</v>
       </c>

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88AB9AE-FF4F-40BD-8881-5052BBAE5BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A787C9-DEDB-49DF-98D5-D831FFAE8E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14235" yWindow="90" windowWidth="37440" windowHeight="20805" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>Price</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>if growth accelerates up</t>
+  </si>
+  <si>
+    <t>Q124</t>
   </si>
 </sst>
 </file>
@@ -834,35 +837,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3BD0B1-E685-4627-8A01-75A3D2BDF860}">
   <dimension ref="N2:P7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="14:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>134.91</v>
-      </c>
-    </row>
-    <row r="3" spans="14:16" x14ac:dyDescent="0.2">
+        <v>129.74</v>
+      </c>
+    </row>
+    <row r="3" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N3" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>325.55700000000002</v>
+        <v>328</v>
       </c>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="14:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N4" t="s">
         <v>2</v>
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>43920.894870000004</v>
-      </c>
-    </row>
-    <row r="5" spans="14:16" x14ac:dyDescent="0.2">
+        <v>42554.720000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N5" t="s">
         <v>3</v>
       </c>
@@ -871,7 +874,7 @@
       </c>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="14:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N6" t="s">
         <v>4</v>
       </c>
@@ -880,13 +883,13 @@
       </c>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="14:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="14:16" x14ac:dyDescent="0.25">
       <c r="N7" t="s">
         <v>5</v>
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>43577.720870000005</v>
+        <v>42211.546000000002</v>
       </c>
     </row>
   </sheetData>
@@ -897,19 +900,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
   <dimension ref="A1:DC54"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="13" width="9.140625" style="2"/>
-    <col min="14" max="14" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="13" width="9.109375" style="2"/>
+    <col min="14" max="14" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:107" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -934,11 +938,14 @@
       <c r="R1" s="13">
         <v>45291</v>
       </c>
+      <c r="S1" s="14">
+        <v>45382</v>
+      </c>
       <c r="V1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:107" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -987,7 +994,9 @@
       <c r="R2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2">
@@ -1031,7 +1040,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:107" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -1048,63 +1057,63 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="4" spans="1:107" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
       <c r="Z4" s="25"/>
     </row>
-    <row r="5" spans="1:107" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
       <c r="V5" t="s">
         <v>69</v>
       </c>
       <c r="W5" s="22">
-        <f>(W6-V6)/V6</f>
+        <f t="shared" ref="W5:AH5" si="1">(W6-V6)/V6</f>
         <v>0.66344892221180896</v>
       </c>
       <c r="X5" s="22">
-        <f>(X6-W6)/W6</f>
+        <f t="shared" si="1"/>
         <v>0.7047919849668417</v>
       </c>
       <c r="Y5" s="22">
-        <f>(Y6-X6)/X6</f>
+        <f t="shared" si="1"/>
         <v>0.62823294296956378</v>
       </c>
       <c r="Z5" s="24">
-        <f>(Z6-Y6)/Y6</f>
+        <f t="shared" si="1"/>
         <v>0.25783535311324701</v>
       </c>
       <c r="AA5" s="24">
         <f>(AA6-Z6)/Z6</f>
-        <v>0.26000000000000006</v>
+        <v>0.23999999999999994</v>
       </c>
       <c r="AB5" s="24">
-        <f>(AB6-AA6)/AA6</f>
-        <v>0.26</v>
+        <f t="shared" si="1"/>
+        <v>0.24000000000000005</v>
       </c>
       <c r="AC5" s="24">
-        <f>(AC6-AB6)/AB6</f>
-        <v>0.26000000000000012</v>
+        <f t="shared" si="1"/>
+        <v>0.23999999999999996</v>
       </c>
       <c r="AD5" s="24">
-        <f>(AD6-AC6)/AC6</f>
-        <v>0.26</v>
+        <f t="shared" si="1"/>
+        <v>0.23999999999999994</v>
       </c>
       <c r="AE5" s="24">
-        <f>(AE6-AD6)/AD6</f>
-        <v>0.26000000000000006</v>
+        <f t="shared" si="1"/>
+        <v>0.24000000000000002</v>
       </c>
       <c r="AF5" s="24">
-        <f>(AF6-AE6)/AE6</f>
-        <v>0.25999999999999995</v>
+        <f t="shared" si="1"/>
+        <v>0.23999999999999994</v>
       </c>
       <c r="AG5" s="24">
-        <f>(AG6-AF6)/AF6</f>
-        <v>0.25999999999999995</v>
+        <f t="shared" si="1"/>
+        <v>0.23999999999999994</v>
       </c>
       <c r="AH5" s="24">
-        <f>(AH6-AG6)/AG6</f>
-        <v>1.0000000000000038E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000097E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1150,7 +1159,11 @@
         <v>547.53599999999994</v>
       </c>
       <c r="R6" s="3">
-        <v>568</v>
+        <v>589.649</v>
+      </c>
+      <c r="S6" s="3">
+        <f>(587+591)/2</f>
+        <v>589</v>
       </c>
       <c r="V6" s="3">
         <v>362.78</v>
@@ -1169,331 +1182,331 @@
         <v>2107</v>
       </c>
       <c r="AA6" s="3">
-        <f t="shared" ref="Z6:AG7" si="1">Z6*(1+$V$23)</f>
-        <v>2654.82</v>
+        <f t="shared" ref="AA6:AG6" si="2">Z6*(1+$V$23)</f>
+        <v>2612.6799999999998</v>
       </c>
       <c r="AB6" s="3">
-        <f t="shared" si="1"/>
-        <v>3345.0732000000003</v>
+        <f t="shared" si="2"/>
+        <v>3239.7231999999999</v>
       </c>
       <c r="AC6" s="3">
-        <f t="shared" si="1"/>
-        <v>4214.7922320000007</v>
+        <f t="shared" si="2"/>
+        <v>4017.2567679999997</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" si="1"/>
-        <v>5310.638212320001</v>
+        <f t="shared" si="2"/>
+        <v>4981.3983923199994</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="1"/>
-        <v>6691.4041475232016</v>
+        <f t="shared" si="2"/>
+        <v>6176.9340064767994</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="1"/>
-        <v>8431.1692258792336</v>
+        <f t="shared" si="2"/>
+        <v>7659.3981680312309</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="1"/>
-        <v>10623.273224607834</v>
+        <f t="shared" si="2"/>
+        <v>9497.6537283587259</v>
       </c>
       <c r="AH6" s="3">
         <f>AG6*(1+$V$24)</f>
-        <v>10729.505956853913</v>
+        <v>9592.630265642314</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" ref="AI6:CT6" si="2">AH6*(1+$V$24)</f>
-        <v>10836.801016422452</v>
+        <f t="shared" ref="AI6:CT6" si="3">AH6*(1+$V$24)</f>
+        <v>9688.5565682987381</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="2"/>
-        <v>10945.169026586676</v>
+        <f t="shared" si="3"/>
+        <v>9785.4421339817254</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="2"/>
-        <v>11054.620716852543</v>
+        <f t="shared" si="3"/>
+        <v>9883.2965553215436</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="2"/>
-        <v>11165.166924021069</v>
+        <f t="shared" si="3"/>
+        <v>9982.1295208747597</v>
       </c>
       <c r="AM6" s="3">
-        <f t="shared" si="2"/>
-        <v>11276.81859326128</v>
+        <f t="shared" si="3"/>
+        <v>10081.950816083507</v>
       </c>
       <c r="AN6" s="3">
-        <f t="shared" si="2"/>
-        <v>11389.586779193893</v>
+        <f t="shared" si="3"/>
+        <v>10182.770324244342</v>
       </c>
       <c r="AO6" s="3">
-        <f t="shared" si="2"/>
-        <v>11503.482646985831</v>
+        <f t="shared" si="3"/>
+        <v>10284.598027486785</v>
       </c>
       <c r="AP6" s="3">
-        <f t="shared" si="2"/>
-        <v>11618.517473455689</v>
+        <f t="shared" si="3"/>
+        <v>10387.444007761653</v>
       </c>
       <c r="AQ6" s="3">
-        <f t="shared" si="2"/>
-        <v>11734.702648190247</v>
+        <f t="shared" si="3"/>
+        <v>10491.318447839269</v>
       </c>
       <c r="AR6" s="3">
-        <f t="shared" si="2"/>
-        <v>11852.049674672149</v>
+        <f t="shared" si="3"/>
+        <v>10596.231632317662</v>
       </c>
       <c r="AS6" s="3">
-        <f t="shared" si="2"/>
-        <v>11970.570171418871</v>
+        <f t="shared" si="3"/>
+        <v>10702.193948640839</v>
       </c>
       <c r="AT6" s="3">
-        <f t="shared" si="2"/>
-        <v>12090.27587313306</v>
+        <f t="shared" si="3"/>
+        <v>10809.215888127248</v>
       </c>
       <c r="AU6" s="3">
-        <f t="shared" si="2"/>
-        <v>12211.17863186439</v>
+        <f t="shared" si="3"/>
+        <v>10917.308047008521</v>
       </c>
       <c r="AV6" s="3">
-        <f t="shared" si="2"/>
-        <v>12333.290418183034</v>
+        <f t="shared" si="3"/>
+        <v>11026.481127478606</v>
       </c>
       <c r="AW6" s="3">
-        <f t="shared" si="2"/>
-        <v>12456.623322364865</v>
+        <f t="shared" si="3"/>
+        <v>11136.745938753393</v>
       </c>
       <c r="AX6" s="3">
-        <f t="shared" si="2"/>
-        <v>12581.189555588513</v>
+        <f t="shared" si="3"/>
+        <v>11248.113398140928</v>
       </c>
       <c r="AY6" s="3">
-        <f t="shared" si="2"/>
-        <v>12707.001451144399</v>
+        <f t="shared" si="3"/>
+        <v>11360.594532122337</v>
       </c>
       <c r="AZ6" s="3">
-        <f t="shared" si="2"/>
-        <v>12834.071465655843</v>
+        <f t="shared" si="3"/>
+        <v>11474.200477443561</v>
       </c>
       <c r="BA6" s="3">
-        <f t="shared" si="2"/>
-        <v>12962.412180312402</v>
+        <f t="shared" si="3"/>
+        <v>11588.942482217997</v>
       </c>
       <c r="BB6" s="3">
-        <f t="shared" si="2"/>
-        <v>13092.036302115526</v>
+        <f t="shared" si="3"/>
+        <v>11704.831907040178</v>
       </c>
       <c r="BC6" s="3">
-        <f t="shared" si="2"/>
-        <v>13222.956665136682</v>
+        <f t="shared" si="3"/>
+        <v>11821.880226110579</v>
       </c>
       <c r="BD6" s="3">
-        <f t="shared" si="2"/>
-        <v>13355.18623178805</v>
+        <f t="shared" si="3"/>
+        <v>11940.099028371686</v>
       </c>
       <c r="BE6" s="3">
-        <f t="shared" si="2"/>
-        <v>13488.738094105931</v>
+        <f t="shared" si="3"/>
+        <v>12059.500018655403</v>
       </c>
       <c r="BF6" s="3">
-        <f t="shared" si="2"/>
-        <v>13623.625475046991</v>
+        <f t="shared" si="3"/>
+        <v>12180.095018841957</v>
       </c>
       <c r="BG6" s="3">
-        <f t="shared" si="2"/>
-        <v>13759.861729797462</v>
+        <f t="shared" si="3"/>
+        <v>12301.895969030376</v>
       </c>
       <c r="BH6" s="3">
-        <f t="shared" si="2"/>
-        <v>13897.460347095437</v>
+        <f t="shared" si="3"/>
+        <v>12424.91492872068</v>
       </c>
       <c r="BI6" s="3">
-        <f t="shared" si="2"/>
-        <v>14036.434950566392</v>
+        <f t="shared" si="3"/>
+        <v>12549.164078007887</v>
       </c>
       <c r="BJ6" s="3">
-        <f t="shared" si="2"/>
-        <v>14176.799300072056</v>
+        <f t="shared" si="3"/>
+        <v>12674.655718787966</v>
       </c>
       <c r="BK6" s="3">
-        <f t="shared" si="2"/>
-        <v>14318.567293072776</v>
+        <f t="shared" si="3"/>
+        <v>12801.402275975846</v>
       </c>
       <c r="BL6" s="3">
-        <f t="shared" si="2"/>
-        <v>14461.752966003503</v>
+        <f t="shared" si="3"/>
+        <v>12929.416298735605</v>
       </c>
       <c r="BM6" s="3">
-        <f t="shared" si="2"/>
-        <v>14606.370495663539</v>
+        <f t="shared" si="3"/>
+        <v>13058.710461722962</v>
       </c>
       <c r="BN6" s="3">
-        <f t="shared" si="2"/>
-        <v>14752.434200620175</v>
+        <f t="shared" si="3"/>
+        <v>13189.297566340192</v>
       </c>
       <c r="BO6" s="3">
-        <f t="shared" si="2"/>
-        <v>14899.958542626377</v>
+        <f t="shared" si="3"/>
+        <v>13321.190542003595</v>
       </c>
       <c r="BP6" s="3">
-        <f t="shared" si="2"/>
-        <v>15048.95812805264</v>
+        <f t="shared" si="3"/>
+        <v>13454.40244742363</v>
       </c>
       <c r="BQ6" s="3">
-        <f t="shared" si="2"/>
-        <v>15199.447709333166</v>
+        <f t="shared" si="3"/>
+        <v>13588.946471897867</v>
       </c>
       <c r="BR6" s="3">
-        <f t="shared" si="2"/>
-        <v>15351.442186426499</v>
+        <f t="shared" si="3"/>
+        <v>13724.835936616846</v>
       </c>
       <c r="BS6" s="3">
-        <f t="shared" si="2"/>
-        <v>15504.956608290764</v>
+        <f t="shared" si="3"/>
+        <v>13862.084295983015</v>
       </c>
       <c r="BT6" s="3">
-        <f t="shared" si="2"/>
-        <v>15660.006174373671</v>
+        <f t="shared" si="3"/>
+        <v>14000.705138942845</v>
       </c>
       <c r="BU6" s="3">
-        <f t="shared" si="2"/>
-        <v>15816.606236117408</v>
+        <f t="shared" si="3"/>
+        <v>14140.712190332273</v>
       </c>
       <c r="BV6" s="3">
-        <f t="shared" si="2"/>
-        <v>15974.772298478581</v>
+        <f t="shared" si="3"/>
+        <v>14282.119312235596</v>
       </c>
       <c r="BW6" s="3">
-        <f t="shared" si="2"/>
-        <v>16134.520021463368</v>
+        <f t="shared" si="3"/>
+        <v>14424.940505357952</v>
       </c>
       <c r="BX6" s="3">
-        <f t="shared" si="2"/>
-        <v>16295.865221678001</v>
+        <f t="shared" si="3"/>
+        <v>14569.189910411531</v>
       </c>
       <c r="BY6" s="3">
-        <f t="shared" si="2"/>
-        <v>16458.82387389478</v>
+        <f t="shared" si="3"/>
+        <v>14714.881809515646</v>
       </c>
       <c r="BZ6" s="3">
-        <f t="shared" si="2"/>
-        <v>16623.412112633727</v>
+        <f t="shared" si="3"/>
+        <v>14862.030627610802</v>
       </c>
       <c r="CA6" s="3">
-        <f t="shared" si="2"/>
-        <v>16789.646233760064</v>
+        <f t="shared" si="3"/>
+        <v>15010.650933886911</v>
       </c>
       <c r="CB6" s="3">
-        <f t="shared" si="2"/>
-        <v>16957.542696097666</v>
+        <f t="shared" si="3"/>
+        <v>15160.757443225781</v>
       </c>
       <c r="CC6" s="3">
-        <f t="shared" si="2"/>
-        <v>17127.118123058641</v>
+        <f t="shared" si="3"/>
+        <v>15312.36501765804</v>
       </c>
       <c r="CD6" s="3">
-        <f t="shared" si="2"/>
-        <v>17298.389304289227</v>
+        <f t="shared" si="3"/>
+        <v>15465.488667834619</v>
       </c>
       <c r="CE6" s="3">
-        <f t="shared" si="2"/>
-        <v>17471.373197332119</v>
+        <f t="shared" si="3"/>
+        <v>15620.143554512966</v>
       </c>
       <c r="CF6" s="3">
-        <f t="shared" si="2"/>
-        <v>17646.086929305442</v>
+        <f t="shared" si="3"/>
+        <v>15776.344990058096</v>
       </c>
       <c r="CG6" s="3">
-        <f t="shared" si="2"/>
-        <v>17822.547798598498</v>
+        <f t="shared" si="3"/>
+        <v>15934.108439958678</v>
       </c>
       <c r="CH6" s="3">
-        <f t="shared" si="2"/>
-        <v>18000.773276584485</v>
+        <f t="shared" si="3"/>
+        <v>16093.449524358264</v>
       </c>
       <c r="CI6" s="3">
-        <f t="shared" si="2"/>
-        <v>18180.781009350329</v>
+        <f t="shared" si="3"/>
+        <v>16254.384019601846</v>
       </c>
       <c r="CJ6" s="3">
-        <f t="shared" si="2"/>
-        <v>18362.58881944383</v>
+        <f t="shared" si="3"/>
+        <v>16416.927859797866</v>
       </c>
       <c r="CK6" s="3">
-        <f t="shared" si="2"/>
-        <v>18546.214707638268</v>
+        <f t="shared" si="3"/>
+        <v>16581.097138395846</v>
       </c>
       <c r="CL6" s="3">
-        <f t="shared" si="2"/>
-        <v>18731.676854714649</v>
+        <f t="shared" si="3"/>
+        <v>16746.908109779804</v>
       </c>
       <c r="CM6" s="3">
-        <f t="shared" si="2"/>
-        <v>18918.993623261795</v>
+        <f t="shared" si="3"/>
+        <v>16914.377190877603</v>
       </c>
       <c r="CN6" s="3">
-        <f t="shared" si="2"/>
-        <v>19108.183559494413</v>
+        <f t="shared" si="3"/>
+        <v>17083.520962786381</v>
       </c>
       <c r="CO6" s="3">
-        <f t="shared" si="2"/>
-        <v>19299.265395089358</v>
+        <f t="shared" si="3"/>
+        <v>17254.356172414246</v>
       </c>
       <c r="CP6" s="3">
-        <f t="shared" si="2"/>
-        <v>19492.258049040251</v>
+        <f t="shared" si="3"/>
+        <v>17426.899734138387</v>
       </c>
       <c r="CQ6" s="3">
-        <f t="shared" si="2"/>
-        <v>19687.180629530652</v>
+        <f t="shared" si="3"/>
+        <v>17601.168731479771</v>
       </c>
       <c r="CR6" s="3">
-        <f t="shared" si="2"/>
-        <v>19884.052435825961</v>
+        <f t="shared" si="3"/>
+        <v>17777.180418794567</v>
       </c>
       <c r="CS6" s="3">
-        <f t="shared" si="2"/>
-        <v>20082.892960184221</v>
+        <f t="shared" si="3"/>
+        <v>17954.952222982512</v>
       </c>
       <c r="CT6" s="3">
-        <f t="shared" si="2"/>
-        <v>20283.721889786062</v>
+        <f t="shared" si="3"/>
+        <v>18134.501745212339</v>
       </c>
       <c r="CU6" s="3">
-        <f t="shared" ref="CU6:DC6" si="3">CT6*(1+$V$24)</f>
-        <v>20486.559108683923</v>
+        <f t="shared" ref="CU6:DC6" si="4">CT6*(1+$V$24)</f>
+        <v>18315.846762664463</v>
       </c>
       <c r="CV6" s="3">
-        <f t="shared" si="3"/>
-        <v>20691.424699770763</v>
+        <f t="shared" si="4"/>
+        <v>18499.00523029111</v>
       </c>
       <c r="CW6" s="3">
-        <f t="shared" si="3"/>
-        <v>20898.338946768472</v>
+        <f t="shared" si="4"/>
+        <v>18683.99528259402</v>
       </c>
       <c r="CX6" s="3">
-        <f t="shared" si="3"/>
-        <v>21107.322336236157</v>
+        <f t="shared" si="4"/>
+        <v>18870.83523541996</v>
       </c>
       <c r="CY6" s="3">
-        <f t="shared" si="3"/>
-        <v>21318.395559598517</v>
+        <f t="shared" si="4"/>
+        <v>19059.543587774158</v>
       </c>
       <c r="CZ6" s="3">
-        <f t="shared" si="3"/>
-        <v>21531.579515194502</v>
+        <f t="shared" si="4"/>
+        <v>19250.1390236519</v>
       </c>
       <c r="DA6" s="3">
-        <f t="shared" si="3"/>
-        <v>21746.895310346448</v>
+        <f t="shared" si="4"/>
+        <v>19442.640413888421</v>
       </c>
       <c r="DB6" s="3">
-        <f t="shared" si="3"/>
-        <v>21964.364263449912</v>
+        <f t="shared" si="4"/>
+        <v>19637.066818027306</v>
       </c>
       <c r="DC6" s="3">
-        <f t="shared" si="3"/>
-        <v>22184.007906084411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="4"/>
+        <v>19833.437486207578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1538,6 +1551,9 @@
       <c r="Q7" s="5">
         <v>103.319</v>
       </c>
+      <c r="R7" s="5">
+        <v>104.82899999999999</v>
+      </c>
       <c r="V7" s="3">
         <v>362.78</v>
       </c>
@@ -1552,430 +1568,434 @@
         <v>1675.1</v>
       </c>
       <c r="Z7" s="5">
-        <f>SUM(O6:U6)</f>
-        <v>2106.89</v>
+        <f>SUM(O6:R6)</f>
+        <v>2128.5389999999998</v>
       </c>
       <c r="AA7" s="3">
-        <f>Z7*(1+$X$23)</f>
-        <v>2738.9569999999999</v>
+        <f>(2555+2575)/2</f>
+        <v>2565</v>
       </c>
       <c r="AB7" s="3">
-        <f>AA7*(1+$X$23)</f>
-        <v>3560.6441</v>
+        <f t="shared" ref="AA7:AG7" si="5">AA7*(1+$X$23)</f>
+        <v>3334.5</v>
       </c>
       <c r="AC7" s="3">
-        <f>AB7*(1+$X$23)</f>
-        <v>4628.8373300000003</v>
+        <f t="shared" si="5"/>
+        <v>4334.8500000000004</v>
       </c>
       <c r="AD7" s="3">
-        <f>AC7*(1+$X$23)</f>
-        <v>6017.4885290000002</v>
+        <f t="shared" si="5"/>
+        <v>5635.3050000000003</v>
       </c>
       <c r="AE7" s="3">
-        <f>AD7*(1+$X$23)</f>
-        <v>7822.7350877000008</v>
+        <f t="shared" si="5"/>
+        <v>7325.8965000000007</v>
       </c>
       <c r="AF7" s="3">
-        <f>AE7*(1+$X$23)</f>
-        <v>10169.555614010002</v>
+        <f t="shared" si="5"/>
+        <v>9523.6654500000004</v>
       </c>
       <c r="AG7" s="3">
-        <f>AF7*(1+$X$23)</f>
-        <v>13220.422298213003</v>
+        <f t="shared" si="5"/>
+        <v>12380.765085000001</v>
       </c>
       <c r="AH7" s="3">
         <f>AG7*(1+$V$24)</f>
-        <v>13352.626521195134</v>
+        <v>12504.572735850001</v>
       </c>
       <c r="AI7" s="3">
         <f>AH7*(1+$V$24)</f>
-        <v>13486.152786407085</v>
+        <v>12629.618463208501</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" ref="AJ7:CU7" si="4">AI7*(1+$V$24)</f>
-        <v>13621.014314271157</v>
+        <f t="shared" ref="AJ7:CU7" si="6">AI7*(1+$V$24)</f>
+        <v>12755.914647840586</v>
       </c>
       <c r="AK7" s="3">
-        <f t="shared" si="4"/>
-        <v>13757.224457413868</v>
+        <f t="shared" si="6"/>
+        <v>12883.473794318992</v>
       </c>
       <c r="AL7" s="3">
-        <f t="shared" si="4"/>
-        <v>13894.796701988007</v>
+        <f t="shared" si="6"/>
+        <v>13012.308532262183</v>
       </c>
       <c r="AM7" s="3">
-        <f t="shared" si="4"/>
-        <v>14033.744669007887</v>
+        <f t="shared" si="6"/>
+        <v>13142.431617584805</v>
       </c>
       <c r="AN7" s="3">
-        <f t="shared" si="4"/>
-        <v>14174.082115697965</v>
+        <f t="shared" si="6"/>
+        <v>13273.855933760653</v>
       </c>
       <c r="AO7" s="3">
-        <f t="shared" si="4"/>
-        <v>14315.822936854946</v>
+        <f t="shared" si="6"/>
+        <v>13406.594493098261</v>
       </c>
       <c r="AP7" s="3">
-        <f t="shared" si="4"/>
-        <v>14458.981166223495</v>
+        <f t="shared" si="6"/>
+        <v>13540.660438029243</v>
       </c>
       <c r="AQ7" s="3">
-        <f t="shared" si="4"/>
-        <v>14603.570977885731</v>
+        <f t="shared" si="6"/>
+        <v>13676.067042409535</v>
       </c>
       <c r="AR7" s="3">
-        <f t="shared" si="4"/>
-        <v>14749.606687664589</v>
+        <f t="shared" si="6"/>
+        <v>13812.82771283363</v>
       </c>
       <c r="AS7" s="3">
-        <f t="shared" si="4"/>
-        <v>14897.102754541234</v>
+        <f t="shared" si="6"/>
+        <v>13950.955989961967</v>
       </c>
       <c r="AT7" s="3">
-        <f t="shared" si="4"/>
-        <v>15046.073782086647</v>
+        <f t="shared" si="6"/>
+        <v>14090.465549861587</v>
       </c>
       <c r="AU7" s="3">
-        <f t="shared" si="4"/>
-        <v>15196.534519907515</v>
+        <f t="shared" si="6"/>
+        <v>14231.370205360203</v>
       </c>
       <c r="AV7" s="3">
-        <f t="shared" si="4"/>
-        <v>15348.499865106591</v>
+        <f t="shared" si="6"/>
+        <v>14373.683907413804</v>
       </c>
       <c r="AW7" s="3">
-        <f t="shared" si="4"/>
-        <v>15501.984863757656</v>
+        <f t="shared" si="6"/>
+        <v>14517.420746487942</v>
       </c>
       <c r="AX7" s="3">
-        <f t="shared" si="4"/>
-        <v>15657.004712395234</v>
+        <f t="shared" si="6"/>
+        <v>14662.594953952821</v>
       </c>
       <c r="AY7" s="3">
-        <f t="shared" si="4"/>
-        <v>15813.574759519186</v>
+        <f t="shared" si="6"/>
+        <v>14809.220903492349</v>
       </c>
       <c r="AZ7" s="3">
-        <f t="shared" si="4"/>
-        <v>15971.710507114378</v>
+        <f t="shared" si="6"/>
+        <v>14957.313112527272</v>
       </c>
       <c r="BA7" s="3">
-        <f t="shared" si="4"/>
-        <v>16131.427612185522</v>
+        <f t="shared" si="6"/>
+        <v>15106.886243652545</v>
       </c>
       <c r="BB7" s="3">
-        <f t="shared" si="4"/>
-        <v>16292.741888307377</v>
+        <f t="shared" si="6"/>
+        <v>15257.95510608907</v>
       </c>
       <c r="BC7" s="3">
-        <f t="shared" si="4"/>
-        <v>16455.669307190452</v>
+        <f t="shared" si="6"/>
+        <v>15410.534657149961</v>
       </c>
       <c r="BD7" s="3">
-        <f t="shared" si="4"/>
-        <v>16620.226000262355</v>
+        <f t="shared" si="6"/>
+        <v>15564.640003721461</v>
       </c>
       <c r="BE7" s="3">
-        <f t="shared" si="4"/>
-        <v>16786.42826026498</v>
+        <f t="shared" si="6"/>
+        <v>15720.286403758675</v>
       </c>
       <c r="BF7" s="3">
-        <f t="shared" si="4"/>
-        <v>16954.292542867632</v>
+        <f t="shared" si="6"/>
+        <v>15877.489267796262</v>
       </c>
       <c r="BG7" s="3">
-        <f t="shared" si="4"/>
-        <v>17123.835468296307</v>
+        <f t="shared" si="6"/>
+        <v>16036.264160474224</v>
       </c>
       <c r="BH7" s="3">
-        <f t="shared" si="4"/>
-        <v>17295.07382297927</v>
+        <f t="shared" si="6"/>
+        <v>16196.626802078967</v>
       </c>
       <c r="BI7" s="3">
-        <f t="shared" si="4"/>
-        <v>17468.024561209062</v>
+        <f t="shared" si="6"/>
+        <v>16358.593070099756</v>
       </c>
       <c r="BJ7" s="3">
-        <f t="shared" si="4"/>
-        <v>17642.704806821152</v>
+        <f t="shared" si="6"/>
+        <v>16522.179000800752</v>
       </c>
       <c r="BK7" s="3">
-        <f t="shared" si="4"/>
-        <v>17819.131854889365</v>
+        <f t="shared" si="6"/>
+        <v>16687.400790808759</v>
       </c>
       <c r="BL7" s="3">
-        <f t="shared" si="4"/>
-        <v>17997.323173438257</v>
+        <f t="shared" si="6"/>
+        <v>16854.274798716848</v>
       </c>
       <c r="BM7" s="3">
-        <f t="shared" si="4"/>
-        <v>18177.296405172641</v>
+        <f t="shared" si="6"/>
+        <v>17022.817546704016</v>
       </c>
       <c r="BN7" s="3">
-        <f t="shared" si="4"/>
-        <v>18359.069369224369</v>
+        <f t="shared" si="6"/>
+        <v>17193.045722171057</v>
       </c>
       <c r="BO7" s="3">
-        <f t="shared" si="4"/>
-        <v>18542.660062916613</v>
+        <f t="shared" si="6"/>
+        <v>17364.976179392768</v>
       </c>
       <c r="BP7" s="3">
-        <f t="shared" si="4"/>
-        <v>18728.086663545779</v>
+        <f t="shared" si="6"/>
+        <v>17538.625941186696</v>
       </c>
       <c r="BQ7" s="3">
-        <f t="shared" si="4"/>
-        <v>18915.367530181236</v>
+        <f t="shared" si="6"/>
+        <v>17714.012200598561</v>
       </c>
       <c r="BR7" s="3">
-        <f t="shared" si="4"/>
-        <v>19104.521205483048</v>
+        <f t="shared" si="6"/>
+        <v>17891.152322604546</v>
       </c>
       <c r="BS7" s="3">
-        <f t="shared" si="4"/>
-        <v>19295.566417537877</v>
+        <f t="shared" si="6"/>
+        <v>18070.063845830591</v>
       </c>
       <c r="BT7" s="3">
-        <f t="shared" si="4"/>
-        <v>19488.522081713258</v>
+        <f t="shared" si="6"/>
+        <v>18250.764484288899</v>
       </c>
       <c r="BU7" s="3">
-        <f t="shared" si="4"/>
-        <v>19683.407302530391</v>
+        <f t="shared" si="6"/>
+        <v>18433.272129131787</v>
       </c>
       <c r="BV7" s="3">
-        <f t="shared" si="4"/>
-        <v>19880.241375555695</v>
+        <f t="shared" si="6"/>
+        <v>18617.604850423104</v>
       </c>
       <c r="BW7" s="3">
-        <f t="shared" si="4"/>
-        <v>20079.043789311254</v>
+        <f t="shared" si="6"/>
+        <v>18803.780898927336</v>
       </c>
       <c r="BX7" s="3">
-        <f t="shared" si="4"/>
-        <v>20279.834227204366</v>
+        <f t="shared" si="6"/>
+        <v>18991.818707916609</v>
       </c>
       <c r="BY7" s="3">
-        <f t="shared" si="4"/>
-        <v>20482.632569476409</v>
+        <f t="shared" si="6"/>
+        <v>19181.736894995774</v>
       </c>
       <c r="BZ7" s="3">
-        <f t="shared" si="4"/>
-        <v>20687.458895171174</v>
+        <f t="shared" si="6"/>
+        <v>19373.554263945731</v>
       </c>
       <c r="CA7" s="3">
-        <f t="shared" si="4"/>
-        <v>20894.333484122886</v>
+        <f t="shared" si="6"/>
+        <v>19567.289806585188</v>
       </c>
       <c r="CB7" s="3">
-        <f t="shared" si="4"/>
-        <v>21103.276818964114</v>
+        <f t="shared" si="6"/>
+        <v>19762.96270465104</v>
       </c>
       <c r="CC7" s="3">
-        <f t="shared" si="4"/>
-        <v>21314.309587153755</v>
+        <f t="shared" si="6"/>
+        <v>19960.59233169755</v>
       </c>
       <c r="CD7" s="3">
-        <f t="shared" si="4"/>
-        <v>21527.452683025294</v>
+        <f t="shared" si="6"/>
+        <v>20160.198255014526</v>
       </c>
       <c r="CE7" s="3">
-        <f t="shared" si="4"/>
-        <v>21742.727209855548</v>
+        <f t="shared" si="6"/>
+        <v>20361.800237564672</v>
       </c>
       <c r="CF7" s="3">
-        <f t="shared" si="4"/>
-        <v>21960.154481954105</v>
+        <f t="shared" si="6"/>
+        <v>20565.418239940318</v>
       </c>
       <c r="CG7" s="3">
-        <f t="shared" si="4"/>
-        <v>22179.756026773648</v>
+        <f t="shared" si="6"/>
+        <v>20771.072422339723</v>
       </c>
       <c r="CH7" s="3">
-        <f t="shared" si="4"/>
-        <v>22401.553587041384</v>
+        <f t="shared" si="6"/>
+        <v>20978.783146563121</v>
       </c>
       <c r="CI7" s="3">
-        <f t="shared" si="4"/>
-        <v>22625.569122911798</v>
+        <f t="shared" si="6"/>
+        <v>21188.570978028751</v>
       </c>
       <c r="CJ7" s="3">
-        <f t="shared" si="4"/>
-        <v>22851.824814140917</v>
+        <f t="shared" si="6"/>
+        <v>21400.456687809037</v>
       </c>
       <c r="CK7" s="3">
-        <f t="shared" si="4"/>
-        <v>23080.343062282325</v>
+        <f t="shared" si="6"/>
+        <v>21614.461254687129</v>
       </c>
       <c r="CL7" s="3">
-        <f t="shared" si="4"/>
-        <v>23311.146492905147</v>
+        <f t="shared" si="6"/>
+        <v>21830.605867234</v>
       </c>
       <c r="CM7" s="3">
-        <f t="shared" si="4"/>
-        <v>23544.257957834197</v>
+        <f t="shared" si="6"/>
+        <v>22048.911925906341</v>
       </c>
       <c r="CN7" s="3">
-        <f t="shared" si="4"/>
-        <v>23779.70053741254</v>
+        <f t="shared" si="6"/>
+        <v>22269.401045165403</v>
       </c>
       <c r="CO7" s="3">
-        <f t="shared" si="4"/>
-        <v>24017.497542786667</v>
+        <f t="shared" si="6"/>
+        <v>22492.095055617057</v>
       </c>
       <c r="CP7" s="3">
-        <f t="shared" si="4"/>
-        <v>24257.672518214535</v>
+        <f t="shared" si="6"/>
+        <v>22717.016006173228</v>
       </c>
       <c r="CQ7" s="3">
-        <f t="shared" si="4"/>
-        <v>24500.24924339668</v>
+        <f t="shared" si="6"/>
+        <v>22944.186166234958</v>
       </c>
       <c r="CR7" s="3">
-        <f t="shared" si="4"/>
-        <v>24745.251735830647</v>
+        <f t="shared" si="6"/>
+        <v>23173.62802789731</v>
       </c>
       <c r="CS7" s="3">
-        <f t="shared" si="4"/>
-        <v>24992.704253188953</v>
+        <f t="shared" si="6"/>
+        <v>23405.364308176282</v>
       </c>
       <c r="CT7" s="3">
-        <f t="shared" si="4"/>
-        <v>25242.631295720843</v>
+        <f t="shared" si="6"/>
+        <v>23639.417951258045</v>
       </c>
       <c r="CU7" s="3">
-        <f t="shared" si="4"/>
-        <v>25495.057608678053</v>
+        <f t="shared" si="6"/>
+        <v>23875.812130770624</v>
       </c>
       <c r="CV7" s="3">
-        <f t="shared" ref="CV7:DC7" si="5">CU7*(1+$V$24)</f>
-        <v>25750.008184764833</v>
+        <f t="shared" ref="CV7:DC7" si="7">CU7*(1+$V$24)</f>
+        <v>24114.570252078331</v>
       </c>
       <c r="CW7" s="3">
-        <f t="shared" si="5"/>
-        <v>26007.50826661248</v>
+        <f t="shared" si="7"/>
+        <v>24355.715954599113</v>
       </c>
       <c r="CX7" s="3">
-        <f t="shared" si="5"/>
-        <v>26267.583349278604</v>
+        <f t="shared" si="7"/>
+        <v>24599.273114145104</v>
       </c>
       <c r="CY7" s="3">
-        <f t="shared" si="5"/>
-        <v>26530.259182771391</v>
+        <f t="shared" si="7"/>
+        <v>24845.265845286554</v>
       </c>
       <c r="CZ7" s="3">
-        <f t="shared" si="5"/>
-        <v>26795.561774599104</v>
+        <f t="shared" si="7"/>
+        <v>25093.718503739419</v>
       </c>
       <c r="DA7" s="3">
-        <f t="shared" si="5"/>
-        <v>27063.517392345097</v>
+        <f t="shared" si="7"/>
+        <v>25344.655688776813</v>
       </c>
       <c r="DB7" s="3">
-        <f t="shared" si="5"/>
-        <v>27334.152566268549</v>
+        <f t="shared" si="7"/>
+        <v>25598.102245664581</v>
       </c>
       <c r="DC7" s="3">
-        <f t="shared" si="5"/>
-        <v>27607.494091931236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="7"/>
+        <v>25854.083268121227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:Q8" si="6">+E6-E7</f>
+        <f t="shared" ref="E8:R8" si="8">+E6-E7</f>
         <v>120.691</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>136.67500000000001</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>151.88300000000001</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>176.45100000000002</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>207.15600000000001</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>259.04899999999998</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>288.56799999999998</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>324.21299999999997</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>342.93400000000003</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>372.642</v>
       </c>
       <c r="O8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>381.8</v>
       </c>
       <c r="P8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>407.79399999999998</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>444.21699999999993</v>
       </c>
+      <c r="R8" s="6">
+        <f t="shared" si="8"/>
+        <v>484.82</v>
+      </c>
       <c r="Z8" s="24">
-        <f>(Z7-Y7)/Y7</f>
-        <v>0.25776968539191691</v>
+        <f t="shared" ref="Z8:AH8" si="9">(Z7-Y7)/Y7</f>
+        <v>0.27069368992895937</v>
       </c>
       <c r="AA8" s="22">
-        <f>(AA7-Z7)/Z7</f>
+        <f t="shared" si="9"/>
+        <v>0.20505191589160465</v>
+      </c>
+      <c r="AB8" s="22">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="AC8" s="22">
+        <f t="shared" si="9"/>
+        <v>0.3000000000000001</v>
+      </c>
+      <c r="AD8" s="22">
+        <f t="shared" si="9"/>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="AE8" s="22">
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AB8" s="22">
-        <f>(AB7-AA7)/AA7</f>
+      <c r="AF8" s="22">
+        <f t="shared" si="9"/>
+        <v>0.29999999999999993</v>
+      </c>
+      <c r="AG8" s="22">
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AC8" s="22">
-        <f>(AC7-AB7)/AB7</f>
-        <v>0.3000000000000001</v>
-      </c>
-      <c r="AD8" s="22">
-        <f>(AD7-AC7)/AC7</f>
-        <v>0.29999999999999993</v>
-      </c>
-      <c r="AE8" s="22">
-        <f>(AE7-AD7)/AD7</f>
-        <v>0.3000000000000001</v>
-      </c>
-      <c r="AF8" s="22">
-        <f>(AF7-AE7)/AE7</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="AG8" s="22">
-        <f>(AG7-AF7)/AF7</f>
-        <v>0.3000000000000001</v>
-      </c>
       <c r="AH8" s="22">
-        <f>(AH7-AG7)/AG7</f>
-        <v>1.0000000000000064E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="9"/>
+        <v>9.9999999999999863E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -2020,8 +2040,11 @@
       <c r="Q9" s="5">
         <v>240.22499999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R9" s="5">
+        <v>253.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
@@ -2066,8 +2089,11 @@
       <c r="Q10" s="5">
         <v>156.87</v>
       </c>
-    </row>
-    <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="5">
+        <v>159.97999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2112,98 +2138,105 @@
       <c r="Q11" s="5">
         <v>51.351999999999997</v>
       </c>
-    </row>
-    <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R11" s="5">
+        <v>43.847999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f t="shared" ref="E12:Q12" si="7">SUM(E9:E11)</f>
+        <f t="shared" ref="E12:R12" si="10">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>145.613</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>164.71299999999999</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>186.33699999999999</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>212.05100000000002</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>250.59399999999999</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>278.154</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>327.35199999999998</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>374.27599999999995</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>407.27</v>
       </c>
       <c r="O12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>416.77</v>
       </c>
       <c r="P12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>429.62</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>448.447</v>
       </c>
-    </row>
-    <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R12" s="6">
+        <f t="shared" si="10"/>
+        <v>457.07800000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f t="shared" ref="E13:Q13" si="8">E8-E12</f>
+        <f t="shared" ref="E13:R13" si="11">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-8.9379999999999882</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-12.829999999999984</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-9.8859999999999673</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-4.8950000000000102</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>8.4549999999999841</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>10.413999999999987</v>
       </c>
       <c r="L13" s="6">
@@ -2211,27 +2244,31 @@
         <v>-3.13900000000001</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-31.341999999999928</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-34.627999999999986</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-34.96999999999997</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-21.826000000000022</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-4.230000000000075</v>
       </c>
-    </row>
-    <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R13" s="6">
+        <f t="shared" si="11"/>
+        <v>27.741999999999962</v>
+      </c>
+    </row>
+    <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2286,67 +2323,75 @@
         <f>-1.303+29.883</f>
         <v>28.58</v>
       </c>
-    </row>
-    <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R14" s="5">
+        <f>-1.292+30.817</f>
+        <v>29.524999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f t="shared" ref="E15:Q15" si="9">+E13+E14</f>
+        <f t="shared" ref="E15:R15" si="12">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-15.166999999999987</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-12.528999999999986</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-9.6579999999999675</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-4.7670000000000101</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>8.531999999999984</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>10.853999999999989</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-1.1000000000010779E-2</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-22.21599999999993</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-25.009999999999987</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-20.423999999999971</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-0.72800000000002285</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>24.349999999999923</v>
       </c>
-    </row>
-    <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R15" s="6">
+        <f t="shared" si="12"/>
+        <v>57.26699999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
@@ -2391,126 +2436,137 @@
       <c r="Q16" s="5">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R16" s="5">
+        <v>3.274</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:Q17" si="10">+E15-E16</f>
+        <f t="shared" ref="E17:R17" si="13">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-16.159999999999986</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-11.989999999999986</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-6.6979999999999675</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-4.0500000000000105</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7.1689999999999845</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>9.7379999999999889</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-4.8790000000000111</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-25.141999999999932</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-28.189999999999987</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-24.08599999999997</v>
       </c>
       <c r="P17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-3.7890000000000228</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>22.679999999999922</v>
       </c>
-    </row>
-    <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R17" s="6">
+        <f t="shared" si="13"/>
+        <v>53.992999999999959</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:Q18" si="11">+E17/E19</f>
+        <f t="shared" ref="E18:R18" si="14">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-5.3147929500060795E-2</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-3.9178653352241861E-2</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-2.1745411809011676E-2</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-1.3054114947122809E-2</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2.0727021455604115E-2</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>2.8171540321927365E-2</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-1.5498975523753589E-2</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-7.9565809044589805E-2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-8.8829928028536453E-2</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-7.5437068960117162E-2</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>-1.1759229086169245E-2</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>6.9665219915406279E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R18" s="7">
+        <f t="shared" si="14"/>
+        <v>0.16416485504492304</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -2555,8 +2611,11 @@
       <c r="Q19" s="5">
         <v>325.55700000000002</v>
       </c>
-    </row>
-    <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R19" s="5">
+        <v>328.89499999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
@@ -2567,76 +2626,80 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:K21" si="12">+I6/E6-1</f>
+        <f t="shared" ref="I21:K21" si="15">+I6/E6-1</f>
         <v>0.74875060610958455</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.83741431074009598</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.82841515192723181</v>
       </c>
       <c r="L21" s="10">
-        <f>+L6/H6-1</f>
+        <f t="shared" ref="L21:S21" si="16">+L6/H6-1</f>
         <v>0.73898411040081502</v>
       </c>
       <c r="M21" s="10">
-        <f>+M6/I6-1</f>
+        <f t="shared" si="16"/>
         <v>0.61387196474520134</v>
       </c>
       <c r="N21" s="10">
-        <f>+N6/J6-1</f>
+        <f t="shared" si="16"/>
         <v>0.43900023911857233</v>
       </c>
       <c r="O21" s="10">
-        <f>+O6/K6-1</f>
+        <f t="shared" si="16"/>
         <v>0.32692614935404807</v>
       </c>
       <c r="P21" s="10">
-        <f>+P6/L6-1</f>
+        <f t="shared" si="16"/>
         <v>0.25484441249033574</v>
       </c>
       <c r="Q21" s="10">
-        <f>+Q6/M6-1</f>
+        <f t="shared" si="16"/>
         <v>0.25428318134024219</v>
       </c>
       <c r="R21" s="10">
-        <f>+R6/N6-1</f>
-        <v>0.21005796774172936</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+        <f t="shared" si="16"/>
+        <v>0.25617864545940661</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" si="16"/>
+        <v>0.22271721394852539</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="13">+E8/E6</f>
+        <f t="shared" ref="E22:H22" si="17">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.76986554460911061</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.7649648197674126</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0.75552025485015994</v>
       </c>
       <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="14">+I8/I6</f>
+        <f t="shared" ref="I22:K22" si="18">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0.79414649997854059</v>
       </c>
       <c r="K22" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0.79488747486433631</v>
       </c>
       <c r="L22" s="12">
@@ -2644,24 +2707,28 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:Q22" si="15">+M8/M6</f>
+        <f t="shared" ref="M22:R22" si="19">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.79387045988593929</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.79258647247121738</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.8001608978887057</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.81130190526285029</v>
+      </c>
+      <c r="R22" s="12">
+        <f t="shared" si="19"/>
+        <v>0.82221796356815668</v>
       </c>
       <c r="U22" t="s">
         <v>71</v>
@@ -2673,12 +2740,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="U23" s="15" t="s">
         <v>62</v>
       </c>
       <c r="V23" s="23">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="W23" s="15" t="s">
         <v>62</v>
@@ -2687,7 +2754,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
@@ -2716,7 +2783,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -2743,7 +2810,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2770,17 +2837,17 @@
       </c>
       <c r="V26" s="18">
         <f>NPV(V25,V6:DC6)</f>
-        <v>58324.781680299697</v>
+        <v>53169.98322190965</v>
       </c>
       <c r="W26" s="17" t="s">
         <v>63</v>
       </c>
       <c r="X26" s="26">
         <f>NPV($V$25,V7:DC7)</f>
-        <v>70118.732659662914</v>
-      </c>
-    </row>
-    <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>65936.250330536161</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -2805,17 +2872,17 @@
       </c>
       <c r="V27" s="21">
         <f>Main!$O$3</f>
-        <v>325.55700000000002</v>
+        <v>328</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>1</v>
       </c>
       <c r="X27" s="21">
         <f>Main!$O$3</f>
-        <v>325.55700000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -2840,17 +2907,17 @@
       </c>
       <c r="V28" s="19">
         <f>V26/V27</f>
-        <v>179.1538246153506</v>
+        <v>162.10360738387089</v>
       </c>
       <c r="W28" s="17" t="s">
         <v>64</v>
       </c>
       <c r="X28" s="19">
         <f>X26/X27</f>
-        <v>215.38081706018579</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>201.02515344675658</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2875,17 +2942,17 @@
       </c>
       <c r="V29" s="20">
         <f>(V28-Main!$O$2)/Main!$O$2</f>
-        <v>0.32795066796642652</v>
+        <v>0.24944972548073749</v>
       </c>
       <c r="W29" s="17" t="s">
         <v>65</v>
       </c>
       <c r="X29" s="20">
         <f>(X28-Main!$O$2)/Main!$O$2</f>
-        <v>0.59647777822389592</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.549446226659138</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -2912,17 +2979,17 @@
       </c>
       <c r="V30" s="18">
         <f>V27*V28</f>
-        <v>58324.781680299697</v>
+        <v>53169.983221909657</v>
       </c>
       <c r="W30" s="17" t="s">
         <v>66</v>
       </c>
       <c r="X30" s="18">
         <f>X27*X28</f>
-        <v>70118.732659662914</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>65936.250330536161</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -2943,7 +3010,7 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
         <v>32</v>
       </c>
@@ -2966,7 +3033,7 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="34" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>40</v>
       </c>
@@ -2987,7 +3054,7 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>41</v>
       </c>
@@ -3008,7 +3075,7 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
         <v>37</v>
       </c>
@@ -3031,7 +3098,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>42</v>
       </c>
@@ -3054,7 +3121,7 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
         <v>4</v>
       </c>
@@ -3075,7 +3142,7 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
         <v>39</v>
       </c>
@@ -3096,7 +3163,7 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
@@ -3117,7 +3184,7 @@
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>44</v>
       </c>
@@ -3140,7 +3207,7 @@
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="43" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>48</v>
       </c>
@@ -3160,7 +3227,7 @@
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
         <v>49</v>
       </c>
@@ -3179,7 +3246,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>50</v>
       </c>
@@ -3198,7 +3265,7 @@
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
         <v>51</v>
       </c>
@@ -3217,7 +3284,7 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>52</v>
       </c>
@@ -3236,7 +3303,7 @@
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
         <v>53</v>
       </c>
@@ -3255,7 +3322,7 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
         <v>54</v>
       </c>
@@ -3274,7 +3341,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
         <v>37</v>
       </c>
@@ -3293,7 +3360,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
         <v>33</v>
       </c>
@@ -3312,7 +3379,7 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
         <v>55</v>
       </c>
@@ -3331,7 +3398,7 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="5" t="s">
         <v>56</v>
       </c>
@@ -3351,7 +3418,7 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
         <v>57</v>
       </c>

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A787C9-DEDB-49DF-98D5-D831FFAE8E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D9861-D47E-4B59-865B-7D39ECFF3979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="40305" yWindow="90" windowWidth="11310" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -837,9 +837,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3BD0B1-E685-4627-8A01-75A3D2BDF860}">
   <dimension ref="N2:P7"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N2" t="s">
         <v>0</v>
       </c>
@@ -847,7 +847,7 @@
         <v>129.74</v>
       </c>
     </row>
-    <row r="3" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N3" t="s">
         <v>1</v>
       </c>
@@ -856,7 +856,7 @@
       </c>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N4" t="s">
         <v>2</v>
       </c>
@@ -865,7 +865,7 @@
         <v>42554.720000000001</v>
       </c>
     </row>
-    <row r="5" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N5" t="s">
         <v>3</v>
       </c>
@@ -874,7 +874,7 @@
       </c>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N6" t="s">
         <v>4</v>
       </c>
@@ -883,7 +883,7 @@
       </c>
       <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="14:16" x14ac:dyDescent="0.2">
       <c r="N7" t="s">
         <v>5</v>
       </c>
@@ -900,20 +900,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
   <dimension ref="A1:DC54"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="13" width="9.109375" style="2"/>
-    <col min="14" max="14" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="13" width="9.140625" style="2"/>
+    <col min="14" max="14" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:107" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -945,7 +945,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:107" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:107" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -1057,10 +1057,10 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="4" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:107" x14ac:dyDescent="0.2">
       <c r="Z4" s="25"/>
     </row>
-    <row r="5" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:107" x14ac:dyDescent="0.2">
       <c r="V5" t="s">
         <v>69</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>1.0000000000000097E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>19833.437486207578</v>
       </c>
     </row>
-    <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>2565</v>
       </c>
       <c r="AB7" s="3">
-        <f t="shared" ref="AA7:AG7" si="5">AA7*(1+$X$23)</f>
+        <f t="shared" ref="AB7:AG7" si="5">AA7*(1+$X$23)</f>
         <v>3334.5</v>
       </c>
       <c r="AC7" s="3">
@@ -1896,7 +1896,7 @@
         <v>25854.083268121227</v>
       </c>
     </row>
-    <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>9.9999999999999863E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>253.25</v>
       </c>
     </row>
-    <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>159.97999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>43.847999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>457.07800000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>27.741999999999962</v>
       </c>
     </row>
-    <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>29.524999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>57.26699999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>3.274</v>
       </c>
     </row>
-    <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>53.992999999999959</v>
       </c>
     </row>
-    <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>0.16416485504492304</v>
       </c>
     </row>
-    <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>328.89499999999998</v>
       </c>
     </row>
-    <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>0.22271721394852539</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
       <c r="U23" s="15" t="s">
         <v>62</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="26" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>65936.250330536161</v>
       </c>
     </row>
-    <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>201.02515344675658</v>
       </c>
     </row>
-    <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>0.549446226659138</v>
       </c>
     </row>
-    <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>65936.250330536161</v>
       </c>
     </row>
-    <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -3010,7 +3010,7 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
         <v>32</v>
       </c>
@@ -3033,7 +3033,7 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="34" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
         <v>40</v>
       </c>
@@ -3054,7 +3054,7 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="5" t="s">
         <v>41</v>
       </c>
@@ -3075,7 +3075,7 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="5" t="s">
         <v>37</v>
       </c>
@@ -3098,7 +3098,7 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
         <v>42</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="5" t="s">
         <v>4</v>
       </c>
@@ -3142,7 +3142,7 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
         <v>39</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
         <v>44</v>
       </c>
@@ -3207,7 +3207,7 @@
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="43" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="5" t="s">
         <v>48</v>
       </c>
@@ -3227,7 +3227,7 @@
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="5" t="s">
         <v>49</v>
       </c>
@@ -3246,7 +3246,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="5" t="s">
         <v>50</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="5" t="s">
         <v>51</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="5" t="s">
         <v>52</v>
       </c>
@@ -3303,7 +3303,7 @@
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="5" t="s">
         <v>53</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="5" t="s">
         <v>54</v>
       </c>
@@ -3341,7 +3341,7 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="5" t="s">
         <v>37</v>
       </c>
@@ -3360,7 +3360,7 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="5" t="s">
         <v>33</v>
       </c>
@@ -3379,7 +3379,7 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="5" t="s">
         <v>55</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="5" t="s">
         <v>56</v>
       </c>
@@ -3418,7 +3418,7 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="5" t="s">
         <v>57</v>
       </c>

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0D9861-D47E-4B59-865B-7D39ECFF3979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F860361-B1DC-497F-A4DE-DF1DD41DEC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40305" yWindow="90" windowWidth="11310" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="30270" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>Price</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Q124</t>
+  </si>
+  <si>
+    <t>Q224</t>
   </si>
 </sst>
 </file>
@@ -844,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>129.74</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -852,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="P3" s="2"/>
     </row>
@@ -862,7 +865,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>42554.720000000001</v>
+        <v>38936.959999999999</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -870,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <v>2080</v>
+        <v>2800</v>
       </c>
       <c r="P5" s="2"/>
     </row>
@@ -889,7 +892,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>42211.546000000002</v>
+        <v>37873.786</v>
       </c>
     </row>
   </sheetData>
@@ -997,7 +1000,9 @@
       <c r="S2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="T2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2">
         <v>2019</v>
@@ -1056,6 +1061,12 @@
       <c r="L3" s="2">
         <v>2420</v>
       </c>
+      <c r="O3">
+        <v>2910</v>
+      </c>
+      <c r="S3">
+        <v>3340</v>
+      </c>
     </row>
     <row r="4" spans="1:107" x14ac:dyDescent="0.2">
       <c r="Z4" s="25"/>
@@ -1082,35 +1093,35 @@
       </c>
       <c r="AA5" s="24">
         <f>(AA6-Z6)/Z6</f>
-        <v>0.23999999999999994</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AB5" s="24">
         <f t="shared" si="1"/>
-        <v>0.24000000000000005</v>
+        <v>0.21999999999999995</v>
       </c>
       <c r="AC5" s="24">
         <f t="shared" si="1"/>
-        <v>0.23999999999999996</v>
+        <v>0.21999999999999992</v>
       </c>
       <c r="AD5" s="24">
         <f t="shared" si="1"/>
-        <v>0.23999999999999994</v>
+        <v>0.22000000000000003</v>
       </c>
       <c r="AE5" s="24">
         <f t="shared" si="1"/>
-        <v>0.24000000000000002</v>
+        <v>0.21999999999999989</v>
       </c>
       <c r="AF5" s="24">
         <f t="shared" si="1"/>
-        <v>0.23999999999999994</v>
+        <v>0.22000000000000003</v>
       </c>
       <c r="AG5" s="24">
         <f t="shared" si="1"/>
-        <v>0.23999999999999994</v>
+        <v>0.21999999999999992</v>
       </c>
       <c r="AH5" s="24">
         <f t="shared" si="1"/>
-        <v>1.0000000000000097E-2</v>
+        <v>1.0000000000000007E-2</v>
       </c>
     </row>
     <row r="6" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1162,8 +1173,11 @@
         <v>589.649</v>
       </c>
       <c r="S6" s="3">
-        <f>(587+591)/2</f>
-        <v>589</v>
+        <v>611</v>
+      </c>
+      <c r="T6" s="3">
+        <f>(620+624)/2</f>
+        <v>622</v>
       </c>
       <c r="V6" s="3">
         <v>362.78</v>
@@ -1183,327 +1197,327 @@
       </c>
       <c r="AA6" s="3">
         <f t="shared" ref="AA6:AG6" si="2">Z6*(1+$V$23)</f>
-        <v>2612.6799999999998</v>
+        <v>2570.54</v>
       </c>
       <c r="AB6" s="3">
         <f t="shared" si="2"/>
-        <v>3239.7231999999999</v>
+        <v>3136.0587999999998</v>
       </c>
       <c r="AC6" s="3">
         <f t="shared" si="2"/>
-        <v>4017.2567679999997</v>
+        <v>3825.9917359999995</v>
       </c>
       <c r="AD6" s="3">
         <f t="shared" si="2"/>
-        <v>4981.3983923199994</v>
+        <v>4667.7099179199995</v>
       </c>
       <c r="AE6" s="3">
         <f t="shared" si="2"/>
-        <v>6176.9340064767994</v>
+        <v>5694.6060998623989</v>
       </c>
       <c r="AF6" s="3">
         <f t="shared" si="2"/>
-        <v>7659.3981680312309</v>
+        <v>6947.4194418321267</v>
       </c>
       <c r="AG6" s="3">
         <f t="shared" si="2"/>
-        <v>9497.6537283587259</v>
+        <v>8475.851719035194</v>
       </c>
       <c r="AH6" s="3">
         <f>AG6*(1+$V$24)</f>
-        <v>9592.630265642314</v>
+        <v>8560.610236225546</v>
       </c>
       <c r="AI6" s="3">
         <f t="shared" ref="AI6:CT6" si="3">AH6*(1+$V$24)</f>
-        <v>9688.5565682987381</v>
+        <v>8646.2163385878011</v>
       </c>
       <c r="AJ6" s="3">
         <f t="shared" si="3"/>
-        <v>9785.4421339817254</v>
+        <v>8732.6785019736799</v>
       </c>
       <c r="AK6" s="3">
         <f t="shared" si="3"/>
-        <v>9883.2965553215436</v>
+        <v>8820.005286993417</v>
       </c>
       <c r="AL6" s="3">
         <f t="shared" si="3"/>
-        <v>9982.1295208747597</v>
+        <v>8908.2053398633507</v>
       </c>
       <c r="AM6" s="3">
         <f t="shared" si="3"/>
-        <v>10081.950816083507</v>
+        <v>8997.2873932619841</v>
       </c>
       <c r="AN6" s="3">
         <f t="shared" si="3"/>
-        <v>10182.770324244342</v>
+        <v>9087.2602671946042</v>
       </c>
       <c r="AO6" s="3">
         <f t="shared" si="3"/>
-        <v>10284.598027486785</v>
+        <v>9178.1328698665511</v>
       </c>
       <c r="AP6" s="3">
         <f t="shared" si="3"/>
-        <v>10387.444007761653</v>
+        <v>9269.9141985652168</v>
       </c>
       <c r="AQ6" s="3">
         <f t="shared" si="3"/>
-        <v>10491.318447839269</v>
+        <v>9362.6133405508699</v>
       </c>
       <c r="AR6" s="3">
         <f t="shared" si="3"/>
-        <v>10596.231632317662</v>
+        <v>9456.2394739563788</v>
       </c>
       <c r="AS6" s="3">
         <f t="shared" si="3"/>
-        <v>10702.193948640839</v>
+        <v>9550.8018686959422</v>
       </c>
       <c r="AT6" s="3">
         <f t="shared" si="3"/>
-        <v>10809.215888127248</v>
+        <v>9646.3098873829022</v>
       </c>
       <c r="AU6" s="3">
         <f t="shared" si="3"/>
-        <v>10917.308047008521</v>
+        <v>9742.7729862567321</v>
       </c>
       <c r="AV6" s="3">
         <f t="shared" si="3"/>
-        <v>11026.481127478606</v>
+        <v>9840.2007161192996</v>
       </c>
       <c r="AW6" s="3">
         <f t="shared" si="3"/>
-        <v>11136.745938753393</v>
+        <v>9938.6027232804936</v>
       </c>
       <c r="AX6" s="3">
         <f t="shared" si="3"/>
-        <v>11248.113398140928</v>
+        <v>10037.988750513299</v>
       </c>
       <c r="AY6" s="3">
         <f t="shared" si="3"/>
-        <v>11360.594532122337</v>
+        <v>10138.368638018432</v>
       </c>
       <c r="AZ6" s="3">
         <f t="shared" si="3"/>
-        <v>11474.200477443561</v>
+        <v>10239.752324398616</v>
       </c>
       <c r="BA6" s="3">
         <f t="shared" si="3"/>
-        <v>11588.942482217997</v>
+        <v>10342.149847642602</v>
       </c>
       <c r="BB6" s="3">
         <f t="shared" si="3"/>
-        <v>11704.831907040178</v>
+        <v>10445.571346119028</v>
       </c>
       <c r="BC6" s="3">
         <f t="shared" si="3"/>
-        <v>11821.880226110579</v>
+        <v>10550.027059580218</v>
       </c>
       <c r="BD6" s="3">
         <f t="shared" si="3"/>
-        <v>11940.099028371686</v>
+        <v>10655.527330176021</v>
       </c>
       <c r="BE6" s="3">
         <f t="shared" si="3"/>
-        <v>12059.500018655403</v>
+        <v>10762.082603477782</v>
       </c>
       <c r="BF6" s="3">
         <f t="shared" si="3"/>
-        <v>12180.095018841957</v>
+        <v>10869.70342951256</v>
       </c>
       <c r="BG6" s="3">
         <f t="shared" si="3"/>
-        <v>12301.895969030376</v>
+        <v>10978.400463807686</v>
       </c>
       <c r="BH6" s="3">
         <f t="shared" si="3"/>
-        <v>12424.91492872068</v>
+        <v>11088.184468445763</v>
       </c>
       <c r="BI6" s="3">
         <f t="shared" si="3"/>
-        <v>12549.164078007887</v>
+        <v>11199.066313130221</v>
       </c>
       <c r="BJ6" s="3">
         <f t="shared" si="3"/>
-        <v>12674.655718787966</v>
+        <v>11311.056976261523</v>
       </c>
       <c r="BK6" s="3">
         <f t="shared" si="3"/>
-        <v>12801.402275975846</v>
+        <v>11424.167546024139</v>
       </c>
       <c r="BL6" s="3">
         <f t="shared" si="3"/>
-        <v>12929.416298735605</v>
+        <v>11538.40922148438</v>
       </c>
       <c r="BM6" s="3">
         <f t="shared" si="3"/>
-        <v>13058.710461722962</v>
+        <v>11653.793313699225</v>
       </c>
       <c r="BN6" s="3">
         <f t="shared" si="3"/>
-        <v>13189.297566340192</v>
+        <v>11770.331246836218</v>
       </c>
       <c r="BO6" s="3">
         <f t="shared" si="3"/>
-        <v>13321.190542003595</v>
+        <v>11888.03455930458</v>
       </c>
       <c r="BP6" s="3">
         <f t="shared" si="3"/>
-        <v>13454.40244742363</v>
+        <v>12006.914904897627</v>
       </c>
       <c r="BQ6" s="3">
         <f t="shared" si="3"/>
-        <v>13588.946471897867</v>
+        <v>12126.984053946604</v>
       </c>
       <c r="BR6" s="3">
         <f t="shared" si="3"/>
-        <v>13724.835936616846</v>
+        <v>12248.25389448607</v>
       </c>
       <c r="BS6" s="3">
         <f t="shared" si="3"/>
-        <v>13862.084295983015</v>
+        <v>12370.736433430931</v>
       </c>
       <c r="BT6" s="3">
         <f t="shared" si="3"/>
-        <v>14000.705138942845</v>
+        <v>12494.443797765241</v>
       </c>
       <c r="BU6" s="3">
         <f t="shared" si="3"/>
-        <v>14140.712190332273</v>
+        <v>12619.388235742894</v>
       </c>
       <c r="BV6" s="3">
         <f t="shared" si="3"/>
-        <v>14282.119312235596</v>
+        <v>12745.582118100323</v>
       </c>
       <c r="BW6" s="3">
         <f t="shared" si="3"/>
-        <v>14424.940505357952</v>
+        <v>12873.037939281327</v>
       </c>
       <c r="BX6" s="3">
         <f t="shared" si="3"/>
-        <v>14569.189910411531</v>
+        <v>13001.76831867414</v>
       </c>
       <c r="BY6" s="3">
         <f t="shared" si="3"/>
-        <v>14714.881809515646</v>
+        <v>13131.786001860881</v>
       </c>
       <c r="BZ6" s="3">
         <f t="shared" si="3"/>
-        <v>14862.030627610802</v>
+        <v>13263.10386187949</v>
       </c>
       <c r="CA6" s="3">
         <f t="shared" si="3"/>
-        <v>15010.650933886911</v>
+        <v>13395.734900498284</v>
       </c>
       <c r="CB6" s="3">
         <f t="shared" si="3"/>
-        <v>15160.757443225781</v>
+        <v>13529.692249503267</v>
       </c>
       <c r="CC6" s="3">
         <f t="shared" si="3"/>
-        <v>15312.36501765804</v>
+        <v>13664.989171998299</v>
       </c>
       <c r="CD6" s="3">
         <f t="shared" si="3"/>
-        <v>15465.488667834619</v>
+        <v>13801.639063718281</v>
       </c>
       <c r="CE6" s="3">
         <f t="shared" si="3"/>
-        <v>15620.143554512966</v>
+        <v>13939.655454355465</v>
       </c>
       <c r="CF6" s="3">
         <f t="shared" si="3"/>
-        <v>15776.344990058096</v>
+        <v>14079.05200889902</v>
       </c>
       <c r="CG6" s="3">
         <f t="shared" si="3"/>
-        <v>15934.108439958678</v>
+        <v>14219.842528988011</v>
       </c>
       <c r="CH6" s="3">
         <f t="shared" si="3"/>
-        <v>16093.449524358264</v>
+        <v>14362.040954277891</v>
       </c>
       <c r="CI6" s="3">
         <f t="shared" si="3"/>
-        <v>16254.384019601846</v>
+        <v>14505.661363820669</v>
       </c>
       <c r="CJ6" s="3">
         <f t="shared" si="3"/>
-        <v>16416.927859797866</v>
+        <v>14650.717977458877</v>
       </c>
       <c r="CK6" s="3">
         <f t="shared" si="3"/>
-        <v>16581.097138395846</v>
+        <v>14797.225157233466</v>
       </c>
       <c r="CL6" s="3">
         <f t="shared" si="3"/>
-        <v>16746.908109779804</v>
+        <v>14945.197408805801</v>
       </c>
       <c r="CM6" s="3">
         <f t="shared" si="3"/>
-        <v>16914.377190877603</v>
+        <v>15094.64938289386</v>
       </c>
       <c r="CN6" s="3">
         <f t="shared" si="3"/>
-        <v>17083.520962786381</v>
+        <v>15245.595876722798</v>
       </c>
       <c r="CO6" s="3">
         <f t="shared" si="3"/>
-        <v>17254.356172414246</v>
+        <v>15398.051835490027</v>
       </c>
       <c r="CP6" s="3">
         <f t="shared" si="3"/>
-        <v>17426.899734138387</v>
+        <v>15552.032353844927</v>
       </c>
       <c r="CQ6" s="3">
         <f t="shared" si="3"/>
-        <v>17601.168731479771</v>
+        <v>15707.552677383375</v>
       </c>
       <c r="CR6" s="3">
         <f t="shared" si="3"/>
-        <v>17777.180418794567</v>
+        <v>15864.628204157209</v>
       </c>
       <c r="CS6" s="3">
         <f t="shared" si="3"/>
-        <v>17954.952222982512</v>
+        <v>16023.274486198781</v>
       </c>
       <c r="CT6" s="3">
         <f t="shared" si="3"/>
-        <v>18134.501745212339</v>
+        <v>16183.507231060768</v>
       </c>
       <c r="CU6" s="3">
         <f t="shared" ref="CU6:DC6" si="4">CT6*(1+$V$24)</f>
-        <v>18315.846762664463</v>
+        <v>16345.342303371377</v>
       </c>
       <c r="CV6" s="3">
         <f t="shared" si="4"/>
-        <v>18499.00523029111</v>
+        <v>16508.795726405089</v>
       </c>
       <c r="CW6" s="3">
         <f t="shared" si="4"/>
-        <v>18683.99528259402</v>
+        <v>16673.883683669141</v>
       </c>
       <c r="CX6" s="3">
         <f t="shared" si="4"/>
-        <v>18870.83523541996</v>
+        <v>16840.622520505833</v>
       </c>
       <c r="CY6" s="3">
         <f t="shared" si="4"/>
-        <v>19059.543587774158</v>
+        <v>17009.02874571089</v>
       </c>
       <c r="CZ6" s="3">
         <f t="shared" si="4"/>
-        <v>19250.1390236519</v>
+        <v>17179.119033167997</v>
       </c>
       <c r="DA6" s="3">
         <f t="shared" si="4"/>
-        <v>19442.640413888421</v>
+        <v>17350.910223499679</v>
       </c>
       <c r="DB6" s="3">
         <f t="shared" si="4"/>
-        <v>19637.066818027306</v>
+        <v>17524.419325734674</v>
       </c>
       <c r="DC6" s="3">
         <f t="shared" si="4"/>
-        <v>19833.437486207578</v>
+        <v>17699.66351899202</v>
       </c>
     </row>
     <row r="7" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1554,6 +1568,9 @@
       <c r="R7" s="5">
         <v>104.82899999999999</v>
       </c>
+      <c r="S7" s="5">
+        <v>110.098</v>
+      </c>
       <c r="V7" s="3">
         <v>362.78</v>
       </c>
@@ -1572,328 +1589,328 @@
         <v>2128.5389999999998</v>
       </c>
       <c r="AA7" s="3">
-        <f>(2555+2575)/2</f>
-        <v>2565</v>
+        <f>(2590+2610)/2</f>
+        <v>2600</v>
       </c>
       <c r="AB7" s="3">
         <f t="shared" ref="AB7:AG7" si="5">AA7*(1+$X$23)</f>
-        <v>3334.5</v>
+        <v>3380</v>
       </c>
       <c r="AC7" s="3">
         <f t="shared" si="5"/>
-        <v>4334.8500000000004</v>
+        <v>4394</v>
       </c>
       <c r="AD7" s="3">
         <f t="shared" si="5"/>
-        <v>5635.3050000000003</v>
+        <v>5712.2</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="5"/>
-        <v>7325.8965000000007</v>
+        <v>7425.86</v>
       </c>
       <c r="AF7" s="3">
         <f t="shared" si="5"/>
-        <v>9523.6654500000004</v>
+        <v>9653.6180000000004</v>
       </c>
       <c r="AG7" s="3">
         <f t="shared" si="5"/>
-        <v>12380.765085000001</v>
+        <v>12549.7034</v>
       </c>
       <c r="AH7" s="3">
         <f>AG7*(1+$V$24)</f>
-        <v>12504.572735850001</v>
+        <v>12675.200434</v>
       </c>
       <c r="AI7" s="3">
         <f>AH7*(1+$V$24)</f>
-        <v>12629.618463208501</v>
+        <v>12801.95243834</v>
       </c>
       <c r="AJ7" s="3">
         <f t="shared" ref="AJ7:CU7" si="6">AI7*(1+$V$24)</f>
-        <v>12755.914647840586</v>
+        <v>12929.971962723401</v>
       </c>
       <c r="AK7" s="3">
         <f t="shared" si="6"/>
-        <v>12883.473794318992</v>
+        <v>13059.271682350634</v>
       </c>
       <c r="AL7" s="3">
         <f t="shared" si="6"/>
-        <v>13012.308532262183</v>
+        <v>13189.864399174141</v>
       </c>
       <c r="AM7" s="3">
         <f t="shared" si="6"/>
-        <v>13142.431617584805</v>
+        <v>13321.763043165882</v>
       </c>
       <c r="AN7" s="3">
         <f t="shared" si="6"/>
-        <v>13273.855933760653</v>
+        <v>13454.98067359754</v>
       </c>
       <c r="AO7" s="3">
         <f t="shared" si="6"/>
-        <v>13406.594493098261</v>
+        <v>13589.530480333515</v>
       </c>
       <c r="AP7" s="3">
         <f t="shared" si="6"/>
-        <v>13540.660438029243</v>
+        <v>13725.425785136849</v>
       </c>
       <c r="AQ7" s="3">
         <f t="shared" si="6"/>
-        <v>13676.067042409535</v>
+        <v>13862.680042988219</v>
       </c>
       <c r="AR7" s="3">
         <f t="shared" si="6"/>
-        <v>13812.82771283363</v>
+        <v>14001.3068434181</v>
       </c>
       <c r="AS7" s="3">
         <f t="shared" si="6"/>
-        <v>13950.955989961967</v>
+        <v>14141.319911852281</v>
       </c>
       <c r="AT7" s="3">
         <f t="shared" si="6"/>
-        <v>14090.465549861587</v>
+        <v>14282.733110970803</v>
       </c>
       <c r="AU7" s="3">
         <f t="shared" si="6"/>
-        <v>14231.370205360203</v>
+        <v>14425.56044208051</v>
       </c>
       <c r="AV7" s="3">
         <f t="shared" si="6"/>
-        <v>14373.683907413804</v>
+        <v>14569.816046501315</v>
       </c>
       <c r="AW7" s="3">
         <f t="shared" si="6"/>
-        <v>14517.420746487942</v>
+        <v>14715.514206966329</v>
       </c>
       <c r="AX7" s="3">
         <f t="shared" si="6"/>
-        <v>14662.594953952821</v>
+        <v>14862.669349035992</v>
       </c>
       <c r="AY7" s="3">
         <f t="shared" si="6"/>
-        <v>14809.220903492349</v>
+        <v>15011.296042526352</v>
       </c>
       <c r="AZ7" s="3">
         <f t="shared" si="6"/>
-        <v>14957.313112527272</v>
+        <v>15161.409002951616</v>
       </c>
       <c r="BA7" s="3">
         <f t="shared" si="6"/>
-        <v>15106.886243652545</v>
+        <v>15313.023092981131</v>
       </c>
       <c r="BB7" s="3">
         <f t="shared" si="6"/>
-        <v>15257.95510608907</v>
+        <v>15466.153323910943</v>
       </c>
       <c r="BC7" s="3">
         <f t="shared" si="6"/>
-        <v>15410.534657149961</v>
+        <v>15620.814857150053</v>
       </c>
       <c r="BD7" s="3">
         <f t="shared" si="6"/>
-        <v>15564.640003721461</v>
+        <v>15777.023005721554</v>
       </c>
       <c r="BE7" s="3">
         <f t="shared" si="6"/>
-        <v>15720.286403758675</v>
+        <v>15934.79323577877</v>
       </c>
       <c r="BF7" s="3">
         <f t="shared" si="6"/>
-        <v>15877.489267796262</v>
+        <v>16094.141168136559</v>
       </c>
       <c r="BG7" s="3">
         <f t="shared" si="6"/>
-        <v>16036.264160474224</v>
+        <v>16255.082579817925</v>
       </c>
       <c r="BH7" s="3">
         <f t="shared" si="6"/>
-        <v>16196.626802078967</v>
+        <v>16417.633405616103</v>
       </c>
       <c r="BI7" s="3">
         <f t="shared" si="6"/>
-        <v>16358.593070099756</v>
+        <v>16581.809739672266</v>
       </c>
       <c r="BJ7" s="3">
         <f t="shared" si="6"/>
-        <v>16522.179000800752</v>
+        <v>16747.627837068991</v>
       </c>
       <c r="BK7" s="3">
         <f t="shared" si="6"/>
-        <v>16687.400790808759</v>
+        <v>16915.104115439681</v>
       </c>
       <c r="BL7" s="3">
         <f t="shared" si="6"/>
-        <v>16854.274798716848</v>
+        <v>17084.255156594078</v>
       </c>
       <c r="BM7" s="3">
         <f t="shared" si="6"/>
-        <v>17022.817546704016</v>
+        <v>17255.097708160018</v>
       </c>
       <c r="BN7" s="3">
         <f t="shared" si="6"/>
-        <v>17193.045722171057</v>
+        <v>17427.648685241616</v>
       </c>
       <c r="BO7" s="3">
         <f t="shared" si="6"/>
-        <v>17364.976179392768</v>
+        <v>17601.925172094034</v>
       </c>
       <c r="BP7" s="3">
         <f t="shared" si="6"/>
-        <v>17538.625941186696</v>
+        <v>17777.944423814974</v>
       </c>
       <c r="BQ7" s="3">
         <f t="shared" si="6"/>
-        <v>17714.012200598561</v>
+        <v>17955.723868053123</v>
       </c>
       <c r="BR7" s="3">
         <f t="shared" si="6"/>
-        <v>17891.152322604546</v>
+        <v>18135.281106733655</v>
       </c>
       <c r="BS7" s="3">
         <f t="shared" si="6"/>
-        <v>18070.063845830591</v>
+        <v>18316.633917800991</v>
       </c>
       <c r="BT7" s="3">
         <f t="shared" si="6"/>
-        <v>18250.764484288899</v>
+        <v>18499.800256979001</v>
       </c>
       <c r="BU7" s="3">
         <f t="shared" si="6"/>
-        <v>18433.272129131787</v>
+        <v>18684.798259548792</v>
       </c>
       <c r="BV7" s="3">
         <f t="shared" si="6"/>
-        <v>18617.604850423104</v>
+        <v>18871.646242144281</v>
       </c>
       <c r="BW7" s="3">
         <f t="shared" si="6"/>
-        <v>18803.780898927336</v>
+        <v>19060.362704565723</v>
       </c>
       <c r="BX7" s="3">
         <f t="shared" si="6"/>
-        <v>18991.818707916609</v>
+        <v>19250.96633161138</v>
       </c>
       <c r="BY7" s="3">
         <f t="shared" si="6"/>
-        <v>19181.736894995774</v>
+        <v>19443.475994927496</v>
       </c>
       <c r="BZ7" s="3">
         <f t="shared" si="6"/>
-        <v>19373.554263945731</v>
+        <v>19637.910754876772</v>
       </c>
       <c r="CA7" s="3">
         <f t="shared" si="6"/>
-        <v>19567.289806585188</v>
+        <v>19834.289862425539</v>
       </c>
       <c r="CB7" s="3">
         <f t="shared" si="6"/>
-        <v>19762.96270465104</v>
+        <v>20032.632761049794</v>
       </c>
       <c r="CC7" s="3">
         <f t="shared" si="6"/>
-        <v>19960.59233169755</v>
+        <v>20232.959088660293</v>
       </c>
       <c r="CD7" s="3">
         <f t="shared" si="6"/>
-        <v>20160.198255014526</v>
+        <v>20435.288679546895</v>
       </c>
       <c r="CE7" s="3">
         <f t="shared" si="6"/>
-        <v>20361.800237564672</v>
+        <v>20639.641566342365</v>
       </c>
       <c r="CF7" s="3">
         <f t="shared" si="6"/>
-        <v>20565.418239940318</v>
+        <v>20846.03798200579</v>
       </c>
       <c r="CG7" s="3">
         <f t="shared" si="6"/>
-        <v>20771.072422339723</v>
+        <v>21054.498361825848</v>
       </c>
       <c r="CH7" s="3">
         <f t="shared" si="6"/>
-        <v>20978.783146563121</v>
+        <v>21265.043345444108</v>
       </c>
       <c r="CI7" s="3">
         <f t="shared" si="6"/>
-        <v>21188.570978028751</v>
+        <v>21477.693778898549</v>
       </c>
       <c r="CJ7" s="3">
         <f t="shared" si="6"/>
-        <v>21400.456687809037</v>
+        <v>21692.470716687534</v>
       </c>
       <c r="CK7" s="3">
         <f t="shared" si="6"/>
-        <v>21614.461254687129</v>
+        <v>21909.39542385441</v>
       </c>
       <c r="CL7" s="3">
         <f t="shared" si="6"/>
-        <v>21830.605867234</v>
+        <v>22128.489378092956</v>
       </c>
       <c r="CM7" s="3">
         <f t="shared" si="6"/>
-        <v>22048.911925906341</v>
+        <v>22349.774271873885</v>
       </c>
       <c r="CN7" s="3">
         <f t="shared" si="6"/>
-        <v>22269.401045165403</v>
+        <v>22573.272014592625</v>
       </c>
       <c r="CO7" s="3">
         <f t="shared" si="6"/>
-        <v>22492.095055617057</v>
+        <v>22799.004734738552</v>
       </c>
       <c r="CP7" s="3">
         <f t="shared" si="6"/>
-        <v>22717.016006173228</v>
+        <v>23026.994782085938</v>
       </c>
       <c r="CQ7" s="3">
         <f t="shared" si="6"/>
-        <v>22944.186166234958</v>
+        <v>23257.264729906798</v>
       </c>
       <c r="CR7" s="3">
         <f t="shared" si="6"/>
-        <v>23173.62802789731</v>
+        <v>23489.837377205866</v>
       </c>
       <c r="CS7" s="3">
         <f t="shared" si="6"/>
-        <v>23405.364308176282</v>
+        <v>23724.735750977925</v>
       </c>
       <c r="CT7" s="3">
         <f t="shared" si="6"/>
-        <v>23639.417951258045</v>
+        <v>23961.983108487704</v>
       </c>
       <c r="CU7" s="3">
         <f t="shared" si="6"/>
-        <v>23875.812130770624</v>
+        <v>24201.602939572582</v>
       </c>
       <c r="CV7" s="3">
         <f t="shared" ref="CV7:DC7" si="7">CU7*(1+$V$24)</f>
-        <v>24114.570252078331</v>
+        <v>24443.618968968309</v>
       </c>
       <c r="CW7" s="3">
         <f t="shared" si="7"/>
-        <v>24355.715954599113</v>
+        <v>24688.055158657993</v>
       </c>
       <c r="CX7" s="3">
         <f t="shared" si="7"/>
-        <v>24599.273114145104</v>
+        <v>24934.935710244572</v>
       </c>
       <c r="CY7" s="3">
         <f t="shared" si="7"/>
-        <v>24845.265845286554</v>
+        <v>25184.285067347017</v>
       </c>
       <c r="CZ7" s="3">
         <f t="shared" si="7"/>
-        <v>25093.718503739419</v>
+        <v>25436.127918020487</v>
       </c>
       <c r="DA7" s="3">
         <f t="shared" si="7"/>
-        <v>25344.655688776813</v>
+        <v>25690.489197200692</v>
       </c>
       <c r="DB7" s="3">
         <f t="shared" si="7"/>
-        <v>25598.102245664581</v>
+        <v>25947.3940891727</v>
       </c>
       <c r="DC7" s="3">
         <f t="shared" si="7"/>
-        <v>25854.083268121227</v>
+        <v>26206.868030064426</v>
       </c>
     </row>
     <row r="8" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1903,7 +1920,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:R8" si="8">+E6-E7</f>
+        <f t="shared" ref="E8:S8" si="8">+E6-E7</f>
         <v>120.691</v>
       </c>
       <c r="F8" s="6">
@@ -1958,13 +1975,17 @@
         <f t="shared" si="8"/>
         <v>484.82</v>
       </c>
+      <c r="S8" s="6">
+        <f t="shared" si="8"/>
+        <v>500.90199999999999</v>
+      </c>
       <c r="Z8" s="24">
         <f t="shared" ref="Z8:AH8" si="9">(Z7-Y7)/Y7</f>
         <v>0.27069368992895937</v>
       </c>
       <c r="AA8" s="22">
         <f t="shared" si="9"/>
-        <v>0.20505191589160465</v>
+        <v>0.22149511942228933</v>
       </c>
       <c r="AB8" s="22">
         <f t="shared" si="9"/>
@@ -1972,7 +1993,7 @@
       </c>
       <c r="AC8" s="22">
         <f t="shared" si="9"/>
-        <v>0.3000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="AD8" s="22">
         <f t="shared" si="9"/>
@@ -1980,19 +2001,19 @@
       </c>
       <c r="AE8" s="22">
         <f t="shared" si="9"/>
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="AF8" s="22">
         <f t="shared" si="9"/>
-        <v>0.29999999999999993</v>
+        <v>0.3000000000000001</v>
       </c>
       <c r="AG8" s="22">
         <f t="shared" si="9"/>
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="AH8" s="22">
         <f t="shared" si="9"/>
-        <v>9.9999999999999863E-3</v>
+        <v>9.9999999999999985E-3</v>
       </c>
     </row>
     <row r="9" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2043,6 +2064,9 @@
       <c r="R9" s="5">
         <v>253.25</v>
       </c>
+      <c r="S9" s="5">
+        <v>269.988</v>
+      </c>
     </row>
     <row r="10" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
@@ -2092,6 +2116,9 @@
       <c r="R10" s="5">
         <v>159.97999999999999</v>
       </c>
+      <c r="S10" s="5">
+        <v>173.881</v>
+      </c>
     </row>
     <row r="11" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
@@ -2141,6 +2168,9 @@
       <c r="R11" s="5">
         <v>43.847999999999999</v>
       </c>
+      <c r="S11" s="5">
+        <v>45.29</v>
+      </c>
     </row>
     <row r="12" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
@@ -2149,7 +2179,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f t="shared" ref="E12:R12" si="10">SUM(E9:E11)</f>
+        <f t="shared" ref="E12:S12" si="10">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
@@ -2204,6 +2234,10 @@
         <f t="shared" si="10"/>
         <v>457.07800000000003</v>
       </c>
+      <c r="S12" s="6">
+        <f t="shared" si="10"/>
+        <v>489.15900000000005</v>
+      </c>
     </row>
     <row r="13" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
@@ -2212,7 +2246,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f t="shared" ref="E13:R13" si="11">E8-E12</f>
+        <f t="shared" ref="E13:S13" si="11">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
@@ -2266,6 +2300,10 @@
       <c r="R13" s="6">
         <f t="shared" si="11"/>
         <v>27.741999999999962</v>
+      </c>
+      <c r="S13" s="6">
+        <f t="shared" si="11"/>
+        <v>11.742999999999938</v>
       </c>
     </row>
     <row r="14" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2327,6 +2365,10 @@
         <f>-1.292+30.817</f>
         <v>29.524999999999999</v>
       </c>
+      <c r="S14" s="5">
+        <f>-1.374+35.563</f>
+        <v>34.189</v>
+      </c>
     </row>
     <row r="15" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
@@ -2335,7 +2377,7 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f t="shared" ref="E15:R15" si="12">+E13+E14</f>
+        <f t="shared" ref="E15:S15" si="12">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
@@ -2389,6 +2431,10 @@
       <c r="R15" s="6">
         <f t="shared" si="12"/>
         <v>57.26699999999996</v>
+      </c>
+      <c r="S15" s="6">
+        <f t="shared" si="12"/>
+        <v>45.931999999999938</v>
       </c>
     </row>
     <row r="16" spans="1:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2439,6 +2485,10 @@
       <c r="R16" s="5">
         <v>3.274</v>
       </c>
+      <c r="S16" s="5">
+        <f>3.554</f>
+        <v>3.5539999999999998</v>
+      </c>
     </row>
     <row r="17" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
@@ -2447,7 +2497,7 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:R17" si="13">+E15-E16</f>
+        <f t="shared" ref="E17:S17" si="13">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
@@ -2502,6 +2552,10 @@
         <f t="shared" si="13"/>
         <v>53.992999999999959</v>
       </c>
+      <c r="S17" s="6">
+        <f t="shared" si="13"/>
+        <v>42.377999999999936</v>
+      </c>
     </row>
     <row r="18" spans="2:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
@@ -2510,7 +2564,7 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:R18" si="14">+E17/E19</f>
+        <f t="shared" ref="E18:S18" si="14">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
@@ -2564,6 +2618,10 @@
       <c r="R18" s="7">
         <f t="shared" si="14"/>
         <v>0.16416485504492304</v>
+      </c>
+      <c r="S18" s="7">
+        <f t="shared" si="14"/>
+        <v>0.12771920941755102</v>
       </c>
     </row>
     <row r="19" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2613,6 +2671,9 @@
       </c>
       <c r="R19" s="5">
         <v>328.89499999999998</v>
+      </c>
+      <c r="S19" s="5">
+        <v>331.80599999999998</v>
       </c>
     </row>
     <row r="21" spans="2:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -2667,7 +2728,7 @@
       </c>
       <c r="S21" s="10">
         <f t="shared" si="16"/>
-        <v>0.22271721394852539</v>
+        <v>0.26838746642198474</v>
       </c>
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.2">
@@ -2707,7 +2768,7 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:R22" si="19">+M8/M6</f>
+        <f t="shared" ref="M22:S22" si="19">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
@@ -2730,6 +2791,10 @@
         <f t="shared" si="19"/>
         <v>0.82221796356815668</v>
       </c>
+      <c r="S22" s="12">
+        <f t="shared" si="19"/>
+        <v>0.81980687397708674</v>
+      </c>
       <c r="U22" t="s">
         <v>71</v>
       </c>
@@ -2745,7 +2810,7 @@
         <v>62</v>
       </c>
       <c r="V23" s="23">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="W23" s="15" t="s">
         <v>62</v>
@@ -2837,14 +2902,14 @@
       </c>
       <c r="V26" s="18">
         <f>NPV(V25,V6:DC6)</f>
-        <v>53169.98322190965</v>
+        <v>48462.55326232707</v>
       </c>
       <c r="W26" s="17" t="s">
         <v>63</v>
       </c>
       <c r="X26" s="26">
         <f>NPV($V$25,V7:DC7)</f>
-        <v>65936.250330536161</v>
+        <v>66780.466791614104</v>
       </c>
     </row>
     <row r="27" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2872,14 +2937,14 @@
       </c>
       <c r="V27" s="21">
         <f>Main!$O$3</f>
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="W27" s="17" t="s">
         <v>1</v>
       </c>
       <c r="X27" s="21">
         <f>Main!$O$3</f>
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2907,14 +2972,14 @@
       </c>
       <c r="V28" s="19">
         <f>V26/V27</f>
-        <v>162.10360738387089</v>
+        <v>145.97154597086467</v>
       </c>
       <c r="W28" s="17" t="s">
         <v>64</v>
       </c>
       <c r="X28" s="19">
         <f>X26/X27</f>
-        <v>201.02515344675658</v>
+        <v>201.14598431209069</v>
       </c>
     </row>
     <row r="29" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2942,14 +3007,14 @@
       </c>
       <c r="V29" s="20">
         <f>(V28-Main!$O$2)/Main!$O$2</f>
-        <v>0.24944972548073749</v>
+        <v>0.24464142198895519</v>
       </c>
       <c r="W29" s="17" t="s">
         <v>65</v>
       </c>
       <c r="X29" s="20">
         <f>(X28-Main!$O$2)/Main!$O$2</f>
-        <v>0.549446226659138</v>
+        <v>0.71509195354784005</v>
       </c>
     </row>
     <row r="30" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2979,14 +3044,14 @@
       </c>
       <c r="V30" s="18">
         <f>V27*V28</f>
-        <v>53169.983221909657</v>
+        <v>48462.55326232707</v>
       </c>
       <c r="W30" s="17" t="s">
         <v>66</v>
       </c>
       <c r="X30" s="18">
         <f>X27*X28</f>
-        <v>65936.250330536161</v>
+        <v>66780.466791614104</v>
       </c>
     </row>
     <row r="31" spans="2:24" s="5" customFormat="1" x14ac:dyDescent="0.2">

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5FCB14-0CC5-4079-9D6A-CBF13E30A9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4E1926-EF23-49B7-8B2F-F568FE2EDE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29895" yWindow="4995" windowWidth="29715" windowHeight="15315" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>Price</t>
   </si>
@@ -284,13 +284,34 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>Terminal Rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Share Price</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -308,6 +329,12 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -329,11 +356,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -361,10 +390,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -764,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>102.27</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -772,8 +806,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <f>311.11036+26.041915</f>
-        <v>337.15227500000003</v>
+        <v>363</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>63</v>
@@ -785,7 +818,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>34480.563164250001</v>
+        <v>56319.450000000004</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -816,7 +849,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>33510.563164250001</v>
+        <v>55349.450000000004</v>
       </c>
     </row>
   </sheetData>
@@ -826,20 +859,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
-  <dimension ref="A1:AH54"/>
+  <dimension ref="A1:DC54"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="27" width="9.140625" style="2"/>
+    <col min="3" max="26" width="9.140625" style="2"/>
+    <col min="27" max="27" width="14.42578125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -931,8 +966,30 @@
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI2">
+        <v>2025</v>
+      </c>
+      <c r="AJ2">
+        <f>+AI2+1</f>
+        <v>2026</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" ref="AK2" si="1">+AJ2+1</f>
+        <v>2027</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" ref="AL2" si="2">+AK2+1</f>
+        <v>2028</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" ref="AM2" si="3">+AL2+1</f>
+        <v>2029</v>
+      </c>
+      <c r="AN2">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -949,7 +1006,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="6" spans="1:34" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1013,7 +1070,8 @@
         <v>761.553</v>
       </c>
       <c r="X6" s="4">
-        <v>790</v>
+        <f>(787+791)/2</f>
+        <v>789</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
@@ -1023,7 +1081,7 @@
         <v>1675.1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1088,80 +1146,80 @@
       </c>
       <c r="X7" s="6">
         <f>+X6-X8</f>
-        <v>158</v>
+        <v>157.79999999999995</v>
       </c>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
     </row>
-    <row r="8" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6">
-        <f t="shared" ref="E8:L8" si="1">+E6-E7</f>
+        <f t="shared" ref="E8:L8" si="4">+E6-E7</f>
         <v>120.691</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>136.67500000000001</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>151.88300000000001</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>176.45100000000002</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>207.15600000000001</v>
       </c>
       <c r="J8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>259.04899999999998</v>
       </c>
       <c r="K8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>288.56799999999998</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>324.21299999999997</v>
       </c>
       <c r="M8" s="6">
-        <f t="shared" ref="M8:T8" si="2">+M6-M7</f>
+        <f t="shared" ref="M8:T8" si="5">+M6-M7</f>
         <v>342.93400000000003</v>
       </c>
       <c r="N8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>372.642</v>
       </c>
       <c r="O8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>381.8</v>
       </c>
       <c r="P8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>407.61399999999998</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>444.21699999999993</v>
       </c>
       <c r="R8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>484.82</v>
       </c>
       <c r="S8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>501.15500000000003</v>
       </c>
       <c r="T8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>521.78</v>
       </c>
       <c r="U8" s="6">
@@ -1178,13 +1236,13 @@
       </c>
       <c r="X8" s="6">
         <f>+X6*0.8</f>
-        <v>632</v>
+        <v>631.20000000000005</v>
       </c>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
     </row>
-    <row r="9" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
@@ -1248,14 +1306,14 @@
         <v>341.06099999999998</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:X10" si="3">+W9+1</f>
+        <f t="shared" ref="X9:X10" si="6">+W9+1</f>
         <v>342.06099999999998</v>
       </c>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
     </row>
-    <row r="10" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
@@ -1319,14 +1377,14 @@
         <v>214.291</v>
       </c>
       <c r="X10" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>215.291</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
       <c r="AA10" s="6"/>
     </row>
-    <row r="11" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1397,187 +1455,187 @@
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
     </row>
-    <row r="12" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f t="shared" ref="E12:L12" si="4">SUM(E9:E11)</f>
+        <f t="shared" ref="E12:L12" si="7">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>145.613</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>164.71299999999999</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>186.33699999999999</v>
       </c>
       <c r="I12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>212.05100000000002</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>250.59399999999999</v>
       </c>
       <c r="K12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>278.154</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>327.35199999999998</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" ref="M12:U12" si="5">+M11+M10+M9</f>
+        <f t="shared" ref="M12:U12" si="8">+M11+M10+M9</f>
         <v>374.27600000000001</v>
       </c>
       <c r="N12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>407.27</v>
       </c>
       <c r="O12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>416.77</v>
       </c>
       <c r="P12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>429.62</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>448.447</v>
       </c>
       <c r="R12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>457.07799999999997</v>
       </c>
       <c r="S12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>489.15899999999999</v>
       </c>
       <c r="T12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>509.16199999999998</v>
       </c>
       <c r="U12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>531.98199999999997</v>
       </c>
       <c r="V12" s="6">
-        <f t="shared" ref="V12:W12" si="6">+V11+V10+V9</f>
+        <f t="shared" ref="V12:W12" si="9">+V11+V10+V9</f>
         <v>584.15700000000004</v>
       </c>
       <c r="W12" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>616.34500000000003</v>
       </c>
       <c r="X12" s="6">
-        <f t="shared" ref="X12" si="7">+X11+X10+X9</f>
+        <f t="shared" ref="X12" si="10">+X11+X10+X9</f>
         <v>619.34500000000003</v>
       </c>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
     </row>
-    <row r="13" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f t="shared" ref="E13:L13" si="8">E8-E12</f>
+        <f t="shared" ref="E13:L13" si="11">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-8.9379999999999882</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-12.829999999999984</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-9.8859999999999673</v>
       </c>
       <c r="I13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-4.8950000000000102</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>8.4549999999999841</v>
       </c>
       <c r="K13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>10.413999999999987</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-3.13900000000001</v>
       </c>
       <c r="M13" s="6">
-        <f t="shared" ref="M13:U13" si="9">+M8-M12</f>
+        <f t="shared" ref="M13:U13" si="12">+M8-M12</f>
         <v>-31.341999999999985</v>
       </c>
       <c r="N13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-34.627999999999986</v>
       </c>
       <c r="O13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-34.96999999999997</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-22.006000000000029</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-4.230000000000075</v>
       </c>
       <c r="R13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>27.742000000000019</v>
       </c>
       <c r="S13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>11.996000000000038</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>12.617999999999995</v>
       </c>
       <c r="U13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20.27800000000002</v>
       </c>
       <c r="V13" s="6">
-        <f t="shared" ref="V13:W13" si="10">+V8-V12</f>
+        <f t="shared" ref="V13:W13" si="13">+V8-V12</f>
         <v>9.3919999999999391</v>
       </c>
       <c r="W13" s="6">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-12.420000000000073</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" ref="X13" si="11">+X8-X12</f>
-        <v>12.654999999999973</v>
+        <f t="shared" ref="X13" si="14">+X8-X12</f>
+        <v>11.855000000000018</v>
       </c>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
     </row>
-    <row r="14" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
@@ -1661,97 +1719,97 @@
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
     </row>
-    <row r="15" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f t="shared" ref="E15:L15" si="12">+E13+E14</f>
+        <f t="shared" ref="E15:L15" si="15">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-15.166999999999987</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-12.528999999999986</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-9.6579999999999675</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-4.7670000000000101</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>8.531999999999984</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>10.853999999999989</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-1.1000000000010779E-2</v>
       </c>
       <c r="M15" s="6">
-        <f t="shared" ref="M15:U15" si="13">+M13+M14</f>
+        <f t="shared" ref="M15:U15" si="16">+M13+M14</f>
         <v>-23.058999999999983</v>
       </c>
       <c r="N15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-25.853999999999985</v>
       </c>
       <c r="O15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-20.423999999999971</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-0.90800000000002967</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>24.299999999999923</v>
       </c>
       <c r="R15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>57.267000000000017</v>
       </c>
       <c r="S15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>46.185000000000038</v>
       </c>
       <c r="T15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>47.792999999999999</v>
       </c>
       <c r="U15" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>56.136000000000017</v>
       </c>
       <c r="V15" s="6">
-        <f t="shared" ref="V15:X15" si="14">+V13+V14</f>
+        <f t="shared" ref="V15:X15" si="17">+V13+V14</f>
         <v>53.825999999999937</v>
       </c>
       <c r="W15" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>31.795999999999928</v>
       </c>
       <c r="X15" s="6">
-        <f t="shared" si="14"/>
-        <v>56.870999999999974</v>
+        <f t="shared" si="17"/>
+        <v>56.071000000000019</v>
       </c>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
     </row>
-    <row r="16" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1816,193 +1874,193 @@
       </c>
       <c r="X16" s="6">
         <f>+X15*0.1</f>
-        <v>5.6870999999999974</v>
+        <v>5.6071000000000026</v>
       </c>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
     </row>
-    <row r="17" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:L17" si="15">+E15-E16</f>
+        <f t="shared" ref="E17:L17" si="18">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-16.159999999999986</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-11.989999999999986</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-6.6979999999999675</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-4.0500000000000105</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>7.1689999999999845</v>
       </c>
       <c r="K17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>9.7379999999999889</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-4.8790000000000111</v>
       </c>
       <c r="M17" s="6">
-        <f t="shared" ref="M17:U17" si="16">+M15-M16</f>
+        <f t="shared" ref="M17:U17" si="19">+M15-M16</f>
         <v>-25.984999999999985</v>
       </c>
       <c r="N17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-29.033999999999985</v>
       </c>
       <c r="O17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-24.08599999999997</v>
       </c>
       <c r="P17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>-3.9690000000000296</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>22.629999999999924</v>
       </c>
       <c r="R17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>53.993000000000016</v>
       </c>
       <c r="S17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>42.631000000000036</v>
       </c>
       <c r="T17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>43.823999999999998</v>
       </c>
       <c r="U17" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>51.697000000000017</v>
       </c>
       <c r="V17" s="6">
-        <f t="shared" ref="V17:X17" si="17">+V15-V16</f>
+        <f t="shared" ref="V17:X17" si="20">+V15-V16</f>
         <v>45.593999999999937</v>
       </c>
       <c r="W17" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>24.641999999999928</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="17"/>
-        <v>51.18389999999998</v>
+        <f t="shared" si="20"/>
+        <v>50.463900000000017</v>
       </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
     </row>
-    <row r="18" spans="2:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:107" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:L18" si="18">+E17/E19</f>
+        <f t="shared" ref="E18:L18" si="21">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-5.3147929500060795E-2</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-3.9178653352241861E-2</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-2.1745411809011676E-2</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-1.3054114947122809E-2</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2.0727021455604115E-2</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>2.8171540321927365E-2</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-1.5498975523753589E-2</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" ref="M18:U18" si="19">+M17/M19</f>
+        <f t="shared" ref="M18:U18" si="22">+M17/M19</f>
         <v>-8.223361498781602E-2</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>-9.1489468974122995E-2</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>-7.5437068960117162E-2</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>-1.2317862296913644E-2</v>
       </c>
       <c r="Q18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>6.4416226171262123E-2</v>
       </c>
       <c r="R18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.15299498168072614</v>
       </c>
       <c r="S18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.11975706432121007</v>
       </c>
       <c r="T18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.12284577002859225</v>
       </c>
       <c r="U18" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>0.14455240678345246</v>
       </c>
       <c r="V18" s="7">
-        <f t="shared" ref="V18:X18" si="20">+V17/V19</f>
+        <f t="shared" ref="V18:X18" si="23">+V17/V19</f>
         <v>0.12632016401617979</v>
       </c>
       <c r="W18" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>6.7869713945763521E-2</v>
       </c>
       <c r="X18" s="7">
-        <f t="shared" si="20"/>
-        <v>0.14097218779435819</v>
+        <f t="shared" si="23"/>
+        <v>0.13898914282881369</v>
       </c>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
       <c r="AA18" s="7"/>
     </row>
-    <row r="19" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -2073,7 +2131,7 @@
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
     </row>
-    <row r="21" spans="2:27" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:107" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
@@ -2084,47 +2142,47 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:K21" si="21">+I6/E6-1</f>
+        <f t="shared" ref="I21:K21" si="24">+I6/E6-1</f>
         <v>0.74875060610958455</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.83741431074009598</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.82841515192723181</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" ref="L21:S21" si="22">+L6/H6-1</f>
+        <f t="shared" ref="L21:S21" si="25">+L6/H6-1</f>
         <v>0.73898411040081502</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.61387196474520134</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.43900023911857233</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.32692614935404807</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.25440121338067367</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.25428318134024219</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.25617864545940661</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.26891267432542976</v>
       </c>
       <c r="T21" s="10">
@@ -2145,42 +2203,350 @@
       </c>
       <c r="X21" s="10">
         <f>+X6/T6-1</f>
-        <v>0.22427663072872361</v>
+        <v>0.22272691347463658</v>
       </c>
       <c r="Y21" s="10"/>
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3">
+        <f>SUM(G6:J6)</f>
+        <v>1028.7840000000001</v>
+      </c>
+      <c r="AF21" s="3">
+        <f>SUM(K6:N6)</f>
+        <v>1675.1</v>
+      </c>
+      <c r="AG21" s="3">
+        <f>SUM(O6:R6)</f>
+        <v>2128.3589999999999</v>
+      </c>
+      <c r="AH21" s="3">
+        <f>SUM(S6:V6)</f>
+        <v>2684.2750000000001</v>
+      </c>
+      <c r="AI21" s="3">
+        <f>AH21*(1+$AB$23)</f>
+        <v>3274.8155000000002</v>
+      </c>
+      <c r="AJ21" s="3">
+        <f t="shared" ref="AJ21:AN21" si="26">AI21*(1+$AB$23)</f>
+        <v>3995.2749100000001</v>
+      </c>
+      <c r="AK21" s="3">
+        <f t="shared" si="26"/>
+        <v>4874.2353902000004</v>
+      </c>
+      <c r="AL21" s="3">
+        <f t="shared" si="26"/>
+        <v>5946.567176044</v>
+      </c>
+      <c r="AM21" s="3">
+        <f t="shared" si="26"/>
+        <v>7254.8119547736796</v>
+      </c>
+      <c r="AN21" s="3">
+        <f t="shared" si="26"/>
+        <v>8850.8705848238897</v>
+      </c>
+      <c r="AO21" s="11">
+        <f>AN21*(1+$AB$24)</f>
+        <v>8939.3792906721283</v>
+      </c>
+      <c r="AP21" s="11">
+        <f t="shared" ref="AP21:DA21" si="27">AO21*(1+$AB$24)</f>
+        <v>9028.7730835788498</v>
+      </c>
+      <c r="AQ21" s="11">
+        <f t="shared" si="27"/>
+        <v>9119.060814414639</v>
+      </c>
+      <c r="AR21" s="11">
+        <f t="shared" si="27"/>
+        <v>9210.2514225587856</v>
+      </c>
+      <c r="AS21" s="11">
+        <f t="shared" si="27"/>
+        <v>9302.3539367843732</v>
+      </c>
+      <c r="AT21" s="11">
+        <f t="shared" si="27"/>
+        <v>9395.3774761522163</v>
+      </c>
+      <c r="AU21" s="11">
+        <f t="shared" si="27"/>
+        <v>9489.3312509137377</v>
+      </c>
+      <c r="AV21" s="11">
+        <f t="shared" si="27"/>
+        <v>9584.2245634228748</v>
+      </c>
+      <c r="AW21" s="11">
+        <f t="shared" si="27"/>
+        <v>9680.0668090571035</v>
+      </c>
+      <c r="AX21" s="11">
+        <f t="shared" si="27"/>
+        <v>9776.8674771476744</v>
+      </c>
+      <c r="AY21" s="11">
+        <f t="shared" si="27"/>
+        <v>9874.6361519191505</v>
+      </c>
+      <c r="AZ21" s="11">
+        <f t="shared" si="27"/>
+        <v>9973.3825134383424</v>
+      </c>
+      <c r="BA21" s="11">
+        <f t="shared" si="27"/>
+        <v>10073.116338572725</v>
+      </c>
+      <c r="BB21" s="11">
+        <f t="shared" si="27"/>
+        <v>10173.847501958453</v>
+      </c>
+      <c r="BC21" s="11">
+        <f t="shared" si="27"/>
+        <v>10275.585976978038</v>
+      </c>
+      <c r="BD21" s="11">
+        <f t="shared" si="27"/>
+        <v>10378.341836747819</v>
+      </c>
+      <c r="BE21" s="11">
+        <f t="shared" si="27"/>
+        <v>10482.125255115297</v>
+      </c>
+      <c r="BF21" s="11">
+        <f t="shared" si="27"/>
+        <v>10586.946507666451</v>
+      </c>
+      <c r="BG21" s="11">
+        <f t="shared" si="27"/>
+        <v>10692.815972743116</v>
+      </c>
+      <c r="BH21" s="11">
+        <f t="shared" si="27"/>
+        <v>10799.744132470547</v>
+      </c>
+      <c r="BI21" s="11">
+        <f t="shared" si="27"/>
+        <v>10907.741573795252</v>
+      </c>
+      <c r="BJ21" s="11">
+        <f t="shared" si="27"/>
+        <v>11016.818989533205</v>
+      </c>
+      <c r="BK21" s="11">
+        <f t="shared" si="27"/>
+        <v>11126.987179428537</v>
+      </c>
+      <c r="BL21" s="11">
+        <f t="shared" si="27"/>
+        <v>11238.257051222823</v>
+      </c>
+      <c r="BM21" s="11">
+        <f t="shared" si="27"/>
+        <v>11350.639621735052</v>
+      </c>
+      <c r="BN21" s="11">
+        <f t="shared" si="27"/>
+        <v>11464.146017952402</v>
+      </c>
+      <c r="BO21" s="11">
+        <f t="shared" si="27"/>
+        <v>11578.787478131926</v>
+      </c>
+      <c r="BP21" s="11">
+        <f t="shared" si="27"/>
+        <v>11694.575352913245</v>
+      </c>
+      <c r="BQ21" s="11">
+        <f t="shared" si="27"/>
+        <v>11811.521106442378</v>
+      </c>
+      <c r="BR21" s="11">
+        <f t="shared" si="27"/>
+        <v>11929.636317506802</v>
+      </c>
+      <c r="BS21" s="11">
+        <f t="shared" si="27"/>
+        <v>12048.93268068187</v>
+      </c>
+      <c r="BT21" s="11">
+        <f t="shared" si="27"/>
+        <v>12169.422007488689</v>
+      </c>
+      <c r="BU21" s="11">
+        <f t="shared" si="27"/>
+        <v>12291.116227563576</v>
+      </c>
+      <c r="BV21" s="11">
+        <f t="shared" si="27"/>
+        <v>12414.027389839212</v>
+      </c>
+      <c r="BW21" s="11">
+        <f t="shared" si="27"/>
+        <v>12538.167663737604</v>
+      </c>
+      <c r="BX21" s="11">
+        <f t="shared" si="27"/>
+        <v>12663.549340374981</v>
+      </c>
+      <c r="BY21" s="11">
+        <f t="shared" si="27"/>
+        <v>12790.184833778731</v>
+      </c>
+      <c r="BZ21" s="11">
+        <f t="shared" si="27"/>
+        <v>12918.086682116518</v>
+      </c>
+      <c r="CA21" s="11">
+        <f t="shared" si="27"/>
+        <v>13047.267548937683</v>
+      </c>
+      <c r="CB21" s="11">
+        <f t="shared" si="27"/>
+        <v>13177.74022442706</v>
+      </c>
+      <c r="CC21" s="11">
+        <f t="shared" si="27"/>
+        <v>13309.51762667133</v>
+      </c>
+      <c r="CD21" s="11">
+        <f t="shared" si="27"/>
+        <v>13442.612802938043</v>
+      </c>
+      <c r="CE21" s="11">
+        <f t="shared" si="27"/>
+        <v>13577.038930967425</v>
+      </c>
+      <c r="CF21" s="11">
+        <f t="shared" si="27"/>
+        <v>13712.8093202771</v>
+      </c>
+      <c r="CG21" s="11">
+        <f t="shared" si="27"/>
+        <v>13849.937413479871</v>
+      </c>
+      <c r="CH21" s="11">
+        <f t="shared" si="27"/>
+        <v>13988.43678761467</v>
+      </c>
+      <c r="CI21" s="11">
+        <f t="shared" si="27"/>
+        <v>14128.321155490816</v>
+      </c>
+      <c r="CJ21" s="11">
+        <f t="shared" si="27"/>
+        <v>14269.604367045724</v>
+      </c>
+      <c r="CK21" s="11">
+        <f t="shared" si="27"/>
+        <v>14412.300410716181</v>
+      </c>
+      <c r="CL21" s="11">
+        <f t="shared" si="27"/>
+        <v>14556.423414823343</v>
+      </c>
+      <c r="CM21" s="11">
+        <f t="shared" si="27"/>
+        <v>14701.987648971577</v>
+      </c>
+      <c r="CN21" s="11">
+        <f t="shared" si="27"/>
+        <v>14849.007525461293</v>
+      </c>
+      <c r="CO21" s="11">
+        <f t="shared" si="27"/>
+        <v>14997.497600715906</v>
+      </c>
+      <c r="CP21" s="11">
+        <f t="shared" si="27"/>
+        <v>15147.472576723065</v>
+      </c>
+      <c r="CQ21" s="11">
+        <f t="shared" si="27"/>
+        <v>15298.947302490296</v>
+      </c>
+      <c r="CR21" s="11">
+        <f t="shared" si="27"/>
+        <v>15451.9367755152</v>
+      </c>
+      <c r="CS21" s="11">
+        <f t="shared" si="27"/>
+        <v>15606.456143270352</v>
+      </c>
+      <c r="CT21" s="11">
+        <f t="shared" si="27"/>
+        <v>15762.520704703056</v>
+      </c>
+      <c r="CU21" s="11">
+        <f t="shared" si="27"/>
+        <v>15920.145911750087</v>
+      </c>
+      <c r="CV21" s="11">
+        <f t="shared" si="27"/>
+        <v>16079.347370867588</v>
+      </c>
+      <c r="CW21" s="11">
+        <f t="shared" si="27"/>
+        <v>16240.140844576264</v>
+      </c>
+      <c r="CX21" s="11">
+        <f t="shared" si="27"/>
+        <v>16402.542253022028</v>
+      </c>
+      <c r="CY21" s="11">
+        <f t="shared" si="27"/>
+        <v>16566.567675552247</v>
+      </c>
+      <c r="CZ21" s="11">
+        <f t="shared" si="27"/>
+        <v>16732.233352307769</v>
+      </c>
+      <c r="DA21" s="11">
+        <f t="shared" si="27"/>
+        <v>16899.555685830848</v>
+      </c>
+      <c r="DB21" s="11">
+        <f t="shared" ref="DB21:DC21" si="28">DA21*(1+$AB$24)</f>
+        <v>17068.551242689158</v>
+      </c>
+      <c r="DC21" s="11">
+        <f t="shared" si="28"/>
+        <v>17239.23675511605</v>
+      </c>
+    </row>
+    <row r="22" spans="2:107" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="23">+E8/E6</f>
+        <f t="shared" ref="E22:H22" si="29">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.76986554460911061</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.7649648197674126</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.75552025485015994</v>
       </c>
       <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="24">+I8/I6</f>
+        <f t="shared" ref="I22:K22" si="30">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79414649997854059</v>
       </c>
       <c r="K22" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79488747486433631</v>
       </c>
       <c r="L22" s="12">
@@ -2188,58 +2554,66 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:P22" si="25">+M8/M6</f>
+        <f t="shared" ref="M22:P22" si="31">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.79387045988593929</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.79258647247121738</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.80009029168138812</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" ref="Q22:R22" si="26">+Q8/Q6</f>
+        <f t="shared" ref="Q22:R22" si="32">+Q8/Q6</f>
         <v>0.81130190526285029</v>
       </c>
       <c r="R22" s="12">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.82221796356815668</v>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ref="S22:U22" si="27">+S8/S6</f>
+        <f t="shared" ref="S22:U22" si="33">+S8/S6</f>
         <v>0.81988145661452783</v>
       </c>
       <c r="T22" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.80861146883751056</v>
       </c>
       <c r="U22" s="12">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.80035825256225945</v>
       </c>
       <c r="V22" s="12">
-        <f t="shared" ref="V22:X22" si="28">+V8/V6</f>
+        <f t="shared" ref="V22:X22" si="34">+V8/V6</f>
         <v>0.80456456114524755</v>
       </c>
       <c r="W22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.79301768885422286</v>
       </c>
       <c r="X22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.8</v>
       </c>
       <c r="Y22" s="12"/>
       <c r="Z22" s="12"/>
       <c r="AA22" s="12"/>
     </row>
-    <row r="24" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:107" x14ac:dyDescent="0.2">
+      <c r="AA23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB23" s="13">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2653,14 @@
       <c r="X24" s="6"/>
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-    </row>
-    <row r="25" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB24" s="13">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
@@ -2317,9 +2696,14 @@
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
       <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
-    </row>
-    <row r="26" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB25" s="13">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="26" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
@@ -2359,9 +2743,15 @@
       <c r="X26" s="6"/>
       <c r="Y26" s="6"/>
       <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
-    </row>
-    <row r="27" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA26" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB26" s="14">
+        <f>NPV(AB25,AE21:DC21)</f>
+        <v>70054.692271372289</v>
+      </c>
+    </row>
+    <row r="27" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
         <v>35</v>
       </c>
@@ -2397,9 +2787,15 @@
       <c r="X27" s="6"/>
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
-      <c r="AA27" s="6"/>
-    </row>
-    <row r="28" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="5">
+        <f>W19</f>
+        <v>363.07799999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
@@ -2435,9 +2831,15 @@
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
-    </row>
-    <row r="29" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB28" s="14">
+        <f>AB26/AB27</f>
+        <v>192.94667336322303</v>
+      </c>
+    </row>
+    <row r="29" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
         <v>37</v>
       </c>
@@ -2473,9 +2875,15 @@
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
-      <c r="AA29" s="6"/>
-    </row>
-    <row r="30" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB29" s="15">
+        <f>(AB28-Main!O2)/Main!O2</f>
+        <v>0.24361375032692892</v>
+      </c>
+    </row>
+    <row r="30" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
         <v>38</v>
       </c>
@@ -2515,9 +2923,8 @@
       <c r="X30" s="6"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
-    </row>
-    <row r="31" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
         <v>39</v>
       </c>
@@ -2553,9 +2960,8 @@
       <c r="X31" s="6"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
-      <c r="AA31" s="6"/>
-    </row>
-    <row r="32" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
         <v>32</v>
       </c>

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4E1926-EF23-49B7-8B2F-F568FE2EDE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC20909A-C594-4D27-B314-5B2B10FBF323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
@@ -362,7 +362,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -393,6 +393,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -798,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>155.15</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -806,10 +807,10 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="14:16" x14ac:dyDescent="0.2">
@@ -818,7 +819,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>56319.450000000004</v>
+        <v>46865.78</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -826,10 +827,11 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <v>1707</v>
+        <f>489+3421</f>
+        <v>3910</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="14:16" x14ac:dyDescent="0.2">
@@ -837,10 +839,10 @@
         <v>4</v>
       </c>
       <c r="O6" s="5">
-        <v>737</v>
+        <v>2627</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="14:16" x14ac:dyDescent="0.2">
@@ -849,7 +851,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>55349.450000000004</v>
+        <v>45582.78</v>
       </c>
     </row>
   </sheetData>
@@ -1006,6 +1008,11 @@
         <v>2420</v>
       </c>
     </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="X5" s="2">
+        <v>789</v>
+      </c>
+    </row>
     <row r="6" spans="1:40" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>7</v>
@@ -1070,10 +1077,12 @@
         <v>761.553</v>
       </c>
       <c r="X6" s="4">
-        <f>(787+791)/2</f>
-        <v>789</v>
-      </c>
-      <c r="Y6" s="4"/>
+        <v>827</v>
+      </c>
+      <c r="Y6" s="4">
+        <f>(847+851)/2</f>
+        <v>849</v>
+      </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
       <c r="AF6" s="3">
@@ -1145,8 +1154,7 @@
         <v>157.62799999999999</v>
       </c>
       <c r="X7" s="6">
-        <f>+X6-X8</f>
-        <v>157.79999999999995</v>
+        <v>165.97800000000001</v>
       </c>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
@@ -1235,8 +1243,8 @@
         <v>603.92499999999995</v>
       </c>
       <c r="X8" s="6">
-        <f>+X6*0.8</f>
-        <v>631.20000000000005</v>
+        <f>+X6-X7</f>
+        <v>661.02199999999993</v>
       </c>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
@@ -1306,8 +1314,7 @@
         <v>341.06099999999998</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" ref="X9:X10" si="6">+W9+1</f>
-        <v>342.06099999999998</v>
+        <v>387.48200000000003</v>
       </c>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
@@ -1377,8 +1384,7 @@
         <v>214.291</v>
       </c>
       <c r="X10" s="6">
-        <f t="shared" si="6"/>
-        <v>215.291</v>
+        <v>239.02600000000001</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
@@ -1448,8 +1454,7 @@
         <v>60.993000000000002</v>
       </c>
       <c r="X11" s="6">
-        <f>+W11+1</f>
-        <v>61.993000000000002</v>
+        <v>69.774000000000001</v>
       </c>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
@@ -1462,84 +1467,84 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <f t="shared" ref="E12:L12" si="7">SUM(E9:E11)</f>
+        <f t="shared" ref="E12:L12" si="6">SUM(E9:E11)</f>
         <v>129.958</v>
       </c>
       <c r="F12" s="6">
+        <f t="shared" si="6"/>
+        <v>145.613</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="6"/>
+        <v>164.71299999999999</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" si="6"/>
+        <v>186.33699999999999</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="6"/>
+        <v>212.05100000000002</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="6"/>
+        <v>250.59399999999999</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="6"/>
+        <v>278.154</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="6"/>
+        <v>327.35199999999998</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" ref="M12:U12" si="7">+M11+M10+M9</f>
+        <v>374.27600000000001</v>
+      </c>
+      <c r="N12" s="6">
         <f t="shared" si="7"/>
-        <v>145.613</v>
-      </c>
-      <c r="G12" s="6">
+        <v>407.27</v>
+      </c>
+      <c r="O12" s="6">
         <f t="shared" si="7"/>
-        <v>164.71299999999999</v>
-      </c>
-      <c r="H12" s="6">
+        <v>416.77</v>
+      </c>
+      <c r="P12" s="6">
         <f t="shared" si="7"/>
-        <v>186.33699999999999</v>
-      </c>
-      <c r="I12" s="6">
+        <v>429.62</v>
+      </c>
+      <c r="Q12" s="6">
         <f t="shared" si="7"/>
-        <v>212.05100000000002</v>
-      </c>
-      <c r="J12" s="6">
+        <v>448.447</v>
+      </c>
+      <c r="R12" s="6">
         <f t="shared" si="7"/>
-        <v>250.59399999999999</v>
-      </c>
-      <c r="K12" s="6">
+        <v>457.07799999999997</v>
+      </c>
+      <c r="S12" s="6">
         <f t="shared" si="7"/>
-        <v>278.154</v>
-      </c>
-      <c r="L12" s="6">
+        <v>489.15899999999999</v>
+      </c>
+      <c r="T12" s="6">
         <f t="shared" si="7"/>
-        <v>327.35199999999998</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" ref="M12:U12" si="8">+M11+M10+M9</f>
-        <v>374.27600000000001</v>
-      </c>
-      <c r="N12" s="6">
+        <v>509.16199999999998</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>531.98199999999997</v>
+      </c>
+      <c r="V12" s="6">
+        <f t="shared" ref="V12:W12" si="8">+V11+V10+V9</f>
+        <v>584.15700000000004</v>
+      </c>
+      <c r="W12" s="6">
         <f t="shared" si="8"/>
-        <v>407.27</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" si="8"/>
-        <v>416.77</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="8"/>
-        <v>429.62</v>
-      </c>
-      <c r="Q12" s="6">
-        <f t="shared" si="8"/>
-        <v>448.447</v>
-      </c>
-      <c r="R12" s="6">
-        <f t="shared" si="8"/>
-        <v>457.07799999999997</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="8"/>
-        <v>489.15899999999999</v>
-      </c>
-      <c r="T12" s="6">
-        <f t="shared" si="8"/>
-        <v>509.16199999999998</v>
-      </c>
-      <c r="U12" s="6">
-        <f t="shared" si="8"/>
-        <v>531.98199999999997</v>
-      </c>
-      <c r="V12" s="6">
-        <f t="shared" ref="V12:W12" si="9">+V11+V10+V9</f>
-        <v>584.15700000000004</v>
-      </c>
-      <c r="W12" s="6">
-        <f t="shared" si="9"/>
         <v>616.34500000000003</v>
       </c>
       <c r="X12" s="6">
-        <f t="shared" ref="X12" si="10">+X11+X10+X9</f>
-        <v>619.34500000000003</v>
+        <f t="shared" ref="X12" si="9">+X11+X10+X9</f>
+        <v>696.28200000000004</v>
       </c>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
@@ -1552,84 +1557,84 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6">
-        <f t="shared" ref="E13:L13" si="11">E8-E12</f>
+        <f t="shared" ref="E13:L13" si="10">E8-E12</f>
         <v>-9.2669999999999959</v>
       </c>
       <c r="F13" s="6">
+        <f t="shared" si="10"/>
+        <v>-8.9379999999999882</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="10"/>
+        <v>-12.829999999999984</v>
+      </c>
+      <c r="H13" s="6">
+        <f t="shared" si="10"/>
+        <v>-9.8859999999999673</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="10"/>
+        <v>-4.8950000000000102</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="10"/>
+        <v>8.4549999999999841</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="10"/>
+        <v>10.413999999999987</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" si="10"/>
+        <v>-3.13900000000001</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" ref="M13:U13" si="11">+M8-M12</f>
+        <v>-31.341999999999985</v>
+      </c>
+      <c r="N13" s="6">
         <f t="shared" si="11"/>
-        <v>-8.9379999999999882</v>
-      </c>
-      <c r="G13" s="6">
+        <v>-34.627999999999986</v>
+      </c>
+      <c r="O13" s="6">
         <f t="shared" si="11"/>
-        <v>-12.829999999999984</v>
-      </c>
-      <c r="H13" s="6">
+        <v>-34.96999999999997</v>
+      </c>
+      <c r="P13" s="6">
         <f t="shared" si="11"/>
-        <v>-9.8859999999999673</v>
-      </c>
-      <c r="I13" s="6">
+        <v>-22.006000000000029</v>
+      </c>
+      <c r="Q13" s="6">
         <f t="shared" si="11"/>
-        <v>-4.8950000000000102</v>
-      </c>
-      <c r="J13" s="6">
+        <v>-4.230000000000075</v>
+      </c>
+      <c r="R13" s="6">
         <f t="shared" si="11"/>
-        <v>8.4549999999999841</v>
-      </c>
-      <c r="K13" s="6">
+        <v>27.742000000000019</v>
+      </c>
+      <c r="S13" s="6">
         <f t="shared" si="11"/>
-        <v>10.413999999999987</v>
-      </c>
-      <c r="L13" s="6">
+        <v>11.996000000000038</v>
+      </c>
+      <c r="T13" s="6">
         <f t="shared" si="11"/>
-        <v>-3.13900000000001</v>
-      </c>
-      <c r="M13" s="6">
-        <f t="shared" ref="M13:U13" si="12">+M8-M12</f>
-        <v>-31.341999999999985</v>
-      </c>
-      <c r="N13" s="6">
+        <v>12.617999999999995</v>
+      </c>
+      <c r="U13" s="6">
+        <f t="shared" si="11"/>
+        <v>20.27800000000002</v>
+      </c>
+      <c r="V13" s="6">
+        <f t="shared" ref="V13:W13" si="12">+V8-V12</f>
+        <v>9.3919999999999391</v>
+      </c>
+      <c r="W13" s="6">
         <f t="shared" si="12"/>
-        <v>-34.627999999999986</v>
-      </c>
-      <c r="O13" s="6">
-        <f t="shared" si="12"/>
-        <v>-34.96999999999997</v>
-      </c>
-      <c r="P13" s="6">
-        <f t="shared" si="12"/>
-        <v>-22.006000000000029</v>
-      </c>
-      <c r="Q13" s="6">
-        <f t="shared" si="12"/>
-        <v>-4.230000000000075</v>
-      </c>
-      <c r="R13" s="6">
-        <f t="shared" si="12"/>
-        <v>27.742000000000019</v>
-      </c>
-      <c r="S13" s="6">
-        <f t="shared" si="12"/>
-        <v>11.996000000000038</v>
-      </c>
-      <c r="T13" s="6">
-        <f t="shared" si="12"/>
-        <v>12.617999999999995</v>
-      </c>
-      <c r="U13" s="6">
-        <f t="shared" si="12"/>
-        <v>20.27800000000002</v>
-      </c>
-      <c r="V13" s="6">
-        <f t="shared" ref="V13:W13" si="13">+V8-V12</f>
-        <v>9.3919999999999391</v>
-      </c>
-      <c r="W13" s="6">
-        <f t="shared" si="13"/>
         <v>-12.420000000000073</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" ref="X13" si="14">+X8-X12</f>
-        <v>11.855000000000018</v>
+        <f t="shared" ref="X13" si="13">+X8-X12</f>
+        <v>-35.260000000000105</v>
       </c>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
@@ -1712,8 +1717,8 @@
         <v>44.216000000000001</v>
       </c>
       <c r="X14" s="6">
-        <f>+W14</f>
-        <v>44.216000000000001</v>
+        <f>44.663-3.075</f>
+        <v>41.587999999999994</v>
       </c>
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
@@ -1726,84 +1731,84 @@
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6">
-        <f t="shared" ref="E15:L15" si="15">+E13+E14</f>
+        <f t="shared" ref="E15:L15" si="14">+E13+E14</f>
         <v>-14.554999999999996</v>
       </c>
       <c r="F15" s="6">
+        <f t="shared" si="14"/>
+        <v>-15.166999999999987</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" si="14"/>
+        <v>-12.528999999999986</v>
+      </c>
+      <c r="H15" s="6">
+        <f t="shared" si="14"/>
+        <v>-9.6579999999999675</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="14"/>
+        <v>-4.7670000000000101</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" si="14"/>
+        <v>8.531999999999984</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="14"/>
+        <v>10.853999999999989</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="14"/>
+        <v>-1.1000000000010779E-2</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" ref="M15:U15" si="15">+M13+M14</f>
+        <v>-23.058999999999983</v>
+      </c>
+      <c r="N15" s="6">
         <f t="shared" si="15"/>
-        <v>-15.166999999999987</v>
-      </c>
-      <c r="G15" s="6">
+        <v>-25.853999999999985</v>
+      </c>
+      <c r="O15" s="6">
         <f t="shared" si="15"/>
-        <v>-12.528999999999986</v>
-      </c>
-      <c r="H15" s="6">
+        <v>-20.423999999999971</v>
+      </c>
+      <c r="P15" s="6">
         <f t="shared" si="15"/>
-        <v>-9.6579999999999675</v>
-      </c>
-      <c r="I15" s="6">
+        <v>-0.90800000000002967</v>
+      </c>
+      <c r="Q15" s="6">
         <f t="shared" si="15"/>
-        <v>-4.7670000000000101</v>
-      </c>
-      <c r="J15" s="6">
+        <v>24.299999999999923</v>
+      </c>
+      <c r="R15" s="6">
         <f t="shared" si="15"/>
-        <v>8.531999999999984</v>
-      </c>
-      <c r="K15" s="6">
+        <v>57.267000000000017</v>
+      </c>
+      <c r="S15" s="6">
         <f t="shared" si="15"/>
-        <v>10.853999999999989</v>
-      </c>
-      <c r="L15" s="6">
+        <v>46.185000000000038</v>
+      </c>
+      <c r="T15" s="6">
         <f t="shared" si="15"/>
-        <v>-1.1000000000010779E-2</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" ref="M15:U15" si="16">+M13+M14</f>
-        <v>-23.058999999999983</v>
-      </c>
-      <c r="N15" s="6">
+        <v>47.792999999999999</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" si="15"/>
+        <v>56.136000000000017</v>
+      </c>
+      <c r="V15" s="6">
+        <f t="shared" ref="V15:X15" si="16">+V13+V14</f>
+        <v>53.825999999999937</v>
+      </c>
+      <c r="W15" s="6">
         <f t="shared" si="16"/>
-        <v>-25.853999999999985</v>
-      </c>
-      <c r="O15" s="6">
+        <v>31.795999999999928</v>
+      </c>
+      <c r="X15" s="6">
         <f t="shared" si="16"/>
-        <v>-20.423999999999971</v>
-      </c>
-      <c r="P15" s="6">
-        <f t="shared" si="16"/>
-        <v>-0.90800000000002967</v>
-      </c>
-      <c r="Q15" s="6">
-        <f t="shared" si="16"/>
-        <v>24.299999999999923</v>
-      </c>
-      <c r="R15" s="6">
-        <f t="shared" si="16"/>
-        <v>57.267000000000017</v>
-      </c>
-      <c r="S15" s="6">
-        <f t="shared" si="16"/>
-        <v>46.185000000000038</v>
-      </c>
-      <c r="T15" s="6">
-        <f t="shared" si="16"/>
-        <v>47.792999999999999</v>
-      </c>
-      <c r="U15" s="6">
-        <f t="shared" si="16"/>
-        <v>56.136000000000017</v>
-      </c>
-      <c r="V15" s="6">
-        <f t="shared" ref="V15:X15" si="17">+V13+V14</f>
-        <v>53.825999999999937</v>
-      </c>
-      <c r="W15" s="6">
-        <f t="shared" si="17"/>
-        <v>31.795999999999928</v>
-      </c>
-      <c r="X15" s="6">
-        <f t="shared" si="17"/>
-        <v>56.071000000000019</v>
+        <v>6.3279999999998893</v>
       </c>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
@@ -1873,8 +1878,7 @@
         <v>7.1539999999999999</v>
       </c>
       <c r="X16" s="6">
-        <f>+X15*0.1</f>
-        <v>5.6071000000000026</v>
+        <v>3.4409999999999998</v>
       </c>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
@@ -1887,84 +1891,84 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6">
-        <f t="shared" ref="E17:L17" si="18">+E15-E16</f>
+        <f t="shared" ref="E17:L17" si="17">+E15-E16</f>
         <v>-15.149999999999997</v>
       </c>
       <c r="F17" s="6">
+        <f t="shared" si="17"/>
+        <v>-16.159999999999986</v>
+      </c>
+      <c r="G17" s="6">
+        <f t="shared" si="17"/>
+        <v>-11.989999999999986</v>
+      </c>
+      <c r="H17" s="6">
+        <f t="shared" si="17"/>
+        <v>-6.6979999999999675</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="17"/>
+        <v>-4.0500000000000105</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="17"/>
+        <v>7.1689999999999845</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="17"/>
+        <v>9.7379999999999889</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="17"/>
+        <v>-4.8790000000000111</v>
+      </c>
+      <c r="M17" s="6">
+        <f t="shared" ref="M17:U17" si="18">+M15-M16</f>
+        <v>-25.984999999999985</v>
+      </c>
+      <c r="N17" s="6">
         <f t="shared" si="18"/>
-        <v>-16.159999999999986</v>
-      </c>
-      <c r="G17" s="6">
+        <v>-29.033999999999985</v>
+      </c>
+      <c r="O17" s="6">
         <f t="shared" si="18"/>
-        <v>-11.989999999999986</v>
-      </c>
-      <c r="H17" s="6">
+        <v>-24.08599999999997</v>
+      </c>
+      <c r="P17" s="6">
         <f t="shared" si="18"/>
-        <v>-6.6979999999999675</v>
-      </c>
-      <c r="I17" s="6">
+        <v>-3.9690000000000296</v>
+      </c>
+      <c r="Q17" s="6">
         <f t="shared" si="18"/>
-        <v>-4.0500000000000105</v>
-      </c>
-      <c r="J17" s="6">
+        <v>22.629999999999924</v>
+      </c>
+      <c r="R17" s="6">
         <f t="shared" si="18"/>
-        <v>7.1689999999999845</v>
-      </c>
-      <c r="K17" s="6">
+        <v>53.993000000000016</v>
+      </c>
+      <c r="S17" s="6">
         <f t="shared" si="18"/>
-        <v>9.7379999999999889</v>
-      </c>
-      <c r="L17" s="6">
+        <v>42.631000000000036</v>
+      </c>
+      <c r="T17" s="6">
         <f t="shared" si="18"/>
-        <v>-4.8790000000000111</v>
-      </c>
-      <c r="M17" s="6">
-        <f t="shared" ref="M17:U17" si="19">+M15-M16</f>
-        <v>-25.984999999999985</v>
-      </c>
-      <c r="N17" s="6">
+        <v>43.823999999999998</v>
+      </c>
+      <c r="U17" s="6">
+        <f t="shared" si="18"/>
+        <v>51.697000000000017</v>
+      </c>
+      <c r="V17" s="6">
+        <f t="shared" ref="V17:X17" si="19">+V15-V16</f>
+        <v>45.593999999999937</v>
+      </c>
+      <c r="W17" s="6">
         <f t="shared" si="19"/>
-        <v>-29.033999999999985</v>
-      </c>
-      <c r="O17" s="6">
+        <v>24.641999999999928</v>
+      </c>
+      <c r="X17" s="6">
         <f t="shared" si="19"/>
-        <v>-24.08599999999997</v>
-      </c>
-      <c r="P17" s="6">
-        <f t="shared" si="19"/>
-        <v>-3.9690000000000296</v>
-      </c>
-      <c r="Q17" s="6">
-        <f t="shared" si="19"/>
-        <v>22.629999999999924</v>
-      </c>
-      <c r="R17" s="6">
-        <f t="shared" si="19"/>
-        <v>53.993000000000016</v>
-      </c>
-      <c r="S17" s="6">
-        <f t="shared" si="19"/>
-        <v>42.631000000000036</v>
-      </c>
-      <c r="T17" s="6">
-        <f t="shared" si="19"/>
-        <v>43.823999999999998</v>
-      </c>
-      <c r="U17" s="6">
-        <f t="shared" si="19"/>
-        <v>51.697000000000017</v>
-      </c>
-      <c r="V17" s="6">
-        <f t="shared" ref="V17:X17" si="20">+V15-V16</f>
-        <v>45.593999999999937</v>
-      </c>
-      <c r="W17" s="6">
-        <f t="shared" si="20"/>
-        <v>24.641999999999928</v>
-      </c>
-      <c r="X17" s="6">
-        <f t="shared" si="20"/>
-        <v>50.463900000000017</v>
+        <v>2.8869999999998894</v>
       </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
@@ -1977,84 +1981,84 @@
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7">
-        <f t="shared" ref="E18:L18" si="21">+E17/E19</f>
+        <f t="shared" ref="E18:L18" si="20">+E17/E19</f>
         <v>-5.0073705850856368E-2</v>
       </c>
       <c r="F18" s="7">
+        <f t="shared" si="20"/>
+        <v>-5.3147929500060795E-2</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="20"/>
+        <v>-3.9178653352241861E-2</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="20"/>
+        <v>-2.1745411809011676E-2</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="20"/>
+        <v>-1.3054114947122809E-2</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="20"/>
+        <v>2.0727021455604115E-2</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="20"/>
+        <v>2.8171540321927365E-2</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="20"/>
+        <v>-1.5498975523753589E-2</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" ref="M18:U18" si="21">+M17/M19</f>
+        <v>-8.223361498781602E-2</v>
+      </c>
+      <c r="N18" s="7">
         <f t="shared" si="21"/>
-        <v>-5.3147929500060795E-2</v>
-      </c>
-      <c r="G18" s="7">
+        <v>-9.1489468974122995E-2</v>
+      </c>
+      <c r="O18" s="7">
         <f t="shared" si="21"/>
-        <v>-3.9178653352241861E-2</v>
-      </c>
-      <c r="H18" s="7">
+        <v>-7.5437068960117162E-2</v>
+      </c>
+      <c r="P18" s="7">
         <f t="shared" si="21"/>
-        <v>-2.1745411809011676E-2</v>
-      </c>
-      <c r="I18" s="7">
+        <v>-1.2317862296913644E-2</v>
+      </c>
+      <c r="Q18" s="7">
         <f t="shared" si="21"/>
-        <v>-1.3054114947122809E-2</v>
-      </c>
-      <c r="J18" s="7">
+        <v>6.4416226171262123E-2</v>
+      </c>
+      <c r="R18" s="7">
         <f t="shared" si="21"/>
-        <v>2.0727021455604115E-2</v>
-      </c>
-      <c r="K18" s="7">
+        <v>0.15299498168072614</v>
+      </c>
+      <c r="S18" s="7">
         <f t="shared" si="21"/>
-        <v>2.8171540321927365E-2</v>
-      </c>
-      <c r="L18" s="7">
+        <v>0.11975706432121007</v>
+      </c>
+      <c r="T18" s="7">
         <f t="shared" si="21"/>
-        <v>-1.5498975523753589E-2</v>
-      </c>
-      <c r="M18" s="7">
-        <f t="shared" ref="M18:U18" si="22">+M17/M19</f>
-        <v>-8.223361498781602E-2</v>
-      </c>
-      <c r="N18" s="7">
+        <v>0.12284577002859225</v>
+      </c>
+      <c r="U18" s="7">
+        <f t="shared" si="21"/>
+        <v>0.14455240678345246</v>
+      </c>
+      <c r="V18" s="7">
+        <f t="shared" ref="V18:X18" si="22">+V17/V19</f>
+        <v>0.12632016401617979</v>
+      </c>
+      <c r="W18" s="7">
         <f t="shared" si="22"/>
-        <v>-9.1489468974122995E-2</v>
-      </c>
-      <c r="O18" s="7">
+        <v>6.7869713945763521E-2</v>
+      </c>
+      <c r="X18" s="7">
         <f t="shared" si="22"/>
-        <v>-7.5437068960117162E-2</v>
-      </c>
-      <c r="P18" s="7">
-        <f t="shared" si="22"/>
-        <v>-1.2317862296913644E-2</v>
-      </c>
-      <c r="Q18" s="7">
-        <f t="shared" si="22"/>
-        <v>6.4416226171262123E-2</v>
-      </c>
-      <c r="R18" s="7">
-        <f t="shared" si="22"/>
-        <v>0.15299498168072614</v>
-      </c>
-      <c r="S18" s="7">
-        <f t="shared" si="22"/>
-        <v>0.11975706432121007</v>
-      </c>
-      <c r="T18" s="7">
-        <f t="shared" si="22"/>
-        <v>0.12284577002859225</v>
-      </c>
-      <c r="U18" s="7">
-        <f t="shared" si="22"/>
-        <v>0.14455240678345246</v>
-      </c>
-      <c r="V18" s="7">
-        <f t="shared" ref="V18:X18" si="23">+V17/V19</f>
-        <v>0.12632016401617979</v>
-      </c>
-      <c r="W18" s="7">
-        <f t="shared" si="23"/>
-        <v>6.7869713945763521E-2</v>
-      </c>
-      <c r="X18" s="7">
-        <f t="shared" si="23"/>
-        <v>0.13898914282881369</v>
+        <v>8.0479475921663921E-3</v>
       </c>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
@@ -2124,12 +2128,21 @@
         <v>363.07799999999997</v>
       </c>
       <c r="X19" s="6">
-        <f>+W19</f>
-        <v>363.07799999999997</v>
+        <v>358.72500000000002</v>
       </c>
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
+      <c r="AI19" s="16">
+        <f>(AI20-AI21)/AI21</f>
+        <v>5.7928472834197734E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:107" x14ac:dyDescent="0.2">
+      <c r="AI20">
+        <f>(3312+3322)/2</f>
+        <v>3317</v>
+      </c>
     </row>
     <row r="21" spans="2:107" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
@@ -2142,47 +2155,47 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:K21" si="24">+I6/E6-1</f>
+        <f t="shared" ref="I21:K21" si="23">+I6/E6-1</f>
         <v>0.74875060610958455</v>
       </c>
       <c r="J21" s="10">
+        <f t="shared" si="23"/>
+        <v>0.83741431074009598</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="23"/>
+        <v>0.82841515192723181</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" ref="L21:S21" si="24">+L6/H6-1</f>
+        <v>0.73898411040081502</v>
+      </c>
+      <c r="M21" s="10">
         <f t="shared" si="24"/>
-        <v>0.83741431074009598</v>
-      </c>
-      <c r="K21" s="10">
+        <v>0.61387196474520134</v>
+      </c>
+      <c r="N21" s="10">
         <f t="shared" si="24"/>
-        <v>0.82841515192723181</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" ref="L21:S21" si="25">+L6/H6-1</f>
-        <v>0.73898411040081502</v>
-      </c>
-      <c r="M21" s="10">
-        <f t="shared" si="25"/>
-        <v>0.61387196474520134</v>
-      </c>
-      <c r="N21" s="10">
-        <f t="shared" si="25"/>
         <v>0.43900023911857233</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.32692614935404807</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.25440121338067367</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.25428318134024219</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.25617864545940661</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0.26891267432542976</v>
       </c>
       <c r="T21" s="10">
@@ -2203,9 +2216,12 @@
       </c>
       <c r="X21" s="10">
         <f>+X6/T6-1</f>
-        <v>0.22272691347463658</v>
-      </c>
-      <c r="Y21" s="10"/>
+        <v>0.28161616912994214</v>
+      </c>
+      <c r="Y21" s="10">
+        <f>+Y6/U6-1</f>
+        <v>0.23040625144924176</v>
+      </c>
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
       <c r="AE21" s="3">
@@ -2226,295 +2242,295 @@
       </c>
       <c r="AI21" s="3">
         <f>AH21*(1+$AB$23)</f>
-        <v>3274.8155000000002</v>
+        <v>3315.0796249999999</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" ref="AJ21:AN21" si="26">AI21*(1+$AB$23)</f>
-        <v>3995.2749100000001</v>
+        <f t="shared" ref="AJ21:AN21" si="25">AI21*(1+$AB$23)</f>
+        <v>4094.1233368749995</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="26"/>
-        <v>4874.2353902000004</v>
+        <f t="shared" si="25"/>
+        <v>5056.2423210406241</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="26"/>
-        <v>5946.567176044</v>
+        <f t="shared" si="25"/>
+        <v>6244.4592664851698</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" si="26"/>
-        <v>7254.8119547736796</v>
+        <f t="shared" si="25"/>
+        <v>7711.9071941091843</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" si="26"/>
-        <v>8850.8705848238897</v>
+        <f t="shared" si="25"/>
+        <v>9524.2053847248408</v>
       </c>
       <c r="AO21" s="11">
         <f>AN21*(1+$AB$24)</f>
-        <v>8939.3792906721283</v>
+        <v>9619.4474385720896</v>
       </c>
       <c r="AP21" s="11">
-        <f t="shared" ref="AP21:DA21" si="27">AO21*(1+$AB$24)</f>
-        <v>9028.7730835788498</v>
+        <f t="shared" ref="AP21:DA21" si="26">AO21*(1+$AB$24)</f>
+        <v>9715.6419129578098</v>
       </c>
       <c r="AQ21" s="11">
+        <f t="shared" si="26"/>
+        <v>9812.7983320873882</v>
+      </c>
+      <c r="AR21" s="11">
+        <f t="shared" si="26"/>
+        <v>9910.9263154082619</v>
+      </c>
+      <c r="AS21" s="11">
+        <f t="shared" si="26"/>
+        <v>10010.035578562345</v>
+      </c>
+      <c r="AT21" s="11">
+        <f t="shared" si="26"/>
+        <v>10110.135934347969</v>
+      </c>
+      <c r="AU21" s="11">
+        <f t="shared" si="26"/>
+        <v>10211.237293691449</v>
+      </c>
+      <c r="AV21" s="11">
+        <f t="shared" si="26"/>
+        <v>10313.349666628363</v>
+      </c>
+      <c r="AW21" s="11">
+        <f t="shared" si="26"/>
+        <v>10416.483163294646</v>
+      </c>
+      <c r="AX21" s="11">
+        <f t="shared" si="26"/>
+        <v>10520.647994927593</v>
+      </c>
+      <c r="AY21" s="11">
+        <f t="shared" si="26"/>
+        <v>10625.854474876869</v>
+      </c>
+      <c r="AZ21" s="11">
+        <f t="shared" si="26"/>
+        <v>10732.113019625638</v>
+      </c>
+      <c r="BA21" s="11">
+        <f t="shared" si="26"/>
+        <v>10839.434149821895</v>
+      </c>
+      <c r="BB21" s="11">
+        <f t="shared" si="26"/>
+        <v>10947.828491320113</v>
+      </c>
+      <c r="BC21" s="11">
+        <f t="shared" si="26"/>
+        <v>11057.306776233314</v>
+      </c>
+      <c r="BD21" s="11">
+        <f t="shared" si="26"/>
+        <v>11167.879843995646</v>
+      </c>
+      <c r="BE21" s="11">
+        <f t="shared" si="26"/>
+        <v>11279.558642435602</v>
+      </c>
+      <c r="BF21" s="11">
+        <f t="shared" si="26"/>
+        <v>11392.354228859958</v>
+      </c>
+      <c r="BG21" s="11">
+        <f t="shared" si="26"/>
+        <v>11506.277771148558</v>
+      </c>
+      <c r="BH21" s="11">
+        <f t="shared" si="26"/>
+        <v>11621.340548860044</v>
+      </c>
+      <c r="BI21" s="11">
+        <f t="shared" si="26"/>
+        <v>11737.553954348645</v>
+      </c>
+      <c r="BJ21" s="11">
+        <f t="shared" si="26"/>
+        <v>11854.929493892132</v>
+      </c>
+      <c r="BK21" s="11">
+        <f t="shared" si="26"/>
+        <v>11973.478788831053</v>
+      </c>
+      <c r="BL21" s="11">
+        <f t="shared" si="26"/>
+        <v>12093.213576719363</v>
+      </c>
+      <c r="BM21" s="11">
+        <f t="shared" si="26"/>
+        <v>12214.145712486557</v>
+      </c>
+      <c r="BN21" s="11">
+        <f t="shared" si="26"/>
+        <v>12336.287169611423</v>
+      </c>
+      <c r="BO21" s="11">
+        <f t="shared" si="26"/>
+        <v>12459.650041307537</v>
+      </c>
+      <c r="BP21" s="11">
+        <f t="shared" si="26"/>
+        <v>12584.246541720613</v>
+      </c>
+      <c r="BQ21" s="11">
+        <f t="shared" si="26"/>
+        <v>12710.08900713782</v>
+      </c>
+      <c r="BR21" s="11">
+        <f t="shared" si="26"/>
+        <v>12837.189897209199</v>
+      </c>
+      <c r="BS21" s="11">
+        <f t="shared" si="26"/>
+        <v>12965.561796181291</v>
+      </c>
+      <c r="BT21" s="11">
+        <f t="shared" si="26"/>
+        <v>13095.217414143104</v>
+      </c>
+      <c r="BU21" s="11">
+        <f t="shared" si="26"/>
+        <v>13226.169588284536</v>
+      </c>
+      <c r="BV21" s="11">
+        <f t="shared" si="26"/>
+        <v>13358.431284167382</v>
+      </c>
+      <c r="BW21" s="11">
+        <f t="shared" si="26"/>
+        <v>13492.015597009056</v>
+      </c>
+      <c r="BX21" s="11">
+        <f t="shared" si="26"/>
+        <v>13626.935752979147</v>
+      </c>
+      <c r="BY21" s="11">
+        <f t="shared" si="26"/>
+        <v>13763.205110508938</v>
+      </c>
+      <c r="BZ21" s="11">
+        <f t="shared" si="26"/>
+        <v>13900.837161614027</v>
+      </c>
+      <c r="CA21" s="11">
+        <f t="shared" si="26"/>
+        <v>14039.845533230167</v>
+      </c>
+      <c r="CB21" s="11">
+        <f t="shared" si="26"/>
+        <v>14180.24398856247</v>
+      </c>
+      <c r="CC21" s="11">
+        <f t="shared" si="26"/>
+        <v>14322.046428448095</v>
+      </c>
+      <c r="CD21" s="11">
+        <f t="shared" si="26"/>
+        <v>14465.266892732576</v>
+      </c>
+      <c r="CE21" s="11">
+        <f t="shared" si="26"/>
+        <v>14609.919561659901</v>
+      </c>
+      <c r="CF21" s="11">
+        <f t="shared" si="26"/>
+        <v>14756.018757276501</v>
+      </c>
+      <c r="CG21" s="11">
+        <f t="shared" si="26"/>
+        <v>14903.578944849265</v>
+      </c>
+      <c r="CH21" s="11">
+        <f t="shared" si="26"/>
+        <v>15052.614734297758</v>
+      </c>
+      <c r="CI21" s="11">
+        <f t="shared" si="26"/>
+        <v>15203.140881640737</v>
+      </c>
+      <c r="CJ21" s="11">
+        <f t="shared" si="26"/>
+        <v>15355.172290457143</v>
+      </c>
+      <c r="CK21" s="11">
+        <f t="shared" si="26"/>
+        <v>15508.724013361714</v>
+      </c>
+      <c r="CL21" s="11">
+        <f t="shared" si="26"/>
+        <v>15663.811253495331</v>
+      </c>
+      <c r="CM21" s="11">
+        <f t="shared" si="26"/>
+        <v>15820.449366030283</v>
+      </c>
+      <c r="CN21" s="11">
+        <f t="shared" si="26"/>
+        <v>15978.653859690587</v>
+      </c>
+      <c r="CO21" s="11">
+        <f t="shared" si="26"/>
+        <v>16138.440398287492</v>
+      </c>
+      <c r="CP21" s="11">
+        <f t="shared" si="26"/>
+        <v>16299.824802270366</v>
+      </c>
+      <c r="CQ21" s="11">
+        <f t="shared" si="26"/>
+        <v>16462.823050293071</v>
+      </c>
+      <c r="CR21" s="11">
+        <f t="shared" si="26"/>
+        <v>16627.451280796002</v>
+      </c>
+      <c r="CS21" s="11">
+        <f t="shared" si="26"/>
+        <v>16793.72579360396</v>
+      </c>
+      <c r="CT21" s="11">
+        <f t="shared" si="26"/>
+        <v>16961.663051539999</v>
+      </c>
+      <c r="CU21" s="11">
+        <f t="shared" si="26"/>
+        <v>17131.279682055399</v>
+      </c>
+      <c r="CV21" s="11">
+        <f t="shared" si="26"/>
+        <v>17302.592478875955</v>
+      </c>
+      <c r="CW21" s="11">
+        <f t="shared" si="26"/>
+        <v>17475.618403664714</v>
+      </c>
+      <c r="CX21" s="11">
+        <f t="shared" si="26"/>
+        <v>17650.374587701361</v>
+      </c>
+      <c r="CY21" s="11">
+        <f t="shared" si="26"/>
+        <v>17826.878333578374</v>
+      </c>
+      <c r="CZ21" s="11">
+        <f t="shared" si="26"/>
+        <v>18005.147116914159</v>
+      </c>
+      <c r="DA21" s="11">
+        <f t="shared" si="26"/>
+        <v>18185.198588083302</v>
+      </c>
+      <c r="DB21" s="11">
+        <f t="shared" ref="DB21:DC21" si="27">DA21*(1+$AB$24)</f>
+        <v>18367.050573964134</v>
+      </c>
+      <c r="DC21" s="11">
         <f t="shared" si="27"/>
-        <v>9119.060814414639</v>
-      </c>
-      <c r="AR21" s="11">
-        <f t="shared" si="27"/>
-        <v>9210.2514225587856</v>
-      </c>
-      <c r="AS21" s="11">
-        <f t="shared" si="27"/>
-        <v>9302.3539367843732</v>
-      </c>
-      <c r="AT21" s="11">
-        <f t="shared" si="27"/>
-        <v>9395.3774761522163</v>
-      </c>
-      <c r="AU21" s="11">
-        <f t="shared" si="27"/>
-        <v>9489.3312509137377</v>
-      </c>
-      <c r="AV21" s="11">
-        <f t="shared" si="27"/>
-        <v>9584.2245634228748</v>
-      </c>
-      <c r="AW21" s="11">
-        <f t="shared" si="27"/>
-        <v>9680.0668090571035</v>
-      </c>
-      <c r="AX21" s="11">
-        <f t="shared" si="27"/>
-        <v>9776.8674771476744</v>
-      </c>
-      <c r="AY21" s="11">
-        <f t="shared" si="27"/>
-        <v>9874.6361519191505</v>
-      </c>
-      <c r="AZ21" s="11">
-        <f t="shared" si="27"/>
-        <v>9973.3825134383424</v>
-      </c>
-      <c r="BA21" s="11">
-        <f t="shared" si="27"/>
-        <v>10073.116338572725</v>
-      </c>
-      <c r="BB21" s="11">
-        <f t="shared" si="27"/>
-        <v>10173.847501958453</v>
-      </c>
-      <c r="BC21" s="11">
-        <f t="shared" si="27"/>
-        <v>10275.585976978038</v>
-      </c>
-      <c r="BD21" s="11">
-        <f t="shared" si="27"/>
-        <v>10378.341836747819</v>
-      </c>
-      <c r="BE21" s="11">
-        <f t="shared" si="27"/>
-        <v>10482.125255115297</v>
-      </c>
-      <c r="BF21" s="11">
-        <f t="shared" si="27"/>
-        <v>10586.946507666451</v>
-      </c>
-      <c r="BG21" s="11">
-        <f t="shared" si="27"/>
-        <v>10692.815972743116</v>
-      </c>
-      <c r="BH21" s="11">
-        <f t="shared" si="27"/>
-        <v>10799.744132470547</v>
-      </c>
-      <c r="BI21" s="11">
-        <f t="shared" si="27"/>
-        <v>10907.741573795252</v>
-      </c>
-      <c r="BJ21" s="11">
-        <f t="shared" si="27"/>
-        <v>11016.818989533205</v>
-      </c>
-      <c r="BK21" s="11">
-        <f t="shared" si="27"/>
-        <v>11126.987179428537</v>
-      </c>
-      <c r="BL21" s="11">
-        <f t="shared" si="27"/>
-        <v>11238.257051222823</v>
-      </c>
-      <c r="BM21" s="11">
-        <f t="shared" si="27"/>
-        <v>11350.639621735052</v>
-      </c>
-      <c r="BN21" s="11">
-        <f t="shared" si="27"/>
-        <v>11464.146017952402</v>
-      </c>
-      <c r="BO21" s="11">
-        <f t="shared" si="27"/>
-        <v>11578.787478131926</v>
-      </c>
-      <c r="BP21" s="11">
-        <f t="shared" si="27"/>
-        <v>11694.575352913245</v>
-      </c>
-      <c r="BQ21" s="11">
-        <f t="shared" si="27"/>
-        <v>11811.521106442378</v>
-      </c>
-      <c r="BR21" s="11">
-        <f t="shared" si="27"/>
-        <v>11929.636317506802</v>
-      </c>
-      <c r="BS21" s="11">
-        <f t="shared" si="27"/>
-        <v>12048.93268068187</v>
-      </c>
-      <c r="BT21" s="11">
-        <f t="shared" si="27"/>
-        <v>12169.422007488689</v>
-      </c>
-      <c r="BU21" s="11">
-        <f t="shared" si="27"/>
-        <v>12291.116227563576</v>
-      </c>
-      <c r="BV21" s="11">
-        <f t="shared" si="27"/>
-        <v>12414.027389839212</v>
-      </c>
-      <c r="BW21" s="11">
-        <f t="shared" si="27"/>
-        <v>12538.167663737604</v>
-      </c>
-      <c r="BX21" s="11">
-        <f t="shared" si="27"/>
-        <v>12663.549340374981</v>
-      </c>
-      <c r="BY21" s="11">
-        <f t="shared" si="27"/>
-        <v>12790.184833778731</v>
-      </c>
-      <c r="BZ21" s="11">
-        <f t="shared" si="27"/>
-        <v>12918.086682116518</v>
-      </c>
-      <c r="CA21" s="11">
-        <f t="shared" si="27"/>
-        <v>13047.267548937683</v>
-      </c>
-      <c r="CB21" s="11">
-        <f t="shared" si="27"/>
-        <v>13177.74022442706</v>
-      </c>
-      <c r="CC21" s="11">
-        <f t="shared" si="27"/>
-        <v>13309.51762667133</v>
-      </c>
-      <c r="CD21" s="11">
-        <f t="shared" si="27"/>
-        <v>13442.612802938043</v>
-      </c>
-      <c r="CE21" s="11">
-        <f t="shared" si="27"/>
-        <v>13577.038930967425</v>
-      </c>
-      <c r="CF21" s="11">
-        <f t="shared" si="27"/>
-        <v>13712.8093202771</v>
-      </c>
-      <c r="CG21" s="11">
-        <f t="shared" si="27"/>
-        <v>13849.937413479871</v>
-      </c>
-      <c r="CH21" s="11">
-        <f t="shared" si="27"/>
-        <v>13988.43678761467</v>
-      </c>
-      <c r="CI21" s="11">
-        <f t="shared" si="27"/>
-        <v>14128.321155490816</v>
-      </c>
-      <c r="CJ21" s="11">
-        <f t="shared" si="27"/>
-        <v>14269.604367045724</v>
-      </c>
-      <c r="CK21" s="11">
-        <f t="shared" si="27"/>
-        <v>14412.300410716181</v>
-      </c>
-      <c r="CL21" s="11">
-        <f t="shared" si="27"/>
-        <v>14556.423414823343</v>
-      </c>
-      <c r="CM21" s="11">
-        <f t="shared" si="27"/>
-        <v>14701.987648971577</v>
-      </c>
-      <c r="CN21" s="11">
-        <f t="shared" si="27"/>
-        <v>14849.007525461293</v>
-      </c>
-      <c r="CO21" s="11">
-        <f t="shared" si="27"/>
-        <v>14997.497600715906</v>
-      </c>
-      <c r="CP21" s="11">
-        <f t="shared" si="27"/>
-        <v>15147.472576723065</v>
-      </c>
-      <c r="CQ21" s="11">
-        <f t="shared" si="27"/>
-        <v>15298.947302490296</v>
-      </c>
-      <c r="CR21" s="11">
-        <f t="shared" si="27"/>
-        <v>15451.9367755152</v>
-      </c>
-      <c r="CS21" s="11">
-        <f t="shared" si="27"/>
-        <v>15606.456143270352</v>
-      </c>
-      <c r="CT21" s="11">
-        <f t="shared" si="27"/>
-        <v>15762.520704703056</v>
-      </c>
-      <c r="CU21" s="11">
-        <f t="shared" si="27"/>
-        <v>15920.145911750087</v>
-      </c>
-      <c r="CV21" s="11">
-        <f t="shared" si="27"/>
-        <v>16079.347370867588</v>
-      </c>
-      <c r="CW21" s="11">
-        <f t="shared" si="27"/>
-        <v>16240.140844576264</v>
-      </c>
-      <c r="CX21" s="11">
-        <f t="shared" si="27"/>
-        <v>16402.542253022028</v>
-      </c>
-      <c r="CY21" s="11">
-        <f t="shared" si="27"/>
-        <v>16566.567675552247</v>
-      </c>
-      <c r="CZ21" s="11">
-        <f t="shared" si="27"/>
-        <v>16732.233352307769</v>
-      </c>
-      <c r="DA21" s="11">
-        <f t="shared" si="27"/>
-        <v>16899.555685830848</v>
-      </c>
-      <c r="DB21" s="11">
-        <f t="shared" ref="DB21:DC21" si="28">DA21*(1+$AB$24)</f>
-        <v>17068.551242689158</v>
-      </c>
-      <c r="DC21" s="11">
-        <f t="shared" si="28"/>
-        <v>17239.23675511605</v>
+        <v>18550.721079703777</v>
       </c>
     </row>
     <row r="22" spans="2:107" x14ac:dyDescent="0.2">
@@ -2522,31 +2538,31 @@
         <v>46</v>
       </c>
       <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="29">+E8/E6</f>
+        <f t="shared" ref="E22:H22" si="28">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
       <c r="F22" s="12">
+        <f t="shared" si="28"/>
+        <v>0.76986554460911061</v>
+      </c>
+      <c r="G22" s="12">
+        <f t="shared" si="28"/>
+        <v>0.7649648197674126</v>
+      </c>
+      <c r="H22" s="12">
+        <f t="shared" si="28"/>
+        <v>0.75552025485015994</v>
+      </c>
+      <c r="I22" s="12">
+        <f t="shared" ref="I22:K22" si="29">+I8/I6</f>
+        <v>0.76586022300434775</v>
+      </c>
+      <c r="J22" s="12">
         <f t="shared" si="29"/>
-        <v>0.76986554460911061</v>
-      </c>
-      <c r="G22" s="12">
+        <v>0.79414649997854059</v>
+      </c>
+      <c r="K22" s="12">
         <f t="shared" si="29"/>
-        <v>0.7649648197674126</v>
-      </c>
-      <c r="H22" s="12">
-        <f t="shared" si="29"/>
-        <v>0.75552025485015994</v>
-      </c>
-      <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="30">+I8/I6</f>
-        <v>0.76586022300434775</v>
-      </c>
-      <c r="J22" s="12">
-        <f t="shared" si="30"/>
-        <v>0.79414649997854059</v>
-      </c>
-      <c r="K22" s="12">
-        <f t="shared" si="30"/>
         <v>0.79488747486433631</v>
       </c>
       <c r="L22" s="12">
@@ -2554,54 +2570,57 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:P22" si="31">+M8/M6</f>
+        <f t="shared" ref="M22:P22" si="30">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
+        <f t="shared" si="30"/>
+        <v>0.79387045988593929</v>
+      </c>
+      <c r="O22" s="12">
+        <f t="shared" si="30"/>
+        <v>0.79258647247121738</v>
+      </c>
+      <c r="P22" s="12">
+        <f t="shared" si="30"/>
+        <v>0.80009029168138812</v>
+      </c>
+      <c r="Q22" s="12">
+        <f t="shared" ref="Q22:R22" si="31">+Q8/Q6</f>
+        <v>0.81130190526285029</v>
+      </c>
+      <c r="R22" s="12">
         <f t="shared" si="31"/>
-        <v>0.79387045988593929</v>
-      </c>
-      <c r="O22" s="12">
-        <f t="shared" si="31"/>
-        <v>0.79258647247121738</v>
-      </c>
-      <c r="P22" s="12">
-        <f t="shared" si="31"/>
-        <v>0.80009029168138812</v>
-      </c>
-      <c r="Q22" s="12">
-        <f t="shared" ref="Q22:R22" si="32">+Q8/Q6</f>
-        <v>0.81130190526285029</v>
-      </c>
-      <c r="R22" s="12">
+        <v>0.82221796356815668</v>
+      </c>
+      <c r="S22" s="12">
+        <f t="shared" ref="S22:U22" si="32">+S8/S6</f>
+        <v>0.81988145661452783</v>
+      </c>
+      <c r="T22" s="12">
         <f t="shared" si="32"/>
-        <v>0.82221796356815668</v>
-      </c>
-      <c r="S22" s="12">
-        <f t="shared" ref="S22:U22" si="33">+S8/S6</f>
-        <v>0.81988145661452783</v>
-      </c>
-      <c r="T22" s="12">
+        <v>0.80861146883751056</v>
+      </c>
+      <c r="U22" s="12">
+        <f t="shared" si="32"/>
+        <v>0.80035825256225945</v>
+      </c>
+      <c r="V22" s="12">
+        <f t="shared" ref="V22:Y22" si="33">+V8/V6</f>
+        <v>0.80456456114524755</v>
+      </c>
+      <c r="W22" s="12">
         <f t="shared" si="33"/>
-        <v>0.80861146883751056</v>
-      </c>
-      <c r="U22" s="12">
+        <v>0.79301768885422286</v>
+      </c>
+      <c r="X22" s="12">
         <f t="shared" si="33"/>
-        <v>0.80035825256225945</v>
-      </c>
-      <c r="V22" s="12">
-        <f t="shared" ref="V22:X22" si="34">+V8/V6</f>
-        <v>0.80456456114524755</v>
-      </c>
-      <c r="W22" s="12">
-        <f t="shared" si="34"/>
-        <v>0.79301768885422286</v>
-      </c>
-      <c r="X22" s="12">
-        <f t="shared" si="34"/>
-        <v>0.8</v>
-      </c>
-      <c r="Y22" s="12"/>
+        <v>0.79930108827085844</v>
+      </c>
+      <c r="Y22" s="12">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
       <c r="Z22" s="12"/>
       <c r="AA22" s="12"/>
     </row>
@@ -2610,7 +2629,7 @@
         <v>70</v>
       </c>
       <c r="AB23" s="13">
-        <v>0.22</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="24" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2700,7 +2719,7 @@
         <v>71</v>
       </c>
       <c r="AB25" s="13">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2748,7 +2767,7 @@
       </c>
       <c r="AB26" s="14">
         <f>NPV(AB25,AE21:DC21)</f>
-        <v>70054.692271372289</v>
+        <v>63644.52081570858</v>
       </c>
     </row>
     <row r="27" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2836,7 +2855,7 @@
       </c>
       <c r="AB28" s="14">
         <f>AB26/AB27</f>
-        <v>192.94667336322303</v>
+        <v>175.29159248345695</v>
       </c>
     </row>
     <row r="29" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -2880,7 +2899,7 @@
       </c>
       <c r="AB29" s="15">
         <f>(AB28-Main!O2)/Main!O2</f>
-        <v>0.24361375032692892</v>
+        <v>0.33902369936182841</v>
       </c>
     </row>
     <row r="30" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC20909A-C594-4D27-B314-5B2B10FBF323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CFA710-C395-4EB8-93E7-DA8386C6C132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>130.91</v>
+        <v>136.68</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -819,7 +819,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>46865.78</v>
+        <v>48931.44</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -851,7 +851,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>45582.78</v>
+        <v>47648.44</v>
       </c>
     </row>
   </sheetData>
@@ -2199,27 +2199,27 @@
         <v>0.26891267432542976</v>
       </c>
       <c r="T21" s="10">
-        <f>+T6/P6-1</f>
+        <f t="shared" ref="T21:Y21" si="25">+T6/P6-1</f>
         <v>0.26659404074902837</v>
       </c>
       <c r="U21" s="10">
-        <f>+U6/Q6-1</f>
+        <f t="shared" si="25"/>
         <v>0.26022033254434418</v>
       </c>
       <c r="V21" s="10">
-        <f>+V6/R6-1</f>
+        <f t="shared" si="25"/>
         <v>0.25112906152643344</v>
       </c>
       <c r="W21" s="10">
-        <f>+W6/S6-1</f>
+        <f t="shared" si="25"/>
         <v>0.24588836373809198</v>
       </c>
       <c r="X21" s="10">
-        <f>+X6/T6-1</f>
+        <f t="shared" si="25"/>
         <v>0.28161616912994214</v>
       </c>
       <c r="Y21" s="10">
-        <f>+Y6/U6-1</f>
+        <f t="shared" si="25"/>
         <v>0.23040625144924176</v>
       </c>
       <c r="Z21" s="10"/>
@@ -2245,23 +2245,23 @@
         <v>3315.0796249999999</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" ref="AJ21:AN21" si="25">AI21*(1+$AB$23)</f>
+        <f t="shared" ref="AJ21:AN21" si="26">AI21*(1+$AB$23)</f>
         <v>4094.1233368749995</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5056.2423210406241</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6244.4592664851698</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7711.9071941091843</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>9524.2053847248408</v>
       </c>
       <c r="AO21" s="11">
@@ -2269,267 +2269,267 @@
         <v>9619.4474385720896</v>
       </c>
       <c r="AP21" s="11">
-        <f t="shared" ref="AP21:DA21" si="26">AO21*(1+$AB$24)</f>
+        <f t="shared" ref="AP21:DA21" si="27">AO21*(1+$AB$24)</f>
         <v>9715.6419129578098</v>
       </c>
       <c r="AQ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9812.7983320873882</v>
       </c>
       <c r="AR21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9910.9263154082619</v>
       </c>
       <c r="AS21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10010.035578562345</v>
       </c>
       <c r="AT21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10110.135934347969</v>
       </c>
       <c r="AU21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10211.237293691449</v>
       </c>
       <c r="AV21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10313.349666628363</v>
       </c>
       <c r="AW21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10416.483163294646</v>
       </c>
       <c r="AX21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10520.647994927593</v>
       </c>
       <c r="AY21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10625.854474876869</v>
       </c>
       <c r="AZ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10732.113019625638</v>
       </c>
       <c r="BA21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10839.434149821895</v>
       </c>
       <c r="BB21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10947.828491320113</v>
       </c>
       <c r="BC21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11057.306776233314</v>
       </c>
       <c r="BD21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11167.879843995646</v>
       </c>
       <c r="BE21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11279.558642435602</v>
       </c>
       <c r="BF21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11392.354228859958</v>
       </c>
       <c r="BG21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11506.277771148558</v>
       </c>
       <c r="BH21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11621.340548860044</v>
       </c>
       <c r="BI21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11737.553954348645</v>
       </c>
       <c r="BJ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11854.929493892132</v>
       </c>
       <c r="BK21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11973.478788831053</v>
       </c>
       <c r="BL21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12093.213576719363</v>
       </c>
       <c r="BM21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12214.145712486557</v>
       </c>
       <c r="BN21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12336.287169611423</v>
       </c>
       <c r="BO21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12459.650041307537</v>
       </c>
       <c r="BP21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12584.246541720613</v>
       </c>
       <c r="BQ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12710.08900713782</v>
       </c>
       <c r="BR21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12837.189897209199</v>
       </c>
       <c r="BS21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12965.561796181291</v>
       </c>
       <c r="BT21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13095.217414143104</v>
       </c>
       <c r="BU21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13226.169588284536</v>
       </c>
       <c r="BV21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13358.431284167382</v>
       </c>
       <c r="BW21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13492.015597009056</v>
       </c>
       <c r="BX21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13626.935752979147</v>
       </c>
       <c r="BY21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13763.205110508938</v>
       </c>
       <c r="BZ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13900.837161614027</v>
       </c>
       <c r="CA21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14039.845533230167</v>
       </c>
       <c r="CB21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14180.24398856247</v>
       </c>
       <c r="CC21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14322.046428448095</v>
       </c>
       <c r="CD21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14465.266892732576</v>
       </c>
       <c r="CE21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14609.919561659901</v>
       </c>
       <c r="CF21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14756.018757276501</v>
       </c>
       <c r="CG21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14903.578944849265</v>
       </c>
       <c r="CH21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15052.614734297758</v>
       </c>
       <c r="CI21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15203.140881640737</v>
       </c>
       <c r="CJ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15355.172290457143</v>
       </c>
       <c r="CK21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15508.724013361714</v>
       </c>
       <c r="CL21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15663.811253495331</v>
       </c>
       <c r="CM21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15820.449366030283</v>
       </c>
       <c r="CN21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15978.653859690587</v>
       </c>
       <c r="CO21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16138.440398287492</v>
       </c>
       <c r="CP21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16299.824802270366</v>
       </c>
       <c r="CQ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16462.823050293071</v>
       </c>
       <c r="CR21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16627.451280796002</v>
       </c>
       <c r="CS21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16793.72579360396</v>
       </c>
       <c r="CT21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16961.663051539999</v>
       </c>
       <c r="CU21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17131.279682055399</v>
       </c>
       <c r="CV21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17302.592478875955</v>
       </c>
       <c r="CW21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17475.618403664714</v>
       </c>
       <c r="CX21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17650.374587701361</v>
       </c>
       <c r="CY21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>17826.878333578374</v>
       </c>
       <c r="CZ21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18005.147116914159</v>
       </c>
       <c r="DA21" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18185.198588083302</v>
       </c>
       <c r="DB21" s="11">
-        <f t="shared" ref="DB21:DC21" si="27">DA21*(1+$AB$24)</f>
+        <f t="shared" ref="DB21:DC21" si="28">DA21*(1+$AB$24)</f>
         <v>18367.050573964134</v>
       </c>
       <c r="DC21" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>18550.721079703777</v>
       </c>
     </row>
@@ -2538,31 +2538,31 @@
         <v>46</v>
       </c>
       <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="28">+E8/E6</f>
+        <f t="shared" ref="E22:H22" si="29">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.76986554460911061</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.7649648197674126</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.75552025485015994</v>
       </c>
       <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="29">+I8/I6</f>
+        <f t="shared" ref="I22:K22" si="30">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.79414649997854059</v>
       </c>
       <c r="K22" s="12">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.79488747486433631</v>
       </c>
       <c r="L22" s="12">
@@ -2570,55 +2570,55 @@
         <v>0.79828284967178642</v>
       </c>
       <c r="M22" s="12">
-        <f t="shared" ref="M22:P22" si="30">+M8/M6</f>
+        <f t="shared" ref="M22:P22" si="31">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.79387045988593929</v>
       </c>
       <c r="O22" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.79258647247121738</v>
       </c>
       <c r="P22" s="12">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.80009029168138812</v>
       </c>
       <c r="Q22" s="12">
-        <f t="shared" ref="Q22:R22" si="31">+Q8/Q6</f>
+        <f t="shared" ref="Q22:R22" si="32">+Q8/Q6</f>
         <v>0.81130190526285029</v>
       </c>
       <c r="R22" s="12">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.82221796356815668</v>
       </c>
       <c r="S22" s="12">
-        <f t="shared" ref="S22:U22" si="32">+S8/S6</f>
+        <f t="shared" ref="S22:U22" si="33">+S8/S6</f>
         <v>0.81988145661452783</v>
       </c>
       <c r="T22" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.80861146883751056</v>
       </c>
       <c r="U22" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.80035825256225945</v>
       </c>
       <c r="V22" s="12">
-        <f t="shared" ref="V22:Y22" si="33">+V8/V6</f>
+        <f t="shared" ref="V22:Y22" si="34">+V8/V6</f>
         <v>0.80456456114524755</v>
       </c>
       <c r="W22" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.79301768885422286</v>
       </c>
       <c r="X22" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.79930108827085844</v>
       </c>
       <c r="Y22" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Z22" s="12"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB29" s="15">
         <f>(AB28-Main!O2)/Main!O2</f>
-        <v>0.33902369936182841</v>
+        <v>0.2824962868265799</v>
       </c>
     </row>
     <row r="30" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">

--- a/DDOG.xlsx
+++ b/DDOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CFA710-C395-4EB8-93E7-DA8386C6C132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F79D74-5E11-4A78-AC10-E46C91D089C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
+    <workbookView xWindow="2730" yWindow="75" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{3FD86B5C-07F1-42A4-9D66-8FB9C4BAF175}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
   <si>
     <t>Price</t>
   </si>
@@ -302,6 +302,18 @@
   </si>
   <si>
     <t>Delta</t>
+  </si>
+  <si>
+    <t>FCF</t>
+  </si>
+  <si>
+    <t>FCF Growth %</t>
+  </si>
+  <si>
+    <t>DCF using FCF</t>
+  </si>
+  <si>
+    <t>Revenue -&gt; FCF Conversion</t>
   </si>
 </sst>
 </file>
@@ -362,7 +374,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -394,6 +406,9 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -428,7 +443,7 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>40297</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>151668</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -799,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="1">
-        <v>136.68</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="3" spans="14:16" x14ac:dyDescent="0.2">
@@ -819,7 +834,7 @@
       </c>
       <c r="O4" s="5">
         <f>+O2*O3</f>
-        <v>48931.44</v>
+        <v>56474.5</v>
       </c>
     </row>
     <row r="5" spans="14:16" x14ac:dyDescent="0.2">
@@ -851,7 +866,7 @@
       </c>
       <c r="O7" s="5">
         <f>+O4-O5+O6</f>
-        <v>47648.44</v>
+        <v>55191.5</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB5D0F6-F818-4D6B-9D91-E5CB5E0CBE0F}">
-  <dimension ref="A1:DC54"/>
+  <dimension ref="A1:DC57"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -2135,7 +2150,7 @@
       <c r="AA19" s="6"/>
       <c r="AI19" s="16">
         <f>(AI20-AI21)/AI21</f>
-        <v>5.7928472834197734E-4</v>
+        <v>4.6466801947173206E-3</v>
       </c>
     </row>
     <row r="20" spans="2:107" x14ac:dyDescent="0.2">
@@ -2241,538 +2256,497 @@
         <v>2684.2750000000001</v>
       </c>
       <c r="AI21" s="3">
-        <f>AH21*(1+$AB$23)</f>
-        <v>3315.0796249999999</v>
+        <f t="shared" ref="AI21:AN21" si="26">AH21*(1+$AB$29)</f>
+        <v>3301.65825</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" ref="AJ21:AN21" si="26">AI21*(1+$AB$23)</f>
-        <v>4094.1233368749995</v>
+        <f t="shared" si="26"/>
+        <v>4061.0396474999998</v>
       </c>
       <c r="AK21" s="3">
         <f t="shared" si="26"/>
-        <v>5056.2423210406241</v>
+        <v>4995.0787664249992</v>
       </c>
       <c r="AL21" s="3">
         <f t="shared" si="26"/>
-        <v>6244.4592664851698</v>
+        <v>6143.9468827027486</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="26"/>
-        <v>7711.9071941091843</v>
+        <v>7557.0546657243804</v>
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="26"/>
-        <v>9524.2053847248408</v>
+        <v>9295.1772388409881</v>
       </c>
       <c r="AO21" s="11">
-        <f>AN21*(1+$AB$24)</f>
-        <v>9619.4474385720896</v>
+        <f t="shared" ref="AO21:BT21" si="27">AN21*(1+$AB$30)</f>
+        <v>9388.1290112293973</v>
       </c>
       <c r="AP21" s="11">
-        <f t="shared" ref="AP21:DA21" si="27">AO21*(1+$AB$24)</f>
-        <v>9715.6419129578098</v>
+        <f t="shared" si="27"/>
+        <v>9482.010301341692</v>
       </c>
       <c r="AQ21" s="11">
         <f t="shared" si="27"/>
-        <v>9812.7983320873882</v>
+        <v>9576.8304043551088</v>
       </c>
       <c r="AR21" s="11">
         <f t="shared" si="27"/>
-        <v>9910.9263154082619</v>
+        <v>9672.5987083986602</v>
       </c>
       <c r="AS21" s="11">
         <f t="shared" si="27"/>
-        <v>10010.035578562345</v>
+        <v>9769.3246954826463</v>
       </c>
       <c r="AT21" s="11">
         <f t="shared" si="27"/>
-        <v>10110.135934347969</v>
+        <v>9867.0179424374728</v>
       </c>
       <c r="AU21" s="11">
         <f t="shared" si="27"/>
-        <v>10211.237293691449</v>
+        <v>9965.6881218618473</v>
       </c>
       <c r="AV21" s="11">
         <f t="shared" si="27"/>
-        <v>10313.349666628363</v>
+        <v>10065.345003080465</v>
       </c>
       <c r="AW21" s="11">
         <f t="shared" si="27"/>
-        <v>10416.483163294646</v>
+        <v>10165.99845311127</v>
       </c>
       <c r="AX21" s="11">
         <f t="shared" si="27"/>
-        <v>10520.647994927593</v>
+        <v>10267.658437642382</v>
       </c>
       <c r="AY21" s="11">
         <f t="shared" si="27"/>
-        <v>10625.854474876869</v>
+        <v>10370.335022018806</v>
       </c>
       <c r="AZ21" s="11">
         <f t="shared" si="27"/>
-        <v>10732.113019625638</v>
+        <v>10474.038372238994</v>
       </c>
       <c r="BA21" s="11">
         <f t="shared" si="27"/>
-        <v>10839.434149821895</v>
+        <v>10578.778755961384</v>
       </c>
       <c r="BB21" s="11">
         <f t="shared" si="27"/>
-        <v>10947.828491320113</v>
+        <v>10684.566543520998</v>
       </c>
       <c r="BC21" s="11">
         <f t="shared" si="27"/>
-        <v>11057.306776233314</v>
+        <v>10791.412208956208</v>
       </c>
       <c r="BD21" s="11">
         <f t="shared" si="27"/>
-        <v>11167.879843995646</v>
+        <v>10899.32633104577</v>
       </c>
       <c r="BE21" s="11">
         <f t="shared" si="27"/>
-        <v>11279.558642435602</v>
+        <v>11008.319594356228</v>
       </c>
       <c r="BF21" s="11">
         <f t="shared" si="27"/>
-        <v>11392.354228859958</v>
+        <v>11118.40279029979</v>
       </c>
       <c r="BG21" s="11">
         <f t="shared" si="27"/>
-        <v>11506.277771148558</v>
+        <v>11229.586818202788</v>
       </c>
       <c r="BH21" s="11">
         <f t="shared" si="27"/>
-        <v>11621.340548860044</v>
+        <v>11341.882686384815</v>
       </c>
       <c r="BI21" s="11">
         <f t="shared" si="27"/>
-        <v>11737.553954348645</v>
+        <v>11455.301513248663</v>
       </c>
       <c r="BJ21" s="11">
         <f t="shared" si="27"/>
-        <v>11854.929493892132</v>
+        <v>11569.854528381151</v>
       </c>
       <c r="BK21" s="11">
         <f t="shared" si="27"/>
-        <v>11973.478788831053</v>
+        <v>11685.553073664962</v>
       </c>
       <c r="BL21" s="11">
         <f t="shared" si="27"/>
-        <v>12093.213576719363</v>
+        <v>11802.408604401611</v>
       </c>
       <c r="BM21" s="11">
         <f t="shared" si="27"/>
-        <v>12214.145712486557</v>
+        <v>11920.432690445627</v>
       </c>
       <c r="BN21" s="11">
         <f t="shared" si="27"/>
-        <v>12336.287169611423</v>
+        <v>12039.637017350084</v>
       </c>
       <c r="BO21" s="11">
         <f t="shared" si="27"/>
-        <v>12459.650041307537</v>
+        <v>12160.033387523585</v>
       </c>
       <c r="BP21" s="11">
         <f t="shared" si="27"/>
-        <v>12584.246541720613</v>
+        <v>12281.633721398821</v>
       </c>
       <c r="BQ21" s="11">
         <f t="shared" si="27"/>
-        <v>12710.08900713782</v>
+        <v>12404.450058612809</v>
       </c>
       <c r="BR21" s="11">
         <f t="shared" si="27"/>
-        <v>12837.189897209199</v>
+        <v>12528.494559198936</v>
       </c>
       <c r="BS21" s="11">
         <f t="shared" si="27"/>
-        <v>12965.561796181291</v>
+        <v>12653.779504790926</v>
       </c>
       <c r="BT21" s="11">
         <f t="shared" si="27"/>
-        <v>13095.217414143104</v>
+        <v>12780.317299838835</v>
       </c>
       <c r="BU21" s="11">
-        <f t="shared" si="27"/>
-        <v>13226.169588284536</v>
+        <f t="shared" ref="BU21:DC21" si="28">BT21*(1+$AB$30)</f>
+        <v>12908.120472837223</v>
       </c>
       <c r="BV21" s="11">
-        <f t="shared" si="27"/>
-        <v>13358.431284167382</v>
+        <f t="shared" si="28"/>
+        <v>13037.201677565596</v>
       </c>
       <c r="BW21" s="11">
-        <f t="shared" si="27"/>
-        <v>13492.015597009056</v>
+        <f t="shared" si="28"/>
+        <v>13167.573694341252</v>
       </c>
       <c r="BX21" s="11">
-        <f t="shared" si="27"/>
-        <v>13626.935752979147</v>
+        <f t="shared" si="28"/>
+        <v>13299.249431284665</v>
       </c>
       <c r="BY21" s="11">
-        <f t="shared" si="27"/>
-        <v>13763.205110508938</v>
+        <f t="shared" si="28"/>
+        <v>13432.241925597511</v>
       </c>
       <c r="BZ21" s="11">
-        <f t="shared" si="27"/>
-        <v>13900.837161614027</v>
+        <f t="shared" si="28"/>
+        <v>13566.564344853487</v>
       </c>
       <c r="CA21" s="11">
-        <f t="shared" si="27"/>
-        <v>14039.845533230167</v>
+        <f t="shared" si="28"/>
+        <v>13702.229988302022</v>
       </c>
       <c r="CB21" s="11">
-        <f t="shared" si="27"/>
-        <v>14180.24398856247</v>
+        <f t="shared" si="28"/>
+        <v>13839.252288185042</v>
       </c>
       <c r="CC21" s="11">
-        <f t="shared" si="27"/>
-        <v>14322.046428448095</v>
+        <f t="shared" si="28"/>
+        <v>13977.644811066892</v>
       </c>
       <c r="CD21" s="11">
-        <f t="shared" si="27"/>
-        <v>14465.266892732576</v>
+        <f t="shared" si="28"/>
+        <v>14117.421259177561</v>
       </c>
       <c r="CE21" s="11">
-        <f t="shared" si="27"/>
-        <v>14609.919561659901</v>
+        <f t="shared" si="28"/>
+        <v>14258.595471769337</v>
       </c>
       <c r="CF21" s="11">
-        <f t="shared" si="27"/>
-        <v>14756.018757276501</v>
+        <f t="shared" si="28"/>
+        <v>14401.18142648703</v>
       </c>
       <c r="CG21" s="11">
-        <f t="shared" si="27"/>
-        <v>14903.578944849265</v>
+        <f t="shared" si="28"/>
+        <v>14545.1932407519</v>
       </c>
       <c r="CH21" s="11">
-        <f t="shared" si="27"/>
-        <v>15052.614734297758</v>
+        <f t="shared" si="28"/>
+        <v>14690.645173159419</v>
       </c>
       <c r="CI21" s="11">
-        <f t="shared" si="27"/>
-        <v>15203.140881640737</v>
+        <f t="shared" si="28"/>
+        <v>14837.551624891013</v>
       </c>
       <c r="CJ21" s="11">
-        <f t="shared" si="27"/>
-        <v>15355.172290457143</v>
+        <f t="shared" si="28"/>
+        <v>14985.927141139924</v>
       </c>
       <c r="CK21" s="11">
-        <f t="shared" si="27"/>
-        <v>15508.724013361714</v>
+        <f t="shared" si="28"/>
+        <v>15135.786412551324</v>
       </c>
       <c r="CL21" s="11">
-        <f t="shared" si="27"/>
-        <v>15663.811253495331</v>
+        <f t="shared" si="28"/>
+        <v>15287.144276676838</v>
       </c>
       <c r="CM21" s="11">
-        <f t="shared" si="27"/>
-        <v>15820.449366030283</v>
+        <f t="shared" si="28"/>
+        <v>15440.015719443607</v>
       </c>
       <c r="CN21" s="11">
-        <f t="shared" si="27"/>
-        <v>15978.653859690587</v>
+        <f t="shared" si="28"/>
+        <v>15594.415876638042</v>
       </c>
       <c r="CO21" s="11">
-        <f t="shared" si="27"/>
-        <v>16138.440398287492</v>
+        <f t="shared" si="28"/>
+        <v>15750.360035404423</v>
       </c>
       <c r="CP21" s="11">
-        <f t="shared" si="27"/>
-        <v>16299.824802270366</v>
+        <f t="shared" si="28"/>
+        <v>15907.863635758467</v>
       </c>
       <c r="CQ21" s="11">
-        <f t="shared" si="27"/>
-        <v>16462.823050293071</v>
+        <f t="shared" si="28"/>
+        <v>16066.942272116052</v>
       </c>
       <c r="CR21" s="11">
-        <f t="shared" si="27"/>
-        <v>16627.451280796002</v>
+        <f t="shared" si="28"/>
+        <v>16227.611694837213</v>
       </c>
       <c r="CS21" s="11">
-        <f t="shared" si="27"/>
-        <v>16793.72579360396</v>
+        <f t="shared" si="28"/>
+        <v>16389.887811785586</v>
       </c>
       <c r="CT21" s="11">
-        <f t="shared" si="27"/>
-        <v>16961.663051539999</v>
+        <f t="shared" si="28"/>
+        <v>16553.786689903442</v>
       </c>
       <c r="CU21" s="11">
-        <f t="shared" si="27"/>
-        <v>17131.279682055399</v>
+        <f t="shared" si="28"/>
+        <v>16719.324556802476</v>
       </c>
       <c r="CV21" s="11">
-        <f t="shared" si="27"/>
-        <v>17302.592478875955</v>
+        <f t="shared" si="28"/>
+        <v>16886.517802370501</v>
       </c>
       <c r="CW21" s="11">
-        <f t="shared" si="27"/>
-        <v>17475.618403664714</v>
+        <f t="shared" si="28"/>
+        <v>17055.382980394206</v>
       </c>
       <c r="CX21" s="11">
-        <f t="shared" si="27"/>
-        <v>17650.374587701361</v>
+        <f t="shared" si="28"/>
+        <v>17225.936810198149</v>
       </c>
       <c r="CY21" s="11">
-        <f t="shared" si="27"/>
-        <v>17826.878333578374</v>
+        <f t="shared" si="28"/>
+        <v>17398.196178300132</v>
       </c>
       <c r="CZ21" s="11">
-        <f t="shared" si="27"/>
-        <v>18005.147116914159</v>
+        <f t="shared" si="28"/>
+        <v>17572.178140083131</v>
       </c>
       <c r="DA21" s="11">
-        <f t="shared" si="27"/>
-        <v>18185.198588083302</v>
+        <f t="shared" si="28"/>
+        <v>17747.899921483964</v>
       </c>
       <c r="DB21" s="11">
-        <f t="shared" ref="DB21:DC21" si="28">DA21*(1+$AB$24)</f>
-        <v>18367.050573964134</v>
+        <f t="shared" si="28"/>
+        <v>17925.378920698804</v>
       </c>
       <c r="DC21" s="11">
         <f t="shared" si="28"/>
-        <v>18550.721079703777</v>
-      </c>
-    </row>
-    <row r="22" spans="2:107" x14ac:dyDescent="0.2">
-      <c r="B22" s="5" t="s">
+        <v>18104.632709905793</v>
+      </c>
+    </row>
+    <row r="22" spans="2:107" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+    </row>
+    <row r="23" spans="2:107" x14ac:dyDescent="0.2">
+      <c r="B23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="12">
-        <f t="shared" ref="E22:H22" si="29">+E8/E6</f>
+      <c r="E23" s="12">
+        <f t="shared" ref="E23:H23" si="29">+E8/E6</f>
         <v>0.78028770001616288</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F23" s="12">
         <f t="shared" si="29"/>
         <v>0.76986554460911061</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G23" s="12">
         <f t="shared" si="29"/>
         <v>0.7649648197674126</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H23" s="12">
         <f t="shared" si="29"/>
         <v>0.75552025485015994</v>
       </c>
-      <c r="I22" s="12">
-        <f t="shared" ref="I22:K22" si="30">+I8/I6</f>
+      <c r="I23" s="12">
+        <f t="shared" ref="I23:K23" si="30">+I8/I6</f>
         <v>0.76586022300434775</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J23" s="12">
         <f t="shared" si="30"/>
         <v>0.79414649997854059</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K23" s="12">
         <f t="shared" si="30"/>
         <v>0.79488747486433631</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L23" s="12">
         <f>+L8/L6</f>
         <v>0.79828284967178642</v>
       </c>
-      <c r="M22" s="12">
-        <f t="shared" ref="M22:P22" si="31">+M8/M6</f>
+      <c r="M23" s="12">
+        <f t="shared" ref="M23:P23" si="31">+M8/M6</f>
         <v>0.78558551129009724</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N23" s="12">
         <f t="shared" si="31"/>
         <v>0.79387045988593929</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O23" s="12">
         <f t="shared" si="31"/>
         <v>0.79258647247121738</v>
       </c>
-      <c r="P22" s="12">
+      <c r="P23" s="12">
         <f t="shared" si="31"/>
         <v>0.80009029168138812</v>
       </c>
-      <c r="Q22" s="12">
-        <f t="shared" ref="Q22:R22" si="32">+Q8/Q6</f>
+      <c r="Q23" s="12">
+        <f t="shared" ref="Q23:R23" si="32">+Q8/Q6</f>
         <v>0.81130190526285029</v>
       </c>
-      <c r="R22" s="12">
+      <c r="R23" s="12">
         <f t="shared" si="32"/>
         <v>0.82221796356815668</v>
       </c>
-      <c r="S22" s="12">
-        <f t="shared" ref="S22:U22" si="33">+S8/S6</f>
+      <c r="S23" s="12">
+        <f t="shared" ref="S23:U23" si="33">+S8/S6</f>
         <v>0.81988145661452783</v>
       </c>
-      <c r="T22" s="12">
+      <c r="T23" s="12">
         <f t="shared" si="33"/>
         <v>0.80861146883751056</v>
       </c>
-      <c r="U22" s="12">
+      <c r="U23" s="12">
         <f t="shared" si="33"/>
         <v>0.80035825256225945</v>
       </c>
-      <c r="V22" s="12">
-        <f t="shared" ref="V22:Y22" si="34">+V8/V6</f>
+      <c r="V23" s="12">
+        <f t="shared" ref="V23:Y23" si="34">+V8/V6</f>
         <v>0.80456456114524755</v>
       </c>
-      <c r="W22" s="12">
+      <c r="W23" s="12">
         <f t="shared" si="34"/>
         <v>0.79301768885422286</v>
       </c>
-      <c r="X22" s="12">
+      <c r="X23" s="12">
         <f t="shared" si="34"/>
         <v>0.79930108827085844</v>
       </c>
-      <c r="Y22" s="12">
+      <c r="Y23" s="12">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="Z22" s="12"/>
-      <c r="AA22" s="12"/>
-    </row>
-    <row r="23" spans="2:107" x14ac:dyDescent="0.2">
-      <c r="AA23" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB23" s="13">
-        <v>0.23499999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AD23">
+        <v>83.207999999999998</v>
+      </c>
+      <c r="AE23">
+        <v>250.52</v>
+      </c>
+      <c r="AF23">
+        <v>353.51799999999997</v>
+      </c>
+      <c r="AG23">
+        <v>597.5</v>
+      </c>
+      <c r="AH23">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="24" spans="2:107" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6">
-        <f>271.686+1399.323+3.424</f>
-        <v>1674.433</v>
-      </c>
-      <c r="L24" s="6">
-        <f>238.859+1464.681+3.214</f>
-        <v>1706.7539999999999</v>
-      </c>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6">
-        <f>282.218+2499.151</f>
-        <v>2781.3689999999997</v>
-      </c>
-      <c r="T24" s="6">
-        <f>410.963+2549.143</f>
-        <v>2960.1060000000002</v>
-      </c>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB24" s="13">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="25" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+      <c r="AE24" s="13">
+        <f>(AE23-AD23)/AD23</f>
+        <v>2.0107681953658303</v>
+      </c>
+      <c r="AF24" s="13">
+        <f>(AF23-AE23)/AE23</f>
+        <v>0.41113683538240442</v>
+      </c>
+      <c r="AG24" s="13">
+        <f>(AG23-AF23)/AF23</f>
+        <v>0.69015439100696441</v>
+      </c>
+      <c r="AH24" s="13">
+        <f>(AH23-AG23)/AG23</f>
+        <v>0.29707112970711297</v>
+      </c>
+    </row>
+    <row r="25" spans="2:107" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6">
-        <v>275.34199999999998</v>
-      </c>
-      <c r="L25" s="6">
-        <v>305.50099999999998</v>
-      </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6">
-        <v>451.05700000000002</v>
-      </c>
-      <c r="T25" s="6">
-        <v>533.29200000000003</v>
-      </c>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB25" s="13">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6">
-        <f>24.688+42.753</f>
-        <v>67.441000000000003</v>
-      </c>
-      <c r="L26" s="6">
-        <f>27.345+46.84</f>
-        <v>74.185000000000002</v>
-      </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6">
-        <f>46.391+73.067</f>
-        <v>119.458</v>
-      </c>
-      <c r="T26" s="6">
-        <f>49.518+77.04</f>
-        <v>126.55800000000001</v>
-      </c>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB26" s="14">
-        <f>NPV(AB25,AE21:DC21)</f>
-        <v>63644.52081570858</v>
-      </c>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="2:107" x14ac:dyDescent="0.2">
+      <c r="B26" s="5"/>
     </row>
     <row r="27" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -2783,10 +2757,12 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6">
-        <v>32.631999999999998</v>
+        <f>271.686+1399.323+3.424</f>
+        <v>1674.433</v>
       </c>
       <c r="L27" s="6">
-        <v>33.201999999999998</v>
+        <f>238.859+1464.681+3.214</f>
+        <v>1706.7539999999999</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
@@ -2795,10 +2771,12 @@
       <c r="Q27" s="6"/>
       <c r="R27" s="6"/>
       <c r="S27" s="6">
-        <v>54.845999999999997</v>
+        <f>282.218+2499.151</f>
+        <v>2781.3689999999997</v>
       </c>
       <c r="T27" s="6">
-        <v>49.173999999999999</v>
+        <f>410.963+2549.143</f>
+        <v>2960.1060000000002</v>
       </c>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
@@ -2806,17 +2784,10 @@
       <c r="X27" s="6"/>
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
-      <c r="AA27" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="5">
-        <f>W19</f>
-        <v>363.07799999999997</v>
-      </c>
     </row>
     <row r="28" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -2827,10 +2798,10 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6">
-        <v>90.712999999999994</v>
+        <v>275.34199999999998</v>
       </c>
       <c r="L28" s="6">
-        <v>97.790999999999997</v>
+        <v>305.50099999999998</v>
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
@@ -2839,10 +2810,10 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="6">
-        <v>182.41900000000001</v>
+        <v>451.05700000000002</v>
       </c>
       <c r="T28" s="6">
-        <v>198.911</v>
+        <v>533.29200000000003</v>
       </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
@@ -2850,17 +2821,10 @@
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
-      <c r="AA28" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB28" s="14">
-        <f>AB26/AB27</f>
-        <v>175.29159248345695</v>
-      </c>
     </row>
     <row r="29" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -2871,10 +2835,12 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6">
-        <v>61.920999999999999</v>
+        <f>24.688+42.753</f>
+        <v>67.441000000000003</v>
       </c>
       <c r="L29" s="6">
-        <v>64.016000000000005</v>
+        <f>27.345+46.84</f>
+        <v>74.185000000000002</v>
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
@@ -2883,10 +2849,12 @@
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
       <c r="S29" s="6">
-        <v>173.27</v>
+        <f>46.391+73.067</f>
+        <v>119.458</v>
       </c>
       <c r="T29" s="6">
-        <v>166.941</v>
+        <f>49.518+77.04</f>
+        <v>126.55800000000001</v>
       </c>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
@@ -2894,17 +2862,16 @@
       <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
-      <c r="AA29" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB29" s="15">
-        <f>(AB28-Main!O2)/Main!O2</f>
-        <v>0.2824962868265799</v>
+      <c r="AA29" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB29" s="13">
+        <v>0.23</v>
       </c>
     </row>
     <row r="30" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -2915,12 +2882,10 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6">
-        <f>292.032+14.088</f>
-        <v>306.12</v>
+        <v>32.631999999999998</v>
       </c>
       <c r="L30" s="6">
-        <f>334.687+17.96</f>
-        <v>352.64699999999999</v>
+        <v>33.201999999999998</v>
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
@@ -2929,12 +2894,10 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="6">
-        <f>351.437+7.312</f>
-        <v>358.74900000000002</v>
+        <v>54.845999999999997</v>
       </c>
       <c r="T30" s="6">
-        <f>350.864+5.804</f>
-        <v>356.66799999999995</v>
+        <v>49.173999999999999</v>
       </c>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
@@ -2942,10 +2905,16 @@
       <c r="X30" s="6"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="6"/>
+      <c r="AA30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB30" s="13">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="31" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -2956,10 +2925,10 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6">
-        <v>20.413</v>
+        <v>90.712999999999994</v>
       </c>
       <c r="L31" s="6">
-        <v>20.390999999999998</v>
+        <v>97.790999999999997</v>
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
@@ -2968,10 +2937,10 @@
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
       <c r="S31" s="6">
-        <v>20.297999999999998</v>
+        <v>182.41900000000001</v>
       </c>
       <c r="T31" s="6">
-        <v>20.741</v>
+        <v>198.911</v>
       </c>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
@@ -2979,10 +2948,16 @@
       <c r="X31" s="6"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
+      <c r="AA31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="32" spans="2:107" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -2993,12 +2968,10 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6">
-        <f>SUM(K24:K31)</f>
-        <v>2529.0149999999999</v>
+        <v>61.920999999999999</v>
       </c>
       <c r="L32" s="6">
-        <f>SUM(L24:L31)</f>
-        <v>2654.4870000000001</v>
+        <v>64.016000000000005</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
@@ -3007,12 +2980,10 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6">
-        <f>SUM(S24:S31)</f>
-        <v>4141.4659999999994</v>
+        <v>173.27</v>
       </c>
       <c r="T32" s="6">
-        <f>SUM(T24:T31)</f>
-        <v>4412.3909999999996</v>
+        <v>166.941</v>
       </c>
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
@@ -3020,11 +2991,65 @@
       <c r="X32" s="6"/>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
-      <c r="AA32" s="6"/>
-    </row>
-    <row r="34" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB32" s="14">
+        <f>NPV(AB31,AE21:DC21)</f>
+        <v>62397.590770116811</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6">
+        <f>292.032+14.088</f>
+        <v>306.12</v>
+      </c>
+      <c r="L33" s="6">
+        <f>334.687+17.96</f>
+        <v>352.64699999999999</v>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6">
+        <f>351.437+7.312</f>
+        <v>358.74900000000002</v>
+      </c>
+      <c r="T33" s="6">
+        <f>350.864+5.804</f>
+        <v>356.66799999999995</v>
+      </c>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="5">
+        <f>W19</f>
+        <v>363.07799999999997</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -3035,10 +3060,10 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6">
-        <v>18.629000000000001</v>
+        <v>20.413</v>
       </c>
       <c r="L34" s="6">
-        <v>47.65</v>
+        <v>20.390999999999998</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
@@ -3047,10 +3072,10 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6">
-        <v>64.316000000000003</v>
+        <v>20.297999999999998</v>
       </c>
       <c r="T34" s="6">
-        <v>115.991</v>
+        <v>20.741</v>
       </c>
       <c r="U34" s="6"/>
       <c r="V34" s="6"/>
@@ -3058,11 +3083,17 @@
       <c r="X34" s="6"/>
       <c r="Y34" s="6"/>
       <c r="Z34" s="6"/>
-      <c r="AA34" s="6"/>
-    </row>
-    <row r="35" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB34" s="14">
+        <f>AB32/AB33</f>
+        <v>171.8572614427666</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -3073,10 +3104,12 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6">
-        <v>108.211</v>
+        <f>SUM(K27:K34)</f>
+        <v>2529.0149999999999</v>
       </c>
       <c r="L35" s="6">
-        <v>111.622</v>
+        <f>SUM(L27:L34)</f>
+        <v>2654.4870000000001</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
@@ -3085,10 +3118,12 @@
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
       <c r="S35" s="6">
-        <v>117.41200000000001</v>
+        <f>SUM(S27:S34)</f>
+        <v>4141.4659999999994</v>
       </c>
       <c r="T35" s="6">
-        <v>104.791</v>
+        <f>SUM(T27:T34)</f>
+        <v>4412.3909999999996</v>
       </c>
       <c r="U35" s="6"/>
       <c r="V35" s="6"/>
@@ -3096,53 +3131,21 @@
       <c r="X35" s="6"/>
       <c r="Y35" s="6"/>
       <c r="Z35" s="6"/>
-      <c r="AA35" s="6"/>
-    </row>
-    <row r="36" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6">
-        <f>20.32+51.817</f>
-        <v>72.137</v>
-      </c>
-      <c r="L36" s="6">
-        <f>22.357+51.771</f>
-        <v>74.128</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6">
-        <f>23.591+190.891</f>
-        <v>214.482</v>
-      </c>
-      <c r="T36" s="6">
-        <f>24.565+193.835</f>
-        <v>218.4</v>
-      </c>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="6"/>
-    </row>
-    <row r="37" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB35" s="15">
+        <f>(AB34-Main!O2)/Main!O2</f>
+        <v>8.9427964771896032E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+    </row>
+    <row r="37" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -3153,12 +3156,10 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6">
-        <f>454.812+12.798</f>
-        <v>467.61</v>
+        <v>18.629000000000001</v>
       </c>
       <c r="L37" s="6">
-        <f>444.247+14.526</f>
-        <v>458.77300000000002</v>
+        <v>47.65</v>
       </c>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
@@ -3167,12 +3168,10 @@
       <c r="Q37" s="6"/>
       <c r="R37" s="6"/>
       <c r="S37" s="6">
-        <f>767.474+26.191</f>
-        <v>793.66500000000008</v>
+        <v>64.316000000000003</v>
       </c>
       <c r="T37" s="6">
-        <f>801.562+14.049</f>
-        <v>815.61099999999999</v>
+        <v>115.991</v>
       </c>
       <c r="U37" s="6"/>
       <c r="V37" s="6"/>
@@ -3182,9 +3181,9 @@
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
     </row>
-    <row r="38" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="5" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -3195,10 +3194,10 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6">
-        <v>736.31799999999998</v>
+        <v>108.211</v>
       </c>
       <c r="L38" s="6">
-        <v>737.16</v>
+        <v>111.622</v>
       </c>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
@@ -3207,10 +3206,10 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="6">
-        <v>743.08500000000004</v>
+        <v>117.41200000000001</v>
       </c>
       <c r="T38" s="6">
-        <v>743.97</v>
+        <v>104.791</v>
       </c>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
@@ -3220,9 +3219,9 @@
       <c r="Z38" s="6"/>
       <c r="AA38" s="6"/>
     </row>
-    <row r="39" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
@@ -3233,10 +3232,12 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
       <c r="K39" s="6">
-        <v>9.2530000000000001</v>
+        <f>20.32+51.817</f>
+        <v>72.137</v>
       </c>
       <c r="L39" s="6">
-        <v>10.034000000000001</v>
+        <f>22.357+51.771</f>
+        <v>74.128</v>
       </c>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
@@ -3245,10 +3246,12 @@
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
       <c r="S39" s="6">
-        <v>6.1509999999999998</v>
+        <f>23.591+190.891</f>
+        <v>214.482</v>
       </c>
       <c r="T39" s="6">
-        <v>6.32</v>
+        <f>24.565+193.835</f>
+        <v>218.4</v>
       </c>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
@@ -3256,11 +3259,13 @@
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
-      <c r="AA39" s="6"/>
-    </row>
-    <row r="40" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA39" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
@@ -3271,10 +3276,12 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6">
-        <v>1116.857</v>
+        <f>454.812+12.798</f>
+        <v>467.61</v>
       </c>
       <c r="L40" s="6">
-        <v>1215.1199999999999</v>
+        <f>444.247+14.526</f>
+        <v>458.77300000000002</v>
       </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
@@ -3283,10 +3290,12 @@
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="6">
-        <v>2202.355</v>
+        <f>767.474+26.191</f>
+        <v>793.66500000000008</v>
       </c>
       <c r="T40" s="6">
-        <v>2407.308</v>
+        <f>801.562+14.049</f>
+        <v>815.61099999999999</v>
       </c>
       <c r="U40" s="6"/>
       <c r="V40" s="6"/>
@@ -3294,11 +3303,13 @@
       <c r="X40" s="6"/>
       <c r="Y40" s="6"/>
       <c r="Z40" s="6"/>
-      <c r="AA40" s="6"/>
-    </row>
-    <row r="41" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AA40" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
@@ -3309,12 +3320,10 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6">
-        <f>SUM(K34:K40)</f>
-        <v>2529.0149999999999</v>
+        <v>736.31799999999998</v>
       </c>
       <c r="L41" s="6">
-        <f>SUM(L34:L40)</f>
-        <v>2654.4870000000001</v>
+        <v>737.16</v>
       </c>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
@@ -3323,12 +3332,10 @@
       <c r="Q41" s="6"/>
       <c r="R41" s="6"/>
       <c r="S41" s="6">
-        <f>SUM(S34:S40)</f>
-        <v>4141.4660000000003</v>
+        <v>743.08500000000004</v>
       </c>
       <c r="T41" s="6">
-        <f>SUM(T34:T40)</f>
-        <v>4412.3909999999996</v>
+        <v>743.97</v>
       </c>
       <c r="U41" s="6"/>
       <c r="V41" s="6"/>
@@ -3338,9 +3345,47 @@
       <c r="Z41" s="6"/>
       <c r="AA41" s="6"/>
     </row>
-    <row r="43" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6">
+        <v>9.2530000000000001</v>
+      </c>
+      <c r="L42" s="6">
+        <v>10.034000000000001</v>
+      </c>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6">
+        <v>6.1509999999999998</v>
+      </c>
+      <c r="T42" s="6">
+        <v>6.32</v>
+      </c>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+    </row>
+    <row r="43" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -3351,10 +3396,11 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6">
-        <f>+K17</f>
-        <v>9.7379999999999889</v>
-      </c>
-      <c r="L43" s="6"/>
+        <v>1116.857</v>
+      </c>
+      <c r="L43" s="6">
+        <v>1215.1199999999999</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
@@ -3362,12 +3408,10 @@
       <c r="Q43" s="6"/>
       <c r="R43" s="6"/>
       <c r="S43" s="6">
-        <f>+S17</f>
-        <v>42.631000000000036</v>
+        <v>2202.355</v>
       </c>
       <c r="T43" s="6">
-        <f>+T17</f>
-        <v>43.823999999999998</v>
+        <v>2407.308</v>
       </c>
       <c r="U43" s="6"/>
       <c r="V43" s="6"/>
@@ -3377,9 +3421,9 @@
       <c r="Z43" s="6"/>
       <c r="AA43" s="6"/>
     </row>
-    <row r="44" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
@@ -3390,9 +3434,13 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="6">
-        <v>9.7379999999999995</v>
-      </c>
-      <c r="L44" s="6"/>
+        <f>SUM(K37:K43)</f>
+        <v>2529.0149999999999</v>
+      </c>
+      <c r="L44" s="6">
+        <f>SUM(L37:L43)</f>
+        <v>2654.4870000000001</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
@@ -3400,9 +3448,13 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6">
-        <v>42.631</v>
-      </c>
-      <c r="T44" s="6"/>
+        <f>SUM(S37:S43)</f>
+        <v>4141.4660000000003</v>
+      </c>
+      <c r="T44" s="6">
+        <f>SUM(T37:T43)</f>
+        <v>4412.3909999999996</v>
+      </c>
       <c r="U44" s="6"/>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
@@ -3411,43 +3463,9 @@
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
     </row>
-    <row r="45" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6">
-        <v>7.3940000000000001</v>
-      </c>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6">
-        <v>12.895</v>
-      </c>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
-      <c r="AA45" s="6"/>
-    </row>
-    <row r="46" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -3458,7 +3476,8 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="K46" s="6">
-        <v>3.9590000000000001</v>
+        <f>+K17</f>
+        <v>9.7379999999999889</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -3468,9 +3487,13 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6">
-        <v>-14.125999999999999</v>
-      </c>
-      <c r="T46" s="6"/>
+        <f>+S17</f>
+        <v>42.631000000000036</v>
+      </c>
+      <c r="T46" s="6">
+        <f>+T17</f>
+        <v>43.823999999999998</v>
+      </c>
       <c r="U46" s="6"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
@@ -3479,9 +3502,9 @@
       <c r="Z46" s="6"/>
       <c r="AA46" s="6"/>
     </row>
-    <row r="47" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -3492,7 +3515,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6">
-        <v>0.84</v>
+        <v>9.7379999999999995</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -3502,7 +3525,7 @@
       <c r="Q47" s="6"/>
       <c r="R47" s="6"/>
       <c r="S47" s="6">
-        <v>0.85</v>
+        <v>42.631</v>
       </c>
       <c r="T47" s="6"/>
       <c r="U47" s="6"/>
@@ -3513,9 +3536,9 @@
       <c r="Z47" s="6"/>
       <c r="AA47" s="6"/>
     </row>
-    <row r="48" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -3526,7 +3549,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6">
-        <v>6.0220000000000002</v>
+        <v>7.3940000000000001</v>
       </c>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
@@ -3536,7 +3559,7 @@
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6">
-        <v>11.843999999999999</v>
+        <v>12.895</v>
       </c>
       <c r="T48" s="6"/>
       <c r="U48" s="6"/>
@@ -3549,7 +3572,7 @@
     </row>
     <row r="49" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -3560,7 +3583,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
       <c r="K49" s="6">
-        <v>66.884</v>
+        <v>3.9590000000000001</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
@@ -3570,7 +3593,7 @@
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6">
-        <v>135.03299999999999</v>
+        <v>-14.125999999999999</v>
       </c>
       <c r="T49" s="6"/>
       <c r="U49" s="6"/>
@@ -3583,7 +3606,7 @@
     </row>
     <row r="50" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3594,7 +3617,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
       <c r="K50" s="6">
-        <v>4.4109999999999996</v>
+        <v>0.84</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
@@ -3604,7 +3627,7 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6">
-        <v>6.81</v>
+        <v>0.85</v>
       </c>
       <c r="T50" s="6"/>
       <c r="U50" s="6"/>
@@ -3617,7 +3640,7 @@
     </row>
     <row r="51" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -3628,7 +3651,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6">
-        <v>0.79800000000000004</v>
+        <v>6.0220000000000002</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
@@ -3638,7 +3661,7 @@
       <c r="Q51" s="6"/>
       <c r="R51" s="6"/>
       <c r="S51" s="6">
-        <v>2.7320000000000002</v>
+        <v>11.843999999999999</v>
       </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
@@ -3651,7 +3674,7 @@
     </row>
     <row r="52" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
@@ -3662,7 +3685,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6">
-        <v>0.82299999999999995</v>
+        <v>66.884</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
@@ -3672,7 +3695,7 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6">
-        <v>4.2999999999999997E-2</v>
+        <v>135.03299999999999</v>
       </c>
       <c r="T52" s="6"/>
       <c r="U52" s="6"/>
@@ -3685,7 +3708,7 @@
     </row>
     <row r="53" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
@@ -3696,8 +3719,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6">
-        <f>-7.319-8.166-8.391-0.805-7.624-2.911+81.735</f>
-        <v>46.518999999999998</v>
+        <v>4.4109999999999996</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
@@ -3707,8 +3729,7 @@
       <c r="Q53" s="6"/>
       <c r="R53" s="6"/>
       <c r="S53" s="6">
-        <f>55.49-12.636-14.075+2.614-17.122-7.433+6.72</f>
-        <v>13.558</v>
+        <v>6.81</v>
       </c>
       <c r="T53" s="6"/>
       <c r="U53" s="6"/>
@@ -3721,7 +3742,7 @@
     </row>
     <row r="54" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="5" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
@@ -3732,26 +3753,19 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
       <c r="K54" s="6">
-        <f>SUM(K44:K53)</f>
-        <v>147.38799999999998</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
-      <c r="Q54" s="6">
-        <v>439.72800000000001</v>
-      </c>
+      <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6">
-        <f>SUM(S44:S53)</f>
-        <v>212.26999999999998</v>
-      </c>
-      <c r="T54" s="6">
-        <f>376-S54</f>
-        <v>163.73000000000002</v>
-      </c>
+        <v>2.7320000000000002</v>
+      </c>
+      <c r="T54" s="6"/>
       <c r="U54" s="6"/>
       <c r="V54" s="6"/>
       <c r="W54" s="6"/>
@@ -3759,6 +3773,117 @@
       <c r="Y54" s="6"/>
       <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
+    </row>
+    <row r="55" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="T55" s="6"/>
+      <c r="U55" s="6"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
+      <c r="X55" s="6"/>
+      <c r="Y55" s="6"/>
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="6"/>
+    </row>
+    <row r="56" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6">
+        <f>-7.319-8.166-8.391-0.805-7.624-2.911+81.735</f>
+        <v>46.518999999999998</v>
+      </c>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6">
+        <f>55.49-12.636-14.075+2.614-17.122-7.433+6.72</f>
+        <v>13.558</v>
+      </c>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6"/>
+    </row>
+    <row r="57" spans="2:27" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6">
+        <f>SUM(K47:K56)</f>
+        <v>147.38799999999998</v>
+      </c>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6">
+        <v>439.72800000000001</v>
+      </c>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6">
+        <f>SUM(S47:S56)</f>
+        <v>212.26999999999998</v>
+      </c>
+      <c r="T57" s="6">
+        <f>376-S57</f>
+        <v>163.73000000000002</v>
+      </c>
+      <c r="U57" s="6"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
